--- a/assets/excel/lbo-model-vedant-fashion.xlsx
+++ b/assets/excel/lbo-model-vedant-fashion.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ANVAY PORTFOLIO (WEBSITE)\Financial Modeling\CORE MODELS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Anvay Document\ANVAY-PORTFOLIO-WEBSITE\assets\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6AA5207-90E8-43FC-B149-C6F67C61AACE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF71E149-FFA9-4726-B99B-E896AACB3E9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="674" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -932,30 +932,6 @@
         </r>
       </text>
     </comment>
-    <comment ref="C77" authorId="0" shapeId="0" xr:uid="{A4449240-1F85-47F9-84AD-15F601D7D9A1}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Anvay:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-This is a standard assumption for Indian PE funds. It gives enough time for operational improvements, debt repayment, business recovery, and scaling of Twamev. The model runs from FY26 to FY31, covering the full holding period after entry.</t>
-        </r>
-      </text>
-    </comment>
     <comment ref="C78" authorId="0" shapeId="0" xr:uid="{01333104-509D-411F-B52A-550D8D899DDF}">
       <text>
         <r>
@@ -1117,9 +1093,6 @@
     <t>Hold Period:</t>
   </si>
   <si>
-    <t>5 Years (Exit: FY2031)</t>
-  </si>
-  <si>
     <t>Projection Period:</t>
   </si>
   <si>
@@ -1678,16 +1651,10 @@
     <t>Interest Expense TLA (10.5% × Avg Balance)</t>
   </si>
   <si>
-    <t>TERM LOAN B (Subordinated — 25% of EV, 12.0% p.a., Bullet Yr 7)</t>
-  </si>
-  <si>
     <t>Interest Expense TLB (12.0% × Avg Balance)</t>
   </si>
   <si>
     <t>NCD / MEZZANINE (5% of EV, 14.0% p.a., Bullet Yr 5)</t>
-  </si>
-  <si>
-    <t>(-) Repayment (Bullet at Year 5 = FY2031)</t>
   </si>
   <si>
     <t>Interest Expense NCD (14.0% × Avg Balance)</t>
@@ -1935,6 +1902,15 @@
   </si>
   <si>
     <t>INFORMATION</t>
+  </si>
+  <si>
+    <t>TERM LOAN B (Subordinated — 25% of EV, 12.0% p.a., Bullet Yr 6)</t>
+  </si>
+  <si>
+    <t>(-) Repayment (Bullet at Year 5 = FY2030)</t>
+  </si>
+  <si>
+    <t>6 Years (Exit: FY2031)</t>
   </si>
 </sst>
 </file>
@@ -3383,7 +3359,7 @@
     </row>
     <row r="10" spans="1:19" ht="18" x14ac:dyDescent="0.35">
       <c r="B10" s="125" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C10" s="125"/>
       <c r="D10" s="125"/>
@@ -3395,7 +3371,7 @@
         <v>3</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="D12" s="11"/>
       <c r="E12" s="12"/>
@@ -3445,104 +3421,104 @@
         <v>12</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>13</v>
+        <v>268</v>
       </c>
       <c r="D17" s="15"/>
       <c r="E17" s="16"/>
     </row>
     <row r="18" spans="2:5" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="C18" s="14" t="s">
         <v>14</v>
-      </c>
-      <c r="C18" s="14" t="s">
-        <v>15</v>
       </c>
       <c r="D18" s="15"/>
       <c r="E18" s="16"/>
     </row>
     <row r="19" spans="2:5" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" s="14" t="s">
         <v>16</v>
-      </c>
-      <c r="C19" s="14" t="s">
-        <v>17</v>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="16"/>
     </row>
     <row r="20" spans="2:5" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" s="18" t="s">
         <v>18</v>
-      </c>
-      <c r="C20" s="18" t="s">
-        <v>19</v>
       </c>
       <c r="D20" s="19"/>
       <c r="E20" s="20"/>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B22" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" s="21" t="s">
         <v>22</v>
-      </c>
-      <c r="C22" s="21" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="23" spans="2:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="C23" s="23" t="s">
         <v>24</v>
-      </c>
-      <c r="C23" s="23" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="24" spans="2:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="C24" s="25" t="s">
         <v>26</v>
-      </c>
-      <c r="C24" s="25" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="25" spans="2:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="C25" s="25" t="s">
         <v>28</v>
-      </c>
-      <c r="C25" s="25" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="26" spans="2:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="C26" s="25" t="s">
         <v>30</v>
-      </c>
-      <c r="C26" s="25" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="27" spans="2:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="26" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C27" s="27" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
     </row>
     <row r="28" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="29" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="28" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30" spans="2:5" ht="24" x14ac:dyDescent="0.3">
       <c r="B30" s="29" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="32" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="/sw90Jq0U5LL1NHvk77zoi5C+C2x789GENW62407Zizmj8MqIPX0DxOgF1r7wfAXlq9gCJXpd1rmgDUjzbmY6w==" saltValue="mxGAk/j0s3hjMDWzG8fLSg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="1lczmibRGI09RS4LcM7ikzIniToVvasltVAM9pQwPRNi/ODYuXfGdaf0fDuVwEflAsf5ssW+mz0SpGoWEOtfEQ==" saltValue="ysGRQ/v3n2V6yjjThTz4kQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="B10:E10"/>
   </mergeCells>
@@ -3593,12 +3569,12 @@
     <row r="3" spans="2:12" ht="8.4" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="2:12" ht="18" x14ac:dyDescent="0.35">
       <c r="B4" s="31" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
     </row>
     <row r="5" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="2" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.3"/>
@@ -3617,7 +3593,7 @@
     </row>
     <row r="9" spans="2:12" s="34" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="32" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C9" s="33"/>
       <c r="D9" s="33"/>
@@ -3632,42 +3608,42 @@
     </row>
     <row r="10" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="35" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="C10" s="36" t="s">
+      <c r="D10" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="D10" s="36" t="s">
+      <c r="E10" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="E10" s="36" t="s">
+      <c r="F10" s="36" t="s">
         <v>37</v>
       </c>
-      <c r="F10" s="36" t="s">
+      <c r="G10" s="36" t="s">
         <v>38</v>
       </c>
-      <c r="G10" s="36" t="s">
+      <c r="H10" s="36" t="s">
         <v>39</v>
       </c>
-      <c r="H10" s="36" t="s">
+      <c r="I10" s="36" t="s">
         <v>40</v>
       </c>
-      <c r="I10" s="36" t="s">
+      <c r="J10" s="36" t="s">
         <v>41</v>
       </c>
-      <c r="J10" s="36" t="s">
+      <c r="K10" s="36" t="s">
         <v>42</v>
       </c>
-      <c r="K10" s="36" t="s">
+      <c r="L10" s="36" t="s">
         <v>43</v>
-      </c>
-      <c r="L10" s="36" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="11" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="37" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C11" s="38">
         <v>1.19</v>
@@ -3702,7 +3678,7 @@
     </row>
     <row r="12" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="37" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C12" s="38">
         <v>10</v>
@@ -3737,25 +3713,25 @@
     </row>
     <row r="13" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="C13" s="39" t="s">
         <v>47</v>
       </c>
-      <c r="C13" s="39" t="s">
-        <v>48</v>
-      </c>
       <c r="D13" s="39" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E13" s="39" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F13" s="39" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G13" s="39" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H13" s="39" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I13" s="38">
         <v>966.95</v>
@@ -3772,34 +3748,34 @@
     </row>
     <row r="14" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="37" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C14" s="39" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D14" s="39" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E14" s="39" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F14" s="39" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G14" s="39" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H14" s="39" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I14" s="39" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J14" s="39" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K14" s="39" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="L14" s="38">
         <v>8506.49</v>
@@ -3807,7 +3783,7 @@
     </row>
     <row r="15" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="37" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D15" s="40"/>
       <c r="E15" s="40"/>
@@ -3823,7 +3799,7 @@
     </row>
     <row r="17" spans="2:23" s="34" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="32" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="C17" s="33"/>
       <c r="D17" s="33"/>
@@ -3838,42 +3814,42 @@
     </row>
     <row r="18" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="35" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="C18" s="36" t="s">
+      <c r="D18" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="D18" s="36" t="s">
+      <c r="E18" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="E18" s="36" t="s">
+      <c r="F18" s="36" t="s">
         <v>37</v>
       </c>
-      <c r="F18" s="36" t="s">
+      <c r="G18" s="36" t="s">
         <v>38</v>
       </c>
-      <c r="G18" s="36" t="s">
+      <c r="H18" s="36" t="s">
         <v>39</v>
       </c>
-      <c r="H18" s="36" t="s">
+      <c r="I18" s="36" t="s">
         <v>40</v>
       </c>
-      <c r="I18" s="36" t="s">
+      <c r="J18" s="36" t="s">
         <v>41</v>
       </c>
-      <c r="J18" s="36" t="s">
+      <c r="K18" s="36" t="s">
         <v>42</v>
       </c>
-      <c r="K18" s="36" t="s">
+      <c r="L18" s="36" t="s">
         <v>43</v>
-      </c>
-      <c r="L18" s="36" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="19" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="37" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C19" s="38">
         <v>504.28</v>
@@ -3908,7 +3884,7 @@
     </row>
     <row r="20" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="37" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C20" s="38">
         <v>107.72</v>
@@ -3944,7 +3920,7 @@
     </row>
     <row r="21" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="37" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C21" s="42"/>
       <c r="D21" s="38">
@@ -3977,7 +3953,7 @@
     </row>
     <row r="22" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="37" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C22" s="42"/>
       <c r="D22" s="38">
@@ -4010,7 +3986,7 @@
     </row>
     <row r="23" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="37" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C23" s="42"/>
       <c r="D23" s="38">
@@ -4044,7 +4020,7 @@
     </row>
     <row r="24" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="37" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C24" s="42"/>
       <c r="D24" s="38">
@@ -4085,7 +4061,7 @@
     </row>
     <row r="25" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="37" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C25" s="38">
         <v>246.07</v>
@@ -4130,7 +4106,7 @@
     </row>
     <row r="26" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="45" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C26" s="53">
         <f>IFERROR(C20+C21+C22+C23+C24+C25,"")</f>
@@ -4185,7 +4161,7 @@
     </row>
     <row r="27" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="45" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C27" s="53">
         <f>C31+C30+C29-C28</f>
@@ -4240,7 +4216,7 @@
     </row>
     <row r="28" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="37" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C28" s="38">
         <v>1.84</v>
@@ -4285,7 +4261,7 @@
     </row>
     <row r="29" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="37" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C29" s="38">
         <v>7.33</v>
@@ -4330,7 +4306,7 @@
     </row>
     <row r="30" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="37" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C30" s="38">
         <v>5.97</v>
@@ -4375,7 +4351,7 @@
     </row>
     <row r="31" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" s="37" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C31" s="38">
         <v>139.03</v>
@@ -4420,7 +4396,7 @@
     </row>
     <row r="32" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="37" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C32" s="38">
         <v>48.87</v>
@@ -4465,7 +4441,7 @@
     </row>
     <row r="33" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="45" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C33" s="46">
         <v>90.16</v>
@@ -4510,7 +4486,7 @@
     </row>
     <row r="34" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="37" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C34" s="38">
         <v>11.86</v>
@@ -4547,7 +4523,7 @@
     </row>
     <row r="36" spans="2:23" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="47" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C36" s="48"/>
       <c r="D36" s="48"/>
@@ -4562,42 +4538,42 @@
     </row>
     <row r="37" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="35" t="s">
+        <v>33</v>
+      </c>
+      <c r="C37" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="C37" s="36" t="s">
+      <c r="D37" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="D37" s="36" t="s">
+      <c r="E37" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="E37" s="36" t="s">
+      <c r="F37" s="36" t="s">
         <v>37</v>
       </c>
-      <c r="F37" s="36" t="s">
+      <c r="G37" s="36" t="s">
         <v>38</v>
       </c>
-      <c r="G37" s="36" t="s">
+      <c r="H37" s="36" t="s">
         <v>39</v>
       </c>
-      <c r="H37" s="36" t="s">
+      <c r="I37" s="36" t="s">
         <v>40</v>
       </c>
-      <c r="I37" s="36" t="s">
+      <c r="J37" s="36" t="s">
         <v>41</v>
       </c>
-      <c r="J37" s="36" t="s">
+      <c r="K37" s="36" t="s">
         <v>42</v>
       </c>
-      <c r="K37" s="36" t="s">
+      <c r="L37" s="36" t="s">
         <v>43</v>
-      </c>
-      <c r="L37" s="36" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="38" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="37" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C38" s="38">
         <v>11.86</v>
@@ -4632,7 +4608,7 @@
     </row>
     <row r="39" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="37" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C39" s="38">
         <v>221.12</v>
@@ -4667,7 +4643,7 @@
     </row>
     <row r="40" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="45" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C40" s="53">
         <f>IFERROR(C38+C39,"")</f>
@@ -4712,7 +4688,7 @@
     </row>
     <row r="41" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="45" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C41" s="49">
         <v>21.76</v>
@@ -4745,7 +4721,7 @@
     </row>
     <row r="42" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="37" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C42" s="38">
         <v>109.35</v>
@@ -4780,7 +4756,7 @@
     </row>
     <row r="43" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="45" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C43" s="54">
         <f>C40+C41+C42</f>
@@ -4825,7 +4801,7 @@
     </row>
     <row r="44" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="37" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C44" s="38">
         <v>104.06</v>
@@ -4860,7 +4836,7 @@
     </row>
     <row r="45" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B45" s="37" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C45" s="38">
         <v>3.06</v>
@@ -4895,7 +4871,7 @@
     </row>
     <row r="46" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B46" s="37" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C46" s="51"/>
       <c r="D46" s="38">
@@ -4928,7 +4904,7 @@
     </row>
     <row r="47" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B47" s="37" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C47" s="38">
         <v>62.240000000000009</v>
@@ -4963,7 +4939,7 @@
     </row>
     <row r="48" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B48" s="37" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C48" s="38">
         <v>107.19</v>
@@ -4998,7 +4974,7 @@
     </row>
     <row r="49" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B49" s="37" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C49" s="38">
         <v>85.86</v>
@@ -5033,7 +5009,7 @@
     </row>
     <row r="50" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B50" s="37" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C50" s="38">
         <v>1.68</v>
@@ -5068,7 +5044,7 @@
     </row>
     <row r="51" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B51" s="45" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C51" s="49">
         <v>364.09</v>
@@ -5106,7 +5082,7 @@
     </row>
     <row r="53" spans="2:12" s="34" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B53" s="32" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C53" s="33"/>
       <c r="D53" s="33"/>
@@ -5121,42 +5097,42 @@
     </row>
     <row r="54" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B54" s="35" t="s">
+        <v>33</v>
+      </c>
+      <c r="C54" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="C54" s="36" t="s">
+      <c r="D54" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="D54" s="36" t="s">
+      <c r="E54" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="E54" s="36" t="s">
+      <c r="F54" s="36" t="s">
         <v>37</v>
       </c>
-      <c r="F54" s="36" t="s">
+      <c r="G54" s="36" t="s">
         <v>38</v>
       </c>
-      <c r="G54" s="36" t="s">
+      <c r="H54" s="36" t="s">
         <v>39</v>
       </c>
-      <c r="H54" s="36" t="s">
+      <c r="I54" s="36" t="s">
         <v>40</v>
       </c>
-      <c r="I54" s="36" t="s">
+      <c r="J54" s="36" t="s">
         <v>41</v>
       </c>
-      <c r="J54" s="36" t="s">
+      <c r="K54" s="36" t="s">
         <v>42</v>
       </c>
-      <c r="K54" s="36" t="s">
+      <c r="L54" s="36" t="s">
         <v>43</v>
-      </c>
-      <c r="L54" s="36" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="55" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B55" s="37" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C55" s="52"/>
       <c r="D55" s="38">
@@ -5189,7 +5165,7 @@
     </row>
     <row r="56" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B56" s="37" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C56" s="52"/>
       <c r="D56" s="38">
@@ -5222,7 +5198,7 @@
     </row>
     <row r="57" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B57" s="37" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C57" s="52"/>
       <c r="D57" s="38">
@@ -5255,7 +5231,7 @@
     </row>
     <row r="58" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B58" s="37" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C58" s="52"/>
       <c r="D58" s="38">
@@ -5288,7 +5264,7 @@
     </row>
     <row r="60" spans="2:12" s="34" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B60" s="32" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C60" s="33"/>
       <c r="D60" s="33"/>
@@ -5303,42 +5279,42 @@
     </row>
     <row r="61" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B61" s="35" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C61" s="36" t="s">
+        <v>84</v>
+      </c>
+      <c r="D61" s="36" t="s">
         <v>85</v>
       </c>
-      <c r="D61" s="36" t="s">
+      <c r="E61" s="36" t="s">
         <v>86</v>
       </c>
-      <c r="E61" s="36" t="s">
+      <c r="F61" s="36" t="s">
         <v>87</v>
       </c>
-      <c r="F61" s="36" t="s">
+      <c r="G61" s="36" t="s">
         <v>88</v>
       </c>
-      <c r="G61" s="36" t="s">
+      <c r="H61" s="36" t="s">
         <v>89</v>
       </c>
-      <c r="H61" s="36" t="s">
+      <c r="I61" s="36" t="s">
         <v>90</v>
       </c>
-      <c r="I61" s="36" t="s">
+      <c r="J61" s="36" t="s">
         <v>91</v>
       </c>
-      <c r="J61" s="36" t="s">
+      <c r="K61" s="36" t="s">
         <v>92</v>
       </c>
-      <c r="K61" s="36" t="s">
+      <c r="L61" s="36" t="s">
         <v>93</v>
-      </c>
-      <c r="L61" s="36" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="62" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B62" s="37" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C62" s="38">
         <v>217.86</v>
@@ -5373,7 +5349,7 @@
     </row>
     <row r="63" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B63" s="37" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C63" s="38">
         <v>125.13</v>
@@ -5408,7 +5384,7 @@
     </row>
     <row r="64" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B64" s="45" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C64" s="49">
         <v>92.73</v>
@@ -5443,7 +5419,7 @@
     </row>
     <row r="65" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B65" s="45" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C65" s="55">
         <f>IFERROR(C64/C62,"")</f>
@@ -5488,7 +5464,7 @@
     </row>
     <row r="66" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B66" s="37" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C66" s="38">
         <v>14.79</v>
@@ -5523,7 +5499,7 @@
     </row>
     <row r="67" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B67" s="37" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C67" s="38">
         <v>31.81</v>
@@ -5558,7 +5534,7 @@
     </row>
     <row r="68" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B68" s="37" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C68" s="38">
         <v>10.68</v>
@@ -5593,7 +5569,7 @@
     </row>
     <row r="69" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B69" s="37" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C69" s="38">
         <v>65.03</v>
@@ -5628,7 +5604,7 @@
     </row>
     <row r="70" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B70" s="37" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C70" s="38">
         <v>16.05</v>
@@ -5663,7 +5639,7 @@
     </row>
     <row r="71" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B71" s="45" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C71" s="49">
         <v>48.99</v>
@@ -5736,7 +5712,7 @@
     </row>
     <row r="3" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="56" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -5758,14 +5734,14 @@
     </row>
     <row r="6" spans="2:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="32" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C6" s="33"/>
       <c r="D6" s="33"/>
     </row>
     <row r="7" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="37" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D7" s="86">
         <f>'Data Sheet'!L19</f>
@@ -5775,7 +5751,7 @@
     </row>
     <row r="8" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="37" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D8" s="86">
         <f>'Data Sheet'!L27</f>
@@ -5785,7 +5761,7 @@
     </row>
     <row r="9" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="37" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D9" s="93">
         <f>D8/D7</f>
@@ -5795,7 +5771,7 @@
     </row>
     <row r="10" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="37" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D10" s="86">
         <f>'Data Sheet'!L29</f>
@@ -5805,7 +5781,7 @@
     </row>
     <row r="11" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="37" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D11" s="94">
         <f>D8-D10</f>
@@ -5815,7 +5791,7 @@
     </row>
     <row r="12" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="37" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D12" s="86">
         <f>'Data Sheet'!L30</f>
@@ -5825,7 +5801,7 @@
     </row>
     <row r="13" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="37" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D13" s="86">
         <f>'Data Sheet'!L31</f>
@@ -5835,7 +5811,7 @@
     </row>
     <row r="14" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="37" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D14" s="93">
         <f>'Data Sheet'!L32/'Data Sheet'!L31</f>
@@ -5845,7 +5821,7 @@
     </row>
     <row r="15" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="37" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D15" s="86">
         <f>'Data Sheet'!L33</f>
@@ -5855,7 +5831,7 @@
     </row>
     <row r="16" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="37" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D16" s="59">
         <v>114</v>
@@ -5864,7 +5840,7 @@
     </row>
     <row r="17" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="37" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D17" s="59">
         <v>104</v>
@@ -5873,7 +5849,7 @@
     </row>
     <row r="18" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="37" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D18" s="86">
         <f>'Data Sheet'!L41</f>
@@ -5883,7 +5859,7 @@
     </row>
     <row r="19" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="37" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D19" s="86">
         <f>'Data Sheet'!L50</f>
@@ -5893,7 +5869,7 @@
     </row>
     <row r="20" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="37" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D20" s="86">
         <f>D18-D19</f>
@@ -5903,14 +5879,14 @@
     </row>
     <row r="22" spans="2:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="32" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C22" s="33"/>
       <c r="D22" s="33"/>
     </row>
     <row r="23" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="37" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D23" s="59">
         <v>350.1</v>
@@ -5919,7 +5895,7 @@
     </row>
     <row r="24" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="37" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D24" s="86">
         <f>'Data Sheet'!L11</f>
@@ -5929,7 +5905,7 @@
     </row>
     <row r="25" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="37" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D25" s="95">
         <f>D23*D24</f>
@@ -5939,7 +5915,7 @@
     </row>
     <row r="26" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="37" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D26" s="61">
         <v>0.3</v>
@@ -5948,7 +5924,7 @@
     </row>
     <row r="27" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="37" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D27" s="86">
         <f>D23*(1+D26)</f>
@@ -5958,7 +5934,7 @@
     </row>
     <row r="28" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="37" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D28" s="86">
         <f>D27*D24</f>
@@ -5968,7 +5944,7 @@
     </row>
     <row r="29" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="37" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D29" s="86">
         <f>D18</f>
@@ -5978,7 +5954,7 @@
     </row>
     <row r="30" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="37" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D30" s="86">
         <f>D19</f>
@@ -5988,7 +5964,7 @@
     </row>
     <row r="31" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" s="45" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D31" s="95">
         <f>D28+D29-D30</f>
@@ -5998,7 +5974,7 @@
     </row>
     <row r="32" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="45" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D32" s="96">
         <f>D31/D8</f>
@@ -6008,7 +5984,7 @@
     </row>
     <row r="33" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="37" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D33" s="61">
         <v>0.02</v>
@@ -6017,7 +5993,7 @@
     </row>
     <row r="34" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="37" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D34" s="86">
         <f>D33*D31</f>
@@ -6027,7 +6003,7 @@
     </row>
     <row r="35" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="62" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C35" s="62"/>
       <c r="D35" s="112">
@@ -6038,7 +6014,7 @@
     </row>
     <row r="37" spans="2:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="126" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C37" s="126"/>
       <c r="D37" s="126"/>
@@ -6050,29 +6026,29 @@
     </row>
     <row r="38" spans="2:9" s="68" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="63" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C38" s="63"/>
       <c r="D38" s="63"/>
       <c r="E38" s="64" t="s">
+        <v>131</v>
+      </c>
+      <c r="F38" s="65" t="s">
         <v>132</v>
       </c>
-      <c r="F38" s="65" t="s">
+      <c r="G38" s="66" t="s">
         <v>133</v>
       </c>
-      <c r="G38" s="66" t="s">
+      <c r="H38" s="65" t="s">
         <v>134</v>
       </c>
-      <c r="H38" s="65" t="s">
+      <c r="I38" s="67" t="s">
         <v>135</v>
-      </c>
-      <c r="I38" s="67" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="39" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="37" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E39" s="69">
         <v>1800</v>
@@ -6094,7 +6070,7 @@
     </row>
     <row r="40" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="37" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E40" s="69">
         <v>700</v>
@@ -6116,7 +6092,7 @@
     </row>
     <row r="41" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="37" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E41" s="69">
         <v>200</v>
@@ -6138,7 +6114,7 @@
     </row>
     <row r="42" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="45" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C42" s="45"/>
       <c r="D42" s="45"/>
@@ -6162,7 +6138,7 @@
     </row>
     <row r="43" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="72" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C43" s="72"/>
       <c r="D43" s="72"/>
@@ -6177,7 +6153,7 @@
     </row>
     <row r="44" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="62" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C44" s="62"/>
       <c r="D44" s="62"/>
@@ -6193,7 +6169,7 @@
     <row r="45" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="46" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B46" s="76" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C46" s="77"/>
       <c r="D46" s="77"/>
@@ -6203,18 +6179,18 @@
     </row>
     <row r="47" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E47" s="78" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="F47" s="78" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="G47" s="78" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="48" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B48" s="2" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="E48" s="100">
         <f>E39</f>
@@ -6231,7 +6207,7 @@
     </row>
     <row r="49" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B49" s="2" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="E49" s="100">
         <f>E40</f>
@@ -6248,7 +6224,7 @@
     </row>
     <row r="50" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B50" s="2" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="E50" s="100">
         <f>E41</f>
@@ -6265,7 +6241,7 @@
     </row>
     <row r="51" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B51" s="2" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="E51" s="100">
         <f>E43</f>
@@ -6282,7 +6258,7 @@
     </row>
     <row r="52" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B52" s="79" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C52" s="80"/>
       <c r="D52" s="80"/>
@@ -6302,7 +6278,7 @@
     <row r="53" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="54" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B54" s="76" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="C54" s="76"/>
       <c r="D54" s="76"/>
@@ -6312,18 +6288,18 @@
     </row>
     <row r="55" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E55" s="78" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="F55" s="78" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="G55" s="78" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="56" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B56" s="2" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="E56" s="100">
         <f>D28</f>
@@ -6340,7 +6316,7 @@
     </row>
     <row r="57" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B57" s="2" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="E57" s="100">
         <f>D29</f>
@@ -6357,7 +6333,7 @@
     </row>
     <row r="58" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B58" s="2" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="E58" s="100">
         <f>D34</f>
@@ -6374,7 +6350,7 @@
     </row>
     <row r="59" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B59" s="79" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C59" s="80"/>
       <c r="D59" s="80"/>
@@ -6394,7 +6370,7 @@
     <row r="60" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="61" spans="2:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B61" s="32" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C61" s="33"/>
       <c r="D61" s="33"/>
@@ -6406,36 +6382,36 @@
     </row>
     <row r="62" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B62" s="35" t="s">
+        <v>143</v>
+      </c>
+      <c r="C62" s="81" t="s">
         <v>144</v>
       </c>
-      <c r="C62" s="81" t="s">
+      <c r="D62" s="81" t="s">
         <v>145</v>
       </c>
-      <c r="D62" s="81" t="s">
+      <c r="E62" s="81" t="s">
         <v>146</v>
       </c>
-      <c r="E62" s="81" t="s">
+      <c r="F62" s="81" t="s">
         <v>147</v>
       </c>
-      <c r="F62" s="81" t="s">
+      <c r="G62" s="81" t="s">
         <v>148</v>
       </c>
-      <c r="G62" s="81" t="s">
+      <c r="H62" s="81" t="s">
         <v>149</v>
       </c>
-      <c r="H62" s="81" t="s">
+      <c r="I62" s="81" t="s">
         <v>150</v>
-      </c>
-      <c r="I62" s="81" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="63" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B63" s="45" t="s">
+        <v>151</v>
+      </c>
+      <c r="C63" s="82" t="s">
         <v>152</v>
-      </c>
-      <c r="C63" s="82" t="s">
-        <v>153</v>
       </c>
       <c r="D63" s="83">
         <v>0.06</v>
@@ -6459,10 +6435,10 @@
     <row r="64" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="65" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B65" s="45" t="s">
+        <v>153</v>
+      </c>
+      <c r="C65" s="82" t="s">
         <v>154</v>
-      </c>
-      <c r="C65" s="82" t="s">
-        <v>155</v>
       </c>
       <c r="D65" s="83">
         <v>0.44</v>
@@ -6486,10 +6462,10 @@
     <row r="66" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="67" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B67" s="45" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C67" s="82" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D67" s="83">
         <v>0.11</v>
@@ -6513,10 +6489,10 @@
     <row r="68" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="69" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B69" s="45" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C69" s="82" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D69" s="83">
         <v>8.5000000000000006E-2</v>
@@ -6540,10 +6516,10 @@
     <row r="70" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="71" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B71" s="45" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C71" s="82" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D71" s="83">
         <v>5.5E-2</v>
@@ -6567,10 +6543,10 @@
     <row r="72" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="73" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B73" s="45" t="s">
+        <v>158</v>
+      </c>
+      <c r="C73" s="82" t="s">
         <v>159</v>
-      </c>
-      <c r="C73" s="82" t="s">
-        <v>160</v>
       </c>
       <c r="D73" s="83">
         <v>0.252</v>
@@ -6594,7 +6570,7 @@
     <row r="74" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="76" spans="2:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B76" s="32" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C76" s="33"/>
       <c r="D76" s="33"/>
@@ -6606,16 +6582,16 @@
     </row>
     <row r="77" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B77" s="37" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C77" s="71">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E77" s="84"/>
     </row>
     <row r="78" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B78" s="45" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C78" s="85">
         <v>22</v>
@@ -6624,7 +6600,7 @@
     </row>
     <row r="79" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B79" s="45" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C79" s="105">
         <f>Financials!M10*C78</f>
@@ -6634,7 +6610,7 @@
     </row>
     <row r="80" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B80" s="37" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C80" s="105">
         <f>C79-'Debt Schedule'!H19</f>
@@ -6643,7 +6619,7 @@
       <c r="E80" s="84"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="dvRGY2rji6dVh9p3nwSAVkiocgp37Ysg9pSJ1HGYMLRlM9zkGG9CwZLf0cgChMkZzY5ZhtqVT6/+F1yXNECo8A==" saltValue="U/UjOsZaqR5AgVZanyynoA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="cKgYt20wjkH6wCjheLSwEOPiTCvvBJmq2SDyPOE+L4ST9RYK+DUnCya3rltdNG9jFriUtUvOzPOlw3t1xI3sLg==" saltValue="3HDXUZyu4YMZbX49MIsj+g==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="B37:I37"/>
   </mergeCells>
@@ -6687,7 +6663,7 @@
     </row>
     <row r="3" spans="2:20" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="106" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -6719,45 +6695,45 @@
     </row>
     <row r="6" spans="2:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="107" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="C6" s="81" t="s">
+        <v>166</v>
+      </c>
+      <c r="D6" s="81" t="s">
         <v>167</v>
       </c>
-      <c r="D6" s="81" t="s">
+      <c r="E6" s="81" t="s">
         <v>168</v>
       </c>
-      <c r="E6" s="81" t="s">
+      <c r="F6" s="81" t="s">
         <v>169</v>
       </c>
-      <c r="F6" s="81" t="s">
+      <c r="G6" s="81" t="s">
         <v>170</v>
       </c>
-      <c r="G6" s="81" t="s">
-        <v>171</v>
-      </c>
       <c r="H6" s="108" t="s">
+        <v>145</v>
+      </c>
+      <c r="I6" s="108" t="s">
         <v>146</v>
       </c>
-      <c r="I6" s="108" t="s">
+      <c r="J6" s="108" t="s">
         <v>147</v>
       </c>
-      <c r="J6" s="108" t="s">
+      <c r="K6" s="108" t="s">
         <v>148</v>
       </c>
-      <c r="K6" s="108" t="s">
+      <c r="L6" s="108" t="s">
         <v>149</v>
       </c>
-      <c r="L6" s="108" t="s">
+      <c r="M6" s="108" t="s">
         <v>150</v>
-      </c>
-      <c r="M6" s="108" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="7" spans="2:20" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="32" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C7" s="32"/>
       <c r="D7" s="32"/>
@@ -6773,7 +6749,7 @@
     </row>
     <row r="8" spans="2:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="45" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C8" s="95">
         <f>'Data Sheet'!H19</f>
@@ -6822,10 +6798,10 @@
     </row>
     <row r="9" spans="2:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="107" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C9" s="109" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D9" s="99">
         <f>D8/C8-1</f>
@@ -6870,7 +6846,7 @@
     </row>
     <row r="10" spans="2:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="45" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C10" s="95">
         <f>'Data Sheet'!H27</f>
@@ -6919,7 +6895,7 @@
     </row>
     <row r="11" spans="2:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="110" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C11" s="99">
         <f>C10/C8</f>
@@ -6968,7 +6944,7 @@
     </row>
     <row r="12" spans="2:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="37" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C12" s="86">
         <f>'Data Sheet'!H29</f>
@@ -7017,7 +6993,7 @@
     </row>
     <row r="13" spans="2:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="45" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C13" s="95">
         <f>C10-C12</f>
@@ -7066,7 +7042,7 @@
     </row>
     <row r="14" spans="2:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="37" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C14" s="86">
         <f>'Data Sheet'!H30</f>
@@ -7115,7 +7091,7 @@
     </row>
     <row r="15" spans="2:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="45" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C15" s="95">
         <f>C13-C14</f>
@@ -7164,7 +7140,7 @@
     </row>
     <row r="16" spans="2:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="37" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C16" s="86">
         <f>'Data Sheet'!H32</f>
@@ -7213,7 +7189,7 @@
     </row>
     <row r="17" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="45" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C17" s="95">
         <f>C15-C16</f>
@@ -7262,7 +7238,7 @@
     </row>
     <row r="18" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="110" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C18" s="99">
         <f>IFERROR(C17/C8,"")</f>
@@ -7311,7 +7287,7 @@
     </row>
     <row r="20" spans="2:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="32" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C20" s="32"/>
       <c r="D20" s="32"/>
@@ -7327,7 +7303,7 @@
     </row>
     <row r="21" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="45" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C21" s="95">
         <f>C10</f>
@@ -7376,7 +7352,7 @@
     </row>
     <row r="22" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="37" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C22" s="86">
         <f t="shared" ref="C22:M22" si="8">C14</f>
@@ -7425,7 +7401,7 @@
     </row>
     <row r="23" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="37" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C23" s="86">
         <f t="shared" ref="C23:L23" si="9">C16</f>
@@ -7474,7 +7450,7 @@
     </row>
     <row r="24" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="37" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C24" s="59">
         <v>23</v>
@@ -7519,7 +7495,7 @@
     </row>
     <row r="25" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="37" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C25" s="59">
         <v>-39</v>
@@ -7564,7 +7540,7 @@
     </row>
     <row r="26" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="37" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C26" s="59">
         <v>0</v>
@@ -7608,7 +7584,7 @@
     </row>
     <row r="27" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="62" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C27" s="112">
         <f t="shared" ref="C27:L27" si="10">C21-C22-C23-C24-C25-C26</f>
@@ -7657,7 +7633,7 @@
     </row>
     <row r="29" spans="2:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="32" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C29" s="32"/>
       <c r="D29" s="32"/>
@@ -7673,45 +7649,45 @@
     </row>
     <row r="30" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="35" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C30" s="81" t="s">
+        <v>166</v>
+      </c>
+      <c r="D30" s="81" t="s">
         <v>167</v>
       </c>
-      <c r="D30" s="81" t="s">
+      <c r="E30" s="81" t="s">
         <v>168</v>
       </c>
-      <c r="E30" s="81" t="s">
+      <c r="F30" s="81" t="s">
         <v>169</v>
       </c>
-      <c r="F30" s="81" t="s">
+      <c r="G30" s="81" t="s">
         <v>170</v>
       </c>
-      <c r="G30" s="81" t="s">
-        <v>171</v>
-      </c>
       <c r="H30" s="108" t="s">
+        <v>145</v>
+      </c>
+      <c r="I30" s="108" t="s">
         <v>146</v>
       </c>
-      <c r="I30" s="108" t="s">
+      <c r="J30" s="108" t="s">
         <v>147</v>
       </c>
-      <c r="J30" s="108" t="s">
+      <c r="K30" s="108" t="s">
         <v>148</v>
       </c>
-      <c r="K30" s="108" t="s">
+      <c r="L30" s="108" t="s">
         <v>149</v>
       </c>
-      <c r="L30" s="108" t="s">
+      <c r="M30" s="108" t="s">
         <v>150</v>
-      </c>
-      <c r="M30" s="108" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="31" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" s="111" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C31" s="99">
         <f t="shared" ref="C31:M31" si="11">IFERROR(C10/C8,"")</f>
@@ -7760,7 +7736,7 @@
     </row>
     <row r="32" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="111" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C32" s="99">
         <f t="shared" ref="C32:M32" si="12">IFERROR(C17/C8,"")</f>
@@ -7809,7 +7785,7 @@
     </row>
     <row r="33" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="111" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C33" s="99">
         <f>IFERROR(C24/C8,"")</f>
@@ -7858,7 +7834,7 @@
     </row>
     <row r="34" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="111" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C34" s="99">
         <f t="shared" ref="C34:M34" si="14">IFERROR(C27/C10,"")</f>
@@ -7940,7 +7916,7 @@
     </row>
     <row r="3" spans="2:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="56" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -7960,30 +7936,30 @@
     </row>
     <row r="6" spans="2:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="57" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C6" s="108" t="s">
+        <v>145</v>
+      </c>
+      <c r="D6" s="108" t="s">
         <v>146</v>
       </c>
-      <c r="D6" s="108" t="s">
+      <c r="E6" s="108" t="s">
         <v>147</v>
       </c>
-      <c r="E6" s="108" t="s">
+      <c r="F6" s="108" t="s">
         <v>148</v>
       </c>
-      <c r="F6" s="108" t="s">
+      <c r="G6" s="108" t="s">
         <v>149</v>
       </c>
-      <c r="G6" s="108" t="s">
+      <c r="H6" s="108" t="s">
         <v>150</v>
-      </c>
-      <c r="H6" s="108" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="7" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="32" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C7" s="32"/>
       <c r="D7" s="32"/>
@@ -7994,7 +7970,7 @@
     </row>
     <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="37" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C8" s="86">
         <f>Assumptions!E39</f>
@@ -8023,7 +7999,7 @@
     </row>
     <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="37" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C9" s="87">
         <f>IFERROR($C$8*0.2,0)</f>
@@ -8051,7 +8027,7 @@
     </row>
     <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="37" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C10" s="87">
         <f t="shared" ref="C10:G10" si="1">IFERROR((C8+C11)/2*0.105,0)</f>
@@ -8080,7 +8056,7 @@
     </row>
     <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="45" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C11" s="88">
         <f>MAX(0,C8-C9)</f>
@@ -8110,7 +8086,7 @@
     <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="13" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="32" t="s">
-        <v>200</v>
+        <v>266</v>
       </c>
       <c r="C13" s="32"/>
       <c r="D13" s="32"/>
@@ -8121,7 +8097,7 @@
     </row>
     <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="37" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C14" s="86">
         <f>Assumptions!E40</f>
@@ -8150,7 +8126,7 @@
     </row>
     <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="37" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C15" s="59">
         <v>0</v>
@@ -8173,7 +8149,7 @@
     </row>
     <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="45" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C16" s="88">
         <f t="shared" ref="C16:H16" si="3">C14-C15</f>
@@ -8202,7 +8178,7 @@
     </row>
     <row r="17" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="37" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C17" s="87">
         <f t="shared" ref="C17:F17" si="4">(C14+C16)/2*0.12</f>
@@ -8232,7 +8208,7 @@
     </row>
     <row r="19" spans="2:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="32" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C19" s="32"/>
       <c r="D19" s="32"/>
@@ -8243,7 +8219,7 @@
     </row>
     <row r="20" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="37" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C20" s="86">
         <f>Assumptions!E41</f>
@@ -8272,7 +8248,7 @@
     </row>
     <row r="21" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="37" t="s">
-        <v>203</v>
+        <v>267</v>
       </c>
       <c r="C21" s="59">
         <v>0</v>
@@ -8296,7 +8272,7 @@
     </row>
     <row r="22" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="45" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C22" s="88">
         <f>MAX(0,C20-C21)</f>
@@ -8325,7 +8301,7 @@
     </row>
     <row r="23" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="37" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C23" s="87">
         <f t="shared" ref="C23:H23" si="6">(C20+C22)/2*0.14</f>
@@ -8354,7 +8330,7 @@
     </row>
     <row r="25" spans="2:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="32" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="C25" s="32"/>
       <c r="D25" s="32"/>
@@ -8365,7 +8341,7 @@
     </row>
     <row r="26" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="37" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="C26" s="88">
         <f t="shared" ref="C26:H26" si="7">C10+C17+C23</f>
@@ -8394,7 +8370,7 @@
     </row>
     <row r="27" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="37" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C27" s="87">
         <f t="shared" ref="C27:H27" si="8">C11+C16+C22</f>
@@ -8423,7 +8399,7 @@
     </row>
     <row r="28" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="37" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C28" s="90">
         <f>IFERROR(C27/Financials!H10,"")</f>
@@ -8452,7 +8428,7 @@
     </row>
     <row r="29" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="37" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C29" s="87">
         <f>C9+C15+C21</f>
@@ -8506,7 +8482,7 @@
     </row>
     <row r="3" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="56" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -8518,39 +8494,39 @@
     </row>
     <row r="6" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="32" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C6" s="32"/>
       <c r="D6" s="32"/>
     </row>
     <row r="7" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="37" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="D7" s="114" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="8" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="37" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D8" s="114" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="9" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="37" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D9" s="117">
         <f>Assumptions!C77</f>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="37" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="D10" s="86">
         <f>Assumptions!D31</f>
@@ -8559,7 +8535,7 @@
     </row>
     <row r="11" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="37" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="D11" s="86">
         <f>Assumptions!E43</f>
@@ -8568,7 +8544,7 @@
     </row>
     <row r="12" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="37" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="D12" s="86">
         <f>Assumptions!D8</f>
@@ -8577,7 +8553,7 @@
     </row>
     <row r="13" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="37" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D13" s="97">
         <f>Assumptions!D32</f>
@@ -8586,14 +8562,14 @@
     </row>
     <row r="15" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="32" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C15" s="32"/>
       <c r="D15" s="32"/>
     </row>
     <row r="16" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="37" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="D16" s="94">
         <f>Financials!M10</f>
@@ -8602,7 +8578,7 @@
     </row>
     <row r="17" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="37" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="D17" s="118">
         <f>Assumptions!C78</f>
@@ -8611,7 +8587,7 @@
     </row>
     <row r="18" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="45" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C18" s="45"/>
       <c r="D18" s="105">
@@ -8621,7 +8597,7 @@
     </row>
     <row r="19" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="37" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="D19" s="86">
         <f>'Debt Schedule'!H27</f>
@@ -8630,7 +8606,7 @@
     </row>
     <row r="20" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="37" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D20" s="94">
         <f>D18-D19</f>
@@ -8639,7 +8615,7 @@
     </row>
     <row r="21" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="37" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D21" s="87">
         <f>D20*0.05</f>
@@ -8648,7 +8624,7 @@
     </row>
     <row r="22" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="45" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C22" s="45"/>
       <c r="D22" s="119">
@@ -8658,23 +8634,23 @@
     </row>
     <row r="25" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="32" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C25" s="32"/>
       <c r="D25" s="32"/>
     </row>
     <row r="26" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="35" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C26" s="35"/>
       <c r="D26" s="81" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
     </row>
     <row r="27" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="115" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="D27" s="88">
         <f>-Assumptions!E43</f>
@@ -8683,7 +8659,7 @@
     </row>
     <row r="28" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="37" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="D28" s="120">
         <f>Financials!H27</f>
@@ -8692,7 +8668,7 @@
     </row>
     <row r="29" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="37" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D29" s="120">
         <f>Financials!I27</f>
@@ -8701,7 +8677,7 @@
     </row>
     <row r="30" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="37" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="D30" s="120">
         <f>Financials!J27</f>
@@ -8710,7 +8686,7 @@
     </row>
     <row r="31" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" s="37" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="D31" s="120">
         <f>Financials!K27</f>
@@ -8719,7 +8695,7 @@
     </row>
     <row r="32" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="115" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="D32" s="105">
         <f>Financials!L27</f>
@@ -8728,7 +8704,7 @@
     </row>
     <row r="33" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="37" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="D33" s="120">
         <f>Financials!M27+D22</f>
@@ -8737,14 +8713,14 @@
     </row>
     <row r="35" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="32" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="C35" s="32"/>
       <c r="D35" s="32"/>
     </row>
     <row r="36" spans="2:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="62" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C36" s="62"/>
       <c r="D36" s="121">
@@ -8754,7 +8730,7 @@
     </row>
     <row r="37" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="45" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="D37" s="122">
         <f>IFERROR(D22/Assumptions!E43,"")</f>
@@ -8763,19 +8739,19 @@
     </row>
     <row r="38" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="107" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
     </row>
     <row r="40" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="116" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C40" s="116"/>
       <c r="D40" s="1"/>
     </row>
     <row r="41" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="37" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="D41" s="94">
         <f>Assumptions!E43</f>
@@ -8784,7 +8760,7 @@
     </row>
     <row r="42" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="37" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="D42" s="86">
         <f>D22-D41</f>
@@ -8793,7 +8769,7 @@
     </row>
     <row r="43" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="37" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="D43" s="86">
         <f>Assumptions!E42-'Debt Schedule'!H19</f>
@@ -8802,7 +8778,7 @@
     </row>
     <row r="44" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="37" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D44" s="86">
         <f>D22</f>
@@ -8811,7 +8787,7 @@
     </row>
     <row r="45" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B45" s="37" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="D45" s="123">
         <f>IFERROR(D22/Assumptions!E43,"")</f>

--- a/assets/excel/lbo-model-vedant-fashion.xlsx
+++ b/assets/excel/lbo-model-vedant-fashion.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Anvay Document\ANVAY-PORTFOLIO-WEBSITE\assets\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF71E149-FFA9-4726-B99B-E896AACB3E9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACEFA7E0-58AF-425F-9B5F-957A3A74E9CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="674" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,8 @@
     <sheet name="Assumptions" sheetId="3" r:id="rId3"/>
     <sheet name="Financials" sheetId="4" r:id="rId4"/>
     <sheet name="Debt Schedule" sheetId="5" r:id="rId5"/>
-    <sheet name="LBO Returns" sheetId="6" r:id="rId6"/>
+    <sheet name="LBO Return" sheetId="6" r:id="rId6"/>
+    <sheet name="Sensitivity Analysis" sheetId="8" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="2">Assumptions!$A$1:$I$80</definedName>
@@ -1052,7 +1053,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="283">
   <si>
     <t>VEDANT FASHIONS LIMITED (MANYAVAR)</t>
   </si>
@@ -1912,12 +1913,214 @@
   <si>
     <t>6 Years (Exit: FY2031)</t>
   </si>
+  <si>
+    <t>VEDANT FASHIONS LBO — SENSITIVITY &amp; SCENARIO ANALYSIS</t>
+  </si>
+  <si>
+    <t>Exit Multiple</t>
+  </si>
+  <si>
+    <t>Revenue CAGR</t>
+  </si>
+  <si>
+    <t>MOIC SENSITIVITY TABLE (Exit Multiple × Revenue CAGR)</t>
+  </si>
+  <si>
+    <t>IRR SENSITIVITY TABLE (Exit Multiple × Revenue CAGR)</t>
+  </si>
+  <si>
+    <t>Thesis</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• Base case gives </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="10"/>
+        <color theme="1" tint="0.34998626667073579"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>~17% IRR and ~2.7x MOIC</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1" tint="0.34998626667073579"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, which is </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="10"/>
+        <color theme="1" tint="0.34998626667073579"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>okay but below PE target (20% IRR)</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1" tint="0.34998626667073579"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• To reach target returns, need </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="10"/>
+        <color theme="1" tint="0.34998626667073579"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>higher growth (12–14%) or higher exit multiple (24x+)</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1" tint="0.34998626667073579"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>• IRR depends more on exit multiple</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1" tint="0.34998626667073579"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, while </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="10"/>
+        <color theme="1" tint="0.34998626667073579"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>MOIC improves with business growth</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1" tint="0.34998626667073579"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• In downside cases, returns fall to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="10"/>
+        <color theme="1" tint="0.34998626667073579"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>~10–13% IRR and ~2x MOIC</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1" tint="0.34998626667073579"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>, so risk is there.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">• In upside cases, returns can go to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="10"/>
+        <color theme="1" tint="0.34998626667073579"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>20%+ IRR and 3x+ MOIC</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color theme="1" tint="0.34998626667073579"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>, making it a good outcome.</t>
+    </r>
+  </si>
+  <si>
+    <t>6. Sensitivity Analysis</t>
+  </si>
+  <si>
+    <t>Returns Sensitivity (IRR &amp; MOIC)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">SENSITIVITY INPUT CELLS </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <vertAlign val="subscript"/>
+        <sz val="10"/>
+        <color rgb="FFE8630A"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>(do not delete this input)</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <numFmts count="7">
+  <numFmts count="9">
     <numFmt numFmtId="164" formatCode="#,##0.00;\(#,##0.00\);\-"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="#,##0.0"/>
@@ -1925,8 +2128,10 @@
     <numFmt numFmtId="168" formatCode="0.00\x"/>
     <numFmt numFmtId="169" formatCode="\₹\ #,##0_);\(\₹\ #,##0\)"/>
     <numFmt numFmtId="170" formatCode="\₹\ #,##0.0;\(\₹\ #,##0.0\)"/>
+    <numFmt numFmtId="171" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="172" formatCode="0&quot;x&quot;"/>
   </numFmts>
-  <fonts count="42" x14ac:knownFonts="1">
+  <fonts count="53" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1944,19 +2149,6 @@
       <b/>
       <sz val="20"/>
       <color rgb="FFE8630A"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="10"/>
-      <color rgb="FFD9D9D9"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -2217,8 +2409,102 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFE8630A"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color rgb="FFE8630A"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13.5"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color theme="1" tint="0.34998626667073579"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="10"/>
+      <color theme="1" tint="0.34998626667073579"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1" tint="0.34998626667073579"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FFD9D9D9"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <vertAlign val="subscript"/>
+      <sz val="10"/>
+      <color rgb="FFE8630A"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="15">
+  <fills count="21">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2303,8 +2589,41 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A1A2E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8630A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="12">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -2435,13 +2754,43 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="127">
+  <cellXfs count="153">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyProtection="1">
       <protection locked="0"/>
@@ -2456,320 +2805,326 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="40" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="13" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="13" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="13" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="40" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="40" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="13" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="13" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="13" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="5" borderId="4" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="35" fillId="5" borderId="4" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="5" borderId="5" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="35" fillId="5" borderId="5" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="5" borderId="6" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="35" fillId="5" borderId="6" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="170" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="170" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="4" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="39" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="170" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="170" fontId="12" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="170" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="20" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="170" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="170" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="16" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="16" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="16" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="170" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="12" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="170" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="23" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="23" fillId="11" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="20" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="20" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="20" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="39" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyProtection="1"/>
+    <xf numFmtId="167" fontId="23" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyProtection="1"/>
+    <xf numFmtId="170" fontId="20" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="170" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="170" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="4" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="34" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="39" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="170" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="170" fontId="14" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="170" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="22" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="170" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="170" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="166" fontId="18" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="18" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="18" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="170" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="13" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="14" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="14" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="170" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="25" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="25" fillId="11" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="22" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="22" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyProtection="1"/>
-    <xf numFmtId="167" fontId="25" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyProtection="1"/>
-    <xf numFmtId="170" fontId="22" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -2777,71 +3132,154 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="170" fontId="34" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="170" fontId="36" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="167" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="3" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="31" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="18" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="34" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="20" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="167" fontId="20" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="36" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="1" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="33" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="20" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="36" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="45" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="45" fillId="19" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="45" fillId="17" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="42" fillId="15" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="44" fillId="18" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="41" fillId="17" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="172" fontId="41" fillId="17" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="172" fontId="43" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="171" fontId="45" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="45" fillId="19" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="45" fillId="17" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2921,6 +3359,7 @@
       <rgbColor rgb="00333333"/>
     </indexedColors>
     <mruColors>
+      <color rgb="FF0000FF"/>
       <color rgb="FF00FF00"/>
       <color rgb="FFF5F5F5"/>
       <color rgb="FFE8630A"/>
@@ -3172,12 +3611,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S32"/>
+  <sheetPr codeName="Sheet1"/>
+  <dimension ref="A1:S33"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="40" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="3" max="3" width="23.5546875" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="15.77734375" customWidth="1"/>
     <col min="6" max="19" width="12" customWidth="1"/>
@@ -3250,7 +3690,7 @@
     </row>
     <row r="4" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4"/>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="126" t="s">
         <v>1</v>
       </c>
       <c r="C4" s="4"/>
@@ -3273,7 +3713,7 @@
     </row>
     <row r="5" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4"/>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="127" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="4"/>
@@ -3337,188 +3777,196 @@
       <c r="S7" s="4"/>
     </row>
     <row r="8" spans="1:19" ht="3.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="8"/>
-      <c r="L8" s="8"/>
-      <c r="M8" s="8"/>
-      <c r="N8" s="8"/>
-      <c r="O8" s="8"/>
-      <c r="P8" s="8"/>
-      <c r="Q8" s="8"/>
-      <c r="R8" s="8"/>
-      <c r="S8" s="8"/>
+      <c r="A8" s="6"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="6"/>
+      <c r="M8" s="6"/>
+      <c r="N8" s="6"/>
+      <c r="O8" s="6"/>
+      <c r="P8" s="6"/>
+      <c r="Q8" s="6"/>
+      <c r="R8" s="6"/>
+      <c r="S8" s="6"/>
     </row>
     <row r="10" spans="1:19" ht="18" x14ac:dyDescent="0.35">
-      <c r="B10" s="125" t="s">
+      <c r="B10" s="124" t="s">
         <v>265</v>
       </c>
-      <c r="C10" s="125"/>
-      <c r="D10" s="125"/>
-      <c r="E10" s="125"/>
+      <c r="C10" s="124"/>
+      <c r="D10" s="124"/>
+      <c r="E10" s="124"/>
     </row>
     <row r="11" spans="1:19" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="12" spans="1:19" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="8" t="s">
         <v>264</v>
       </c>
-      <c r="D12" s="11"/>
-      <c r="E12" s="12"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="10"/>
     </row>
     <row r="13" spans="1:19" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="C13" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="D13" s="15"/>
-      <c r="E13" s="16"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="14"/>
     </row>
     <row r="14" spans="1:19" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="13" t="s">
+      <c r="B14" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="C14" s="14" t="s">
+      <c r="C14" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="D14" s="15"/>
-      <c r="E14" s="16"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="14"/>
     </row>
     <row r="15" spans="1:19" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="13" t="s">
+      <c r="B15" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="14" t="s">
+      <c r="C15" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="D15" s="15"/>
-      <c r="E15" s="16"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="14"/>
     </row>
     <row r="16" spans="1:19" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="13" t="s">
+      <c r="B16" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="14" t="s">
+      <c r="C16" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="D16" s="15"/>
-      <c r="E16" s="16"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="14"/>
     </row>
     <row r="17" spans="2:5" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="13" t="s">
+      <c r="B17" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C17" s="14" t="s">
+      <c r="C17" s="12" t="s">
         <v>268</v>
       </c>
-      <c r="D17" s="15"/>
-      <c r="E17" s="16"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="14"/>
     </row>
     <row r="18" spans="2:5" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="13" t="s">
+      <c r="B18" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C18" s="14" t="s">
+      <c r="C18" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="D18" s="15"/>
-      <c r="E18" s="16"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="14"/>
     </row>
     <row r="19" spans="2:5" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="13" t="s">
+      <c r="B19" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C19" s="14" t="s">
+      <c r="C19" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D19" s="15"/>
-      <c r="E19" s="16"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="14"/>
     </row>
     <row r="20" spans="2:5" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="17" t="s">
+      <c r="B20" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="C20" s="18" t="s">
+      <c r="C20" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="D20" s="19"/>
-      <c r="E20" s="20"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="18"/>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B22" s="21" t="s">
+      <c r="B22" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="21" t="s">
+      <c r="C22" s="19" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="23" spans="2:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="22" t="s">
+      <c r="B23" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="C23" s="23" t="s">
+      <c r="C23" s="21" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="24" spans="2:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="24" t="s">
+      <c r="B24" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="C24" s="25" t="s">
+      <c r="C24" s="23" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="25" spans="2:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="24" t="s">
+      <c r="B25" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="C25" s="25" t="s">
+      <c r="C25" s="23" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="26" spans="2:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="24" t="s">
+      <c r="B26" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="C26" s="25" t="s">
+      <c r="C26" s="23" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="27" spans="2:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="26" t="s">
+      <c r="B27" s="22" t="s">
         <v>31</v>
       </c>
-      <c r="C27" s="27" t="s">
+      <c r="C27" s="23" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="28" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="29" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="28" t="s">
+    <row r="28" spans="2:5" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="24" t="s">
+        <v>281</v>
+      </c>
+      <c r="C28" s="25" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="30" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B30" s="26" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="30" spans="2:5" ht="24" x14ac:dyDescent="0.3">
-      <c r="B30" s="29" t="s">
+    <row r="31" spans="2:5" ht="24" x14ac:dyDescent="0.3">
+      <c r="B31" s="27" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="31" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="32" spans="2:5" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="33" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="1lczmibRGI09RS4LcM7ikzIniToVvasltVAM9pQwPRNi/ODYuXfGdaf0fDuVwEflAsf5ssW+mz0SpGoWEOtfEQ==" saltValue="ysGRQ/v3n2V6yjjThTz4kQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="vYUxXQlxE+hwMUBqL/ItDUxE8wV9uFF/R9Qq0iCKGm/pPLLnIAsF4XL28uoA6YBDGjzzskngMxQiqEoc11WgiQ==" saltValue="pcoxC5PGKDcFNbOy29pcZQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="B10:E10"/>
   </mergeCells>
@@ -3528,18 +3976,19 @@
     <hyperlink ref="C25" location="'3. Debt Schedule'!A1" display="3. Debt Schedule" xr:uid="{1D3D559D-A79A-4495-A3A4-0372D72BEA4A}"/>
     <hyperlink ref="C26" location="'4. LBO Returns'!A1" display="4. LBO Returns" xr:uid="{7D3C603F-7B1A-437F-8B38-F4C0F3BD1846}"/>
     <hyperlink ref="C27" location="'Data Sheet'!A1" display="5. Data Sheet" xr:uid="{C480F2E6-07A9-4441-90B7-778B0C8F7C2E}"/>
+    <hyperlink ref="C28" location="'Sensitivity Analysis'!A1" display="6. Sensitivity Analysis" xr:uid="{6290EE14-74CB-44E1-8F7B-8733DD624167}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="83" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <rowBreaks count="1" manualBreakCount="1">
-    <brk id="27" max="5" man="1"/>
+    <brk id="28" max="5" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <sheetPr>
+  <sheetPr codeName="Sheet2">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B2:W71"/>
@@ -3554,21 +4003,21 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12" x14ac:dyDescent="0.3">
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30"/>
-      <c r="J2" s="30"/>
-      <c r="K2" s="30"/>
-      <c r="L2" s="30"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="28"/>
+      <c r="K2" s="28"/>
+      <c r="L2" s="28"/>
     </row>
     <row r="3" spans="2:12" ht="8.4" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="2:12" ht="18" x14ac:dyDescent="0.35">
-      <c r="B4" s="31" t="s">
+      <c r="B4" s="29" t="s">
         <v>255</v>
       </c>
     </row>
@@ -3579,2101 +4028,2101 @@
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.3"/>
     <row r="7" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="30"/>
-      <c r="C7" s="30"/>
-      <c r="D7" s="30"/>
-      <c r="E7" s="30"/>
-      <c r="F7" s="30"/>
-      <c r="G7" s="30"/>
-      <c r="H7" s="30"/>
-      <c r="I7" s="30"/>
-      <c r="J7" s="30"/>
-      <c r="K7" s="30"/>
-      <c r="L7" s="30"/>
-    </row>
-    <row r="9" spans="2:12" s="34" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="32" t="s">
+      <c r="B7" s="28"/>
+      <c r="C7" s="28"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="28"/>
+      <c r="H7" s="28"/>
+      <c r="I7" s="28"/>
+      <c r="J7" s="28"/>
+      <c r="K7" s="28"/>
+      <c r="L7" s="28"/>
+    </row>
+    <row r="9" spans="2:12" s="32" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="33"/>
-      <c r="D9" s="33"/>
-      <c r="E9" s="33"/>
-      <c r="F9" s="33"/>
-      <c r="G9" s="33"/>
-      <c r="H9" s="33"/>
-      <c r="I9" s="33"/>
-      <c r="J9" s="33"/>
-      <c r="K9" s="33"/>
-      <c r="L9" s="33"/>
+      <c r="C9" s="31"/>
+      <c r="D9" s="31"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="31"/>
+      <c r="G9" s="31"/>
+      <c r="H9" s="31"/>
+      <c r="I9" s="31"/>
+      <c r="J9" s="31"/>
+      <c r="K9" s="31"/>
+      <c r="L9" s="31"/>
     </row>
     <row r="10" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="35" t="s">
+      <c r="B10" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="C10" s="36" t="s">
+      <c r="C10" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="D10" s="36" t="s">
+      <c r="D10" s="34" t="s">
         <v>35</v>
       </c>
-      <c r="E10" s="36" t="s">
+      <c r="E10" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="F10" s="36" t="s">
+      <c r="F10" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="G10" s="36" t="s">
+      <c r="G10" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="H10" s="36" t="s">
+      <c r="H10" s="34" t="s">
         <v>39</v>
       </c>
-      <c r="I10" s="36" t="s">
+      <c r="I10" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="J10" s="36" t="s">
+      <c r="J10" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="K10" s="36" t="s">
+      <c r="K10" s="34" t="s">
         <v>42</v>
       </c>
-      <c r="L10" s="36" t="s">
+      <c r="L10" s="34" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="11" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="37" t="s">
+      <c r="B11" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="C11" s="38">
+      <c r="C11" s="36">
         <v>1.19</v>
       </c>
-      <c r="D11" s="38">
+      <c r="D11" s="36">
         <v>1.19</v>
       </c>
-      <c r="E11" s="38">
+      <c r="E11" s="36">
         <v>12.51</v>
       </c>
-      <c r="F11" s="38">
+      <c r="F11" s="36">
         <v>12.52</v>
       </c>
-      <c r="G11" s="38">
+      <c r="G11" s="36">
         <v>12.52</v>
       </c>
-      <c r="H11" s="38">
+      <c r="H11" s="36">
         <v>12.39</v>
       </c>
-      <c r="I11" s="38">
+      <c r="I11" s="36">
         <v>24.27</v>
       </c>
-      <c r="J11" s="38">
+      <c r="J11" s="36">
         <v>24.28</v>
       </c>
-      <c r="K11" s="38">
+      <c r="K11" s="36">
         <v>24.29</v>
       </c>
-      <c r="L11" s="38">
+      <c r="L11" s="36">
         <v>24.29</v>
       </c>
     </row>
     <row r="12" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="37" t="s">
+      <c r="B12" s="35" t="s">
         <v>45</v>
       </c>
-      <c r="C12" s="38">
+      <c r="C12" s="36">
         <v>10</v>
       </c>
-      <c r="D12" s="38">
+      <c r="D12" s="36">
         <v>10</v>
       </c>
-      <c r="E12" s="38">
+      <c r="E12" s="36">
         <v>2</v>
       </c>
-      <c r="F12" s="38">
+      <c r="F12" s="36">
         <v>2</v>
       </c>
-      <c r="G12" s="38">
+      <c r="G12" s="36">
         <v>2</v>
       </c>
-      <c r="H12" s="38">
+      <c r="H12" s="36">
         <v>2</v>
       </c>
-      <c r="I12" s="38">
+      <c r="I12" s="36">
         <v>1</v>
       </c>
-      <c r="J12" s="38">
+      <c r="J12" s="36">
         <v>1</v>
       </c>
-      <c r="K12" s="38">
+      <c r="K12" s="36">
         <v>1</v>
       </c>
-      <c r="L12" s="38">
+      <c r="L12" s="36">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="37" t="s">
+      <c r="B13" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="C13" s="39" t="s">
+      <c r="C13" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="D13" s="39" t="s">
+      <c r="D13" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="E13" s="39" t="s">
+      <c r="E13" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="F13" s="39" t="s">
+      <c r="F13" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="G13" s="39" t="s">
+      <c r="G13" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="H13" s="39" t="s">
+      <c r="H13" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="I13" s="38">
+      <c r="I13" s="36">
         <v>966.95</v>
       </c>
-      <c r="J13" s="38">
+      <c r="J13" s="36">
         <v>1139.1500000000001</v>
       </c>
-      <c r="K13" s="38">
+      <c r="K13" s="36">
         <v>926.5</v>
       </c>
-      <c r="L13" s="38">
+      <c r="L13" s="36">
         <v>775.85</v>
       </c>
     </row>
     <row r="14" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="37" t="s">
+      <c r="B14" s="35" t="s">
         <v>48</v>
       </c>
-      <c r="C14" s="39" t="s">
+      <c r="C14" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="D14" s="39" t="s">
+      <c r="D14" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="E14" s="39" t="s">
+      <c r="E14" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="F14" s="39" t="s">
+      <c r="F14" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="G14" s="39" t="s">
+      <c r="G14" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="H14" s="39" t="s">
+      <c r="H14" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="I14" s="39" t="s">
+      <c r="I14" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="J14" s="39" t="s">
+      <c r="J14" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="K14" s="39" t="s">
+      <c r="K14" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="L14" s="38">
+      <c r="L14" s="36">
         <v>8506.49</v>
       </c>
     </row>
     <row r="15" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="37" t="s">
+      <c r="B15" s="35" t="s">
         <v>49</v>
       </c>
-      <c r="D15" s="40"/>
-      <c r="E15" s="40"/>
-      <c r="F15" s="40"/>
-      <c r="G15" s="40"/>
-      <c r="H15" s="40"/>
-      <c r="I15" s="40"/>
-      <c r="J15" s="40"/>
-      <c r="K15" s="40"/>
-      <c r="L15" s="38">
+      <c r="D15" s="38"/>
+      <c r="E15" s="38"/>
+      <c r="F15" s="38"/>
+      <c r="G15" s="38"/>
+      <c r="H15" s="38"/>
+      <c r="I15" s="38"/>
+      <c r="J15" s="38"/>
+      <c r="K15" s="38"/>
+      <c r="L15" s="36">
         <v>350.1</v>
       </c>
     </row>
-    <row r="17" spans="2:23" s="34" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="32" t="s">
+    <row r="17" spans="2:23" s="32" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="30" t="s">
         <v>257</v>
       </c>
-      <c r="C17" s="33"/>
-      <c r="D17" s="33"/>
-      <c r="E17" s="33"/>
-      <c r="F17" s="33"/>
-      <c r="G17" s="33"/>
-      <c r="H17" s="33"/>
-      <c r="I17" s="33"/>
-      <c r="J17" s="33"/>
-      <c r="K17" s="33"/>
-      <c r="L17" s="33"/>
+      <c r="C17" s="31"/>
+      <c r="D17" s="31"/>
+      <c r="E17" s="31"/>
+      <c r="F17" s="31"/>
+      <c r="G17" s="31"/>
+      <c r="H17" s="31"/>
+      <c r="I17" s="31"/>
+      <c r="J17" s="31"/>
+      <c r="K17" s="31"/>
+      <c r="L17" s="31"/>
     </row>
     <row r="18" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="35" t="s">
+      <c r="B18" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="C18" s="36" t="s">
+      <c r="C18" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="D18" s="36" t="s">
+      <c r="D18" s="34" t="s">
         <v>35</v>
       </c>
-      <c r="E18" s="36" t="s">
+      <c r="E18" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="F18" s="36" t="s">
+      <c r="F18" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="G18" s="36" t="s">
+      <c r="G18" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="H18" s="36" t="s">
+      <c r="H18" s="34" t="s">
         <v>39</v>
       </c>
-      <c r="I18" s="36" t="s">
+      <c r="I18" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="J18" s="36" t="s">
+      <c r="J18" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="K18" s="36" t="s">
+      <c r="K18" s="34" t="s">
         <v>42</v>
       </c>
-      <c r="L18" s="36" t="s">
+      <c r="L18" s="34" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="19" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="37" t="s">
+      <c r="B19" s="35" t="s">
         <v>50</v>
       </c>
-      <c r="C19" s="38">
+      <c r="C19" s="36">
         <v>504.28</v>
       </c>
-      <c r="D19" s="38">
+      <c r="D19" s="36">
         <v>596.37</v>
       </c>
-      <c r="E19" s="38">
+      <c r="E19" s="36">
         <v>759.73</v>
       </c>
-      <c r="F19" s="38">
+      <c r="F19" s="36">
         <v>794.15</v>
       </c>
-      <c r="G19" s="38">
+      <c r="G19" s="36">
         <v>915.17</v>
       </c>
-      <c r="H19" s="38">
+      <c r="H19" s="36">
         <v>542.41</v>
       </c>
-      <c r="I19" s="38">
+      <c r="I19" s="36">
         <v>1008.75</v>
       </c>
-      <c r="J19" s="38">
+      <c r="J19" s="36">
         <v>1325.96</v>
       </c>
-      <c r="K19" s="38">
+      <c r="K19" s="36">
         <v>1367.53</v>
       </c>
-      <c r="L19" s="38">
+      <c r="L19" s="36">
         <v>1386.48</v>
       </c>
     </row>
     <row r="20" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="37" t="s">
+      <c r="B20" s="35" t="s">
         <v>51</v>
       </c>
-      <c r="C20" s="38">
+      <c r="C20" s="36">
         <v>107.72</v>
       </c>
-      <c r="D20" s="38">
+      <c r="D20" s="36">
         <v>144.15</v>
       </c>
-      <c r="E20" s="38">
+      <c r="E20" s="36">
         <v>242.85</v>
       </c>
-      <c r="F20" s="38">
+      <c r="F20" s="36">
         <v>222.97</v>
       </c>
-      <c r="G20" s="38">
+      <c r="G20" s="36">
         <v>261.10000000000002</v>
       </c>
-      <c r="H20" s="38">
+      <c r="H20" s="36">
         <v>126.25</v>
       </c>
-      <c r="I20" s="38">
+      <c r="I20" s="36">
         <v>285.85000000000002</v>
       </c>
-      <c r="J20" s="38">
+      <c r="J20" s="36">
         <v>371.74</v>
       </c>
-      <c r="K20" s="38">
+      <c r="K20" s="36">
         <v>334.92</v>
       </c>
-      <c r="L20" s="38">
+      <c r="L20" s="36">
         <v>413.73</v>
       </c>
-      <c r="N20" s="41"/>
+      <c r="N20" s="39"/>
     </row>
     <row r="21" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="37" t="s">
+      <c r="B21" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="C21" s="42"/>
-      <c r="D21" s="38">
+      <c r="C21" s="40"/>
+      <c r="D21" s="36">
         <v>10.5</v>
       </c>
-      <c r="E21" s="38">
+      <c r="E21" s="36">
         <v>-1.92</v>
       </c>
-      <c r="F21" s="38">
+      <c r="F21" s="36">
         <v>0.65</v>
       </c>
-      <c r="G21" s="38">
+      <c r="G21" s="36">
         <v>19.63</v>
       </c>
-      <c r="H21" s="38">
+      <c r="H21" s="36">
         <v>-5.92</v>
       </c>
-      <c r="I21" s="38">
+      <c r="I21" s="36">
         <v>36.89</v>
       </c>
-      <c r="J21" s="38">
+      <c r="J21" s="36">
         <v>40.35</v>
       </c>
-      <c r="K21" s="38">
+      <c r="K21" s="36">
         <v>-28.6</v>
       </c>
-      <c r="L21" s="38">
+      <c r="L21" s="36">
         <v>62.39</v>
       </c>
     </row>
     <row r="22" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="37" t="s">
+      <c r="B22" s="35" t="s">
         <v>53</v>
       </c>
-      <c r="C22" s="42"/>
-      <c r="D22" s="38">
+      <c r="C22" s="40"/>
+      <c r="D22" s="36">
         <v>84.38</v>
       </c>
-      <c r="E22" s="38">
+      <c r="E22" s="36">
         <v>48.03</v>
       </c>
-      <c r="F22" s="38">
+      <c r="F22" s="36">
         <v>46.11</v>
       </c>
-      <c r="G22" s="38">
+      <c r="G22" s="36">
         <v>50.79</v>
       </c>
-      <c r="H22" s="38">
+      <c r="H22" s="36">
         <v>36.590000000000003</v>
       </c>
-      <c r="I22" s="38">
+      <c r="I22" s="36">
         <v>56.64</v>
       </c>
-      <c r="J22" s="38">
+      <c r="J22" s="36">
         <v>56.38</v>
       </c>
-      <c r="K22" s="38">
+      <c r="K22" s="36">
         <v>57.98</v>
       </c>
-      <c r="L22" s="38">
+      <c r="L22" s="36">
         <v>61</v>
       </c>
     </row>
     <row r="23" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="37" t="s">
+      <c r="B23" s="35" t="s">
         <v>54</v>
       </c>
-      <c r="C23" s="42"/>
-      <c r="D23" s="38">
+      <c r="C23" s="40"/>
+      <c r="D23" s="36">
         <v>134.04</v>
       </c>
-      <c r="E23" s="38">
+      <c r="E23" s="36">
         <v>76.290000000000006</v>
       </c>
-      <c r="F23" s="38">
+      <c r="F23" s="36">
         <v>163.04</v>
       </c>
-      <c r="G23" s="38">
+      <c r="G23" s="36">
         <v>126.7</v>
       </c>
-      <c r="H23" s="38">
+      <c r="H23" s="36">
         <v>70.33</v>
       </c>
-      <c r="I23" s="38">
+      <c r="I23" s="36">
         <v>107.8</v>
       </c>
-      <c r="J23" s="38">
+      <c r="J23" s="36">
         <v>145.37</v>
       </c>
-      <c r="K23" s="38">
+      <c r="K23" s="36">
         <v>171.94</v>
       </c>
-      <c r="L23" s="38">
+      <c r="L23" s="36">
         <v>192.96</v>
       </c>
-      <c r="O23" s="43"/>
+      <c r="O23" s="41"/>
     </row>
     <row r="24" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="37" t="s">
+      <c r="B24" s="35" t="s">
         <v>55</v>
       </c>
-      <c r="C24" s="42"/>
-      <c r="D24" s="38">
+      <c r="C24" s="40"/>
+      <c r="D24" s="36">
         <v>0.02</v>
       </c>
-      <c r="E24" s="38">
+      <c r="E24" s="36">
         <v>0.01</v>
       </c>
-      <c r="F24" s="42"/>
-      <c r="G24" s="38">
+      <c r="F24" s="40"/>
+      <c r="G24" s="36">
         <v>80.92</v>
       </c>
-      <c r="H24" s="38">
+      <c r="H24" s="36">
         <v>51.79</v>
       </c>
-      <c r="I24" s="38">
+      <c r="I24" s="36">
         <v>96.15</v>
       </c>
-      <c r="J24" s="38">
+      <c r="J24" s="36">
         <v>109.77</v>
       </c>
-      <c r="K24" s="38">
+      <c r="K24" s="36">
         <v>85.84</v>
       </c>
-      <c r="L24" s="38">
+      <c r="L24" s="36">
         <v>104.06</v>
       </c>
-      <c r="N24" s="44"/>
-      <c r="O24" s="44"/>
-      <c r="P24" s="44"/>
-      <c r="Q24" s="44"/>
-      <c r="R24" s="44"/>
-      <c r="S24" s="44"/>
-      <c r="T24" s="44"/>
-      <c r="U24" s="44"/>
-      <c r="V24" s="44"/>
-      <c r="W24" s="44"/>
+      <c r="N24" s="42"/>
+      <c r="O24" s="42"/>
+      <c r="P24" s="42"/>
+      <c r="Q24" s="42"/>
+      <c r="R24" s="42"/>
+      <c r="S24" s="42"/>
+      <c r="T24" s="42"/>
+      <c r="U24" s="42"/>
+      <c r="V24" s="42"/>
+      <c r="W24" s="42"/>
     </row>
     <row r="25" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="37" t="s">
+      <c r="B25" s="35" t="s">
         <v>56</v>
       </c>
-      <c r="C25" s="38">
+      <c r="C25" s="36">
         <v>246.07</v>
       </c>
-      <c r="D25" s="38">
+      <c r="D25" s="36">
         <v>65.459999999999994</v>
       </c>
-      <c r="E25" s="38">
+      <c r="E25" s="36">
         <v>154.86000000000001</v>
       </c>
-      <c r="F25" s="38">
+      <c r="F25" s="36">
         <v>88.06</v>
       </c>
-      <c r="G25" s="38">
+      <c r="G25" s="36">
         <v>16.3</v>
       </c>
-      <c r="H25" s="38">
+      <c r="H25" s="36">
         <v>15.81</v>
       </c>
-      <c r="I25" s="38">
+      <c r="I25" s="36">
         <v>18.059999999999999</v>
       </c>
-      <c r="J25" s="38">
+      <c r="J25" s="36">
         <v>24.21</v>
       </c>
-      <c r="K25" s="38">
+      <c r="K25" s="36">
         <v>28.84</v>
       </c>
-      <c r="L25" s="38">
+      <c r="L25" s="36">
         <v>33.119999999999997</v>
       </c>
-      <c r="N25" s="44"/>
-      <c r="O25" s="44"/>
-      <c r="P25" s="44"/>
-      <c r="Q25" s="44"/>
-      <c r="R25" s="44"/>
-      <c r="S25" s="44"/>
-      <c r="T25" s="44"/>
-      <c r="U25" s="44"/>
-      <c r="V25" s="44"/>
-      <c r="W25" s="44"/>
+      <c r="N25" s="42"/>
+      <c r="O25" s="42"/>
+      <c r="P25" s="42"/>
+      <c r="Q25" s="42"/>
+      <c r="R25" s="42"/>
+      <c r="S25" s="42"/>
+      <c r="T25" s="42"/>
+      <c r="U25" s="42"/>
+      <c r="V25" s="42"/>
+      <c r="W25" s="42"/>
     </row>
     <row r="26" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="45" t="s">
+      <c r="B26" s="43" t="s">
         <v>57</v>
       </c>
-      <c r="C26" s="53">
+      <c r="C26" s="51">
         <f>IFERROR(C20+C21+C22+C23+C24+C25,"")</f>
         <v>353.78999999999996</v>
       </c>
-      <c r="D26" s="53">
+      <c r="D26" s="51">
         <f t="shared" ref="D26:K26" si="0">IFERROR(D20+D21+D22+D23+D24+D25,"")</f>
         <v>438.54999999999995</v>
       </c>
-      <c r="E26" s="53">
+      <c r="E26" s="51">
         <f t="shared" si="0"/>
         <v>520.12000000000012</v>
       </c>
-      <c r="F26" s="53">
+      <c r="F26" s="51">
         <f t="shared" si="0"/>
         <v>520.82999999999993</v>
       </c>
-      <c r="G26" s="53">
+      <c r="G26" s="51">
         <f t="shared" si="0"/>
         <v>555.43999999999994</v>
       </c>
-      <c r="H26" s="53">
+      <c r="H26" s="51">
         <f t="shared" si="0"/>
         <v>294.85000000000002</v>
       </c>
-      <c r="I26" s="53">
+      <c r="I26" s="51">
         <f>IFERROR(I20+I21+I22+I23+I24+I25,"")</f>
         <v>601.39</v>
       </c>
-      <c r="J26" s="53">
+      <c r="J26" s="51">
         <f t="shared" si="0"/>
         <v>747.82</v>
       </c>
-      <c r="K26" s="53">
+      <c r="K26" s="51">
         <f t="shared" si="0"/>
         <v>650.92000000000007</v>
       </c>
-      <c r="L26" s="53">
+      <c r="L26" s="51">
         <f>IFERROR(L20+L21+L22+L23+L24+L25,"")</f>
         <v>867.2600000000001</v>
       </c>
-      <c r="N26" s="44"/>
-      <c r="O26" s="44"/>
-      <c r="P26" s="44"/>
-      <c r="Q26" s="44"/>
-      <c r="R26" s="44"/>
-      <c r="S26" s="44"/>
-      <c r="T26" s="44"/>
-      <c r="U26" s="44"/>
-      <c r="V26" s="44"/>
-      <c r="W26" s="44"/>
+      <c r="N26" s="42"/>
+      <c r="O26" s="42"/>
+      <c r="P26" s="42"/>
+      <c r="Q26" s="42"/>
+      <c r="R26" s="42"/>
+      <c r="S26" s="42"/>
+      <c r="T26" s="42"/>
+      <c r="U26" s="42"/>
+      <c r="V26" s="42"/>
+      <c r="W26" s="42"/>
     </row>
     <row r="27" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="45" t="s">
+      <c r="B27" s="43" t="s">
         <v>58</v>
       </c>
-      <c r="C27" s="53">
+      <c r="C27" s="51">
         <f>C31+C30+C29-C28</f>
         <v>150.49</v>
       </c>
-      <c r="D27" s="53">
+      <c r="D27" s="51">
         <f t="shared" ref="D27:K27" si="1">D31+D30+D29-D28</f>
         <v>173.01999999999998</v>
       </c>
-      <c r="E27" s="53">
+      <c r="E27" s="51">
         <f t="shared" si="1"/>
         <v>233.68</v>
       </c>
-      <c r="F27" s="53">
+      <c r="F27" s="51">
         <f>F31+F30+F29-F28</f>
         <v>273.59000000000003</v>
       </c>
-      <c r="G27" s="53">
+      <c r="G27" s="51">
         <f t="shared" si="1"/>
         <v>398.12</v>
       </c>
-      <c r="H27" s="53">
+      <c r="H27" s="51">
         <f t="shared" si="1"/>
         <v>235.03999999999996</v>
       </c>
-      <c r="I27" s="53">
+      <c r="I27" s="51">
         <f>I31+I30+I29-I28</f>
         <v>480.34000000000003</v>
       </c>
-      <c r="J27" s="53">
+      <c r="J27" s="51">
         <f t="shared" si="1"/>
         <v>657.80000000000007</v>
       </c>
-      <c r="K27" s="53">
+      <c r="K27" s="51">
         <f t="shared" si="1"/>
         <v>658.09</v>
       </c>
-      <c r="L27" s="53">
+      <c r="L27" s="51">
         <f>L31+L30+L29-L28</f>
         <v>642.61</v>
       </c>
-      <c r="N27" s="44"/>
-      <c r="O27" s="44"/>
-      <c r="P27" s="44"/>
-      <c r="Q27" s="44"/>
-      <c r="R27" s="44"/>
-      <c r="S27" s="44"/>
-      <c r="T27" s="44"/>
-      <c r="U27" s="44"/>
-      <c r="V27" s="44"/>
-      <c r="W27" s="44"/>
+      <c r="N27" s="42"/>
+      <c r="O27" s="42"/>
+      <c r="P27" s="42"/>
+      <c r="Q27" s="42"/>
+      <c r="R27" s="42"/>
+      <c r="S27" s="42"/>
+      <c r="T27" s="42"/>
+      <c r="U27" s="42"/>
+      <c r="V27" s="42"/>
+      <c r="W27" s="42"/>
     </row>
     <row r="28" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="37" t="s">
+      <c r="B28" s="35" t="s">
         <v>59</v>
       </c>
-      <c r="C28" s="38">
+      <c r="C28" s="36">
         <v>1.84</v>
       </c>
-      <c r="D28" s="38">
+      <c r="D28" s="36">
         <v>3.4</v>
       </c>
-      <c r="E28" s="38">
+      <c r="E28" s="36">
         <v>10.48</v>
       </c>
-      <c r="F28" s="38">
+      <c r="F28" s="36">
         <v>19.09</v>
       </c>
-      <c r="G28" s="38">
+      <c r="G28" s="36">
         <v>31.95</v>
       </c>
-      <c r="H28" s="38">
+      <c r="H28" s="36">
         <v>57.56</v>
       </c>
-      <c r="I28" s="38">
+      <c r="I28" s="36">
         <v>48.53</v>
       </c>
-      <c r="J28" s="38">
+      <c r="J28" s="36">
         <v>37.04</v>
       </c>
-      <c r="K28" s="38">
+      <c r="K28" s="36">
         <v>69.67</v>
       </c>
-      <c r="L28" s="38">
+      <c r="L28" s="36">
         <v>85.16</v>
       </c>
-      <c r="N28" s="44"/>
-      <c r="O28" s="44"/>
-      <c r="P28" s="44"/>
-      <c r="Q28" s="44"/>
-      <c r="R28" s="44"/>
-      <c r="S28" s="44"/>
-      <c r="T28" s="44"/>
-      <c r="U28" s="44"/>
-      <c r="V28" s="44"/>
-      <c r="W28" s="44"/>
+      <c r="N28" s="42"/>
+      <c r="O28" s="42"/>
+      <c r="P28" s="42"/>
+      <c r="Q28" s="42"/>
+      <c r="R28" s="42"/>
+      <c r="S28" s="42"/>
+      <c r="T28" s="42"/>
+      <c r="U28" s="42"/>
+      <c r="V28" s="42"/>
+      <c r="W28" s="42"/>
     </row>
     <row r="29" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="37" t="s">
+      <c r="B29" s="35" t="s">
         <v>60</v>
       </c>
-      <c r="C29" s="38">
+      <c r="C29" s="36">
         <v>7.33</v>
       </c>
-      <c r="D29" s="38">
+      <c r="D29" s="36">
         <v>7.57</v>
       </c>
-      <c r="E29" s="38">
+      <c r="E29" s="36">
         <v>9.59</v>
       </c>
-      <c r="F29" s="38">
+      <c r="F29" s="36">
         <v>8.4600000000000009</v>
       </c>
-      <c r="G29" s="38">
+      <c r="G29" s="36">
         <v>82.46</v>
       </c>
-      <c r="H29" s="38">
+      <c r="H29" s="36">
         <v>89.05</v>
       </c>
-      <c r="I29" s="38">
+      <c r="I29" s="36">
         <v>88.03</v>
       </c>
-      <c r="J29" s="38">
+      <c r="J29" s="36">
         <v>97.46</v>
       </c>
-      <c r="K29" s="38">
+      <c r="K29" s="36">
         <v>134.85</v>
       </c>
-      <c r="L29" s="38">
+      <c r="L29" s="36">
         <v>153.06</v>
       </c>
-      <c r="N29" s="44"/>
-      <c r="O29" s="44"/>
-      <c r="P29" s="44"/>
-      <c r="Q29" s="44"/>
-      <c r="R29" s="44"/>
-      <c r="S29" s="44"/>
-      <c r="T29" s="44"/>
-      <c r="U29" s="44"/>
-      <c r="V29" s="44"/>
-      <c r="W29" s="44"/>
+      <c r="N29" s="42"/>
+      <c r="O29" s="42"/>
+      <c r="P29" s="42"/>
+      <c r="Q29" s="42"/>
+      <c r="R29" s="42"/>
+      <c r="S29" s="42"/>
+      <c r="T29" s="42"/>
+      <c r="U29" s="42"/>
+      <c r="V29" s="42"/>
+      <c r="W29" s="42"/>
     </row>
     <row r="30" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="37" t="s">
+      <c r="B30" s="35" t="s">
         <v>61</v>
       </c>
-      <c r="C30" s="38">
+      <c r="C30" s="36">
         <v>5.97</v>
       </c>
-      <c r="D30" s="38">
+      <c r="D30" s="36">
         <v>5.0599999999999996</v>
       </c>
-      <c r="E30" s="38">
+      <c r="E30" s="36">
         <v>6.04</v>
       </c>
-      <c r="F30" s="38">
+      <c r="F30" s="36">
         <v>4.3499999999999996</v>
       </c>
-      <c r="G30" s="38">
+      <c r="G30" s="36">
         <v>24.8</v>
       </c>
-      <c r="H30" s="38">
+      <c r="H30" s="36">
         <v>25.07</v>
       </c>
-      <c r="I30" s="38">
+      <c r="I30" s="36">
         <v>27.07</v>
       </c>
-      <c r="J30" s="38">
+      <c r="J30" s="36">
         <v>30.35</v>
       </c>
-      <c r="K30" s="38">
+      <c r="K30" s="36">
         <v>44.5</v>
       </c>
-      <c r="L30" s="38">
+      <c r="L30" s="36">
         <v>55.21</v>
       </c>
-      <c r="N30" s="44"/>
-      <c r="O30" s="44"/>
-      <c r="P30" s="44"/>
-      <c r="Q30" s="44"/>
-      <c r="R30" s="44"/>
-      <c r="S30" s="44"/>
-      <c r="T30" s="44"/>
-      <c r="U30" s="44"/>
-      <c r="V30" s="44"/>
-      <c r="W30" s="44"/>
+      <c r="N30" s="42"/>
+      <c r="O30" s="42"/>
+      <c r="P30" s="42"/>
+      <c r="Q30" s="42"/>
+      <c r="R30" s="42"/>
+      <c r="S30" s="42"/>
+      <c r="T30" s="42"/>
+      <c r="U30" s="42"/>
+      <c r="V30" s="42"/>
+      <c r="W30" s="42"/>
     </row>
     <row r="31" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="37" t="s">
+      <c r="B31" s="35" t="s">
         <v>62</v>
       </c>
-      <c r="C31" s="38">
+      <c r="C31" s="36">
         <v>139.03</v>
       </c>
-      <c r="D31" s="38">
+      <c r="D31" s="36">
         <v>163.79</v>
       </c>
-      <c r="E31" s="38">
+      <c r="E31" s="36">
         <v>228.53</v>
       </c>
-      <c r="F31" s="38">
+      <c r="F31" s="36">
         <v>279.87</v>
       </c>
-      <c r="G31" s="38">
+      <c r="G31" s="36">
         <v>322.81</v>
       </c>
-      <c r="H31" s="38">
+      <c r="H31" s="36">
         <v>178.48</v>
       </c>
-      <c r="I31" s="38">
+      <c r="I31" s="36">
         <v>413.77</v>
       </c>
-      <c r="J31" s="38">
+      <c r="J31" s="36">
         <v>567.03</v>
       </c>
-      <c r="K31" s="38">
+      <c r="K31" s="36">
         <v>548.41</v>
       </c>
-      <c r="L31" s="38">
+      <c r="L31" s="36">
         <v>519.5</v>
       </c>
-      <c r="N31" s="44"/>
-      <c r="O31" s="44"/>
-      <c r="P31" s="44"/>
-      <c r="Q31" s="44"/>
-      <c r="R31" s="44"/>
-      <c r="S31" s="44"/>
-      <c r="T31" s="44"/>
-      <c r="U31" s="44"/>
-      <c r="V31" s="44"/>
-      <c r="W31" s="44"/>
+      <c r="N31" s="42"/>
+      <c r="O31" s="42"/>
+      <c r="P31" s="42"/>
+      <c r="Q31" s="42"/>
+      <c r="R31" s="42"/>
+      <c r="S31" s="42"/>
+      <c r="T31" s="42"/>
+      <c r="U31" s="42"/>
+      <c r="V31" s="42"/>
+      <c r="W31" s="42"/>
     </row>
     <row r="32" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="37" t="s">
+      <c r="B32" s="35" t="s">
         <v>63</v>
       </c>
-      <c r="C32" s="38">
+      <c r="C32" s="36">
         <v>48.87</v>
       </c>
-      <c r="D32" s="38">
+      <c r="D32" s="36">
         <v>57.75</v>
       </c>
-      <c r="E32" s="38">
+      <c r="E32" s="36">
         <v>79.11</v>
       </c>
-      <c r="F32" s="38">
+      <c r="F32" s="36">
         <v>97.59</v>
       </c>
-      <c r="G32" s="38">
+      <c r="G32" s="36">
         <v>77.680000000000007</v>
       </c>
-      <c r="H32" s="38">
+      <c r="H32" s="36">
         <v>47.74</v>
       </c>
-      <c r="I32" s="38">
+      <c r="I32" s="36">
         <v>105.41</v>
       </c>
-      <c r="J32" s="38">
+      <c r="J32" s="36">
         <v>144.13999999999999</v>
       </c>
-      <c r="K32" s="38">
+      <c r="K32" s="36">
         <v>134.22999999999999</v>
       </c>
-      <c r="L32" s="38">
+      <c r="L32" s="36">
         <v>131.03</v>
       </c>
-      <c r="N32" s="44"/>
-      <c r="O32" s="44"/>
-      <c r="P32" s="44"/>
-      <c r="Q32" s="44"/>
-      <c r="R32" s="44"/>
-      <c r="S32" s="44"/>
-      <c r="T32" s="44"/>
-      <c r="U32" s="44"/>
-      <c r="V32" s="44"/>
-      <c r="W32" s="44"/>
+      <c r="N32" s="42"/>
+      <c r="O32" s="42"/>
+      <c r="P32" s="42"/>
+      <c r="Q32" s="42"/>
+      <c r="R32" s="42"/>
+      <c r="S32" s="42"/>
+      <c r="T32" s="42"/>
+      <c r="U32" s="42"/>
+      <c r="V32" s="42"/>
+      <c r="W32" s="42"/>
     </row>
     <row r="33" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="45" t="s">
+      <c r="B33" s="43" t="s">
         <v>64</v>
       </c>
-      <c r="C33" s="46">
+      <c r="C33" s="44">
         <v>90.16</v>
       </c>
-      <c r="D33" s="46">
+      <c r="D33" s="44">
         <v>106.04</v>
       </c>
-      <c r="E33" s="46">
+      <c r="E33" s="44">
         <v>149.41999999999999</v>
       </c>
-      <c r="F33" s="46">
+      <c r="F33" s="44">
         <v>182.27</v>
       </c>
-      <c r="G33" s="46">
+      <c r="G33" s="44">
         <v>245.12</v>
       </c>
-      <c r="H33" s="46">
+      <c r="H33" s="44">
         <v>130.74</v>
       </c>
-      <c r="I33" s="46">
+      <c r="I33" s="44">
         <v>308.35000000000002</v>
       </c>
-      <c r="J33" s="46">
+      <c r="J33" s="44">
         <v>422.89</v>
       </c>
-      <c r="K33" s="46">
+      <c r="K33" s="44">
         <v>414.17</v>
       </c>
-      <c r="L33" s="46">
+      <c r="L33" s="44">
         <v>388.47</v>
       </c>
-      <c r="N33" s="44"/>
-      <c r="O33" s="44"/>
-      <c r="P33" s="44"/>
-      <c r="Q33" s="44"/>
-      <c r="R33" s="44"/>
-      <c r="S33" s="44"/>
-      <c r="T33" s="44"/>
-      <c r="U33" s="44"/>
-      <c r="V33" s="44"/>
-      <c r="W33" s="44"/>
+      <c r="N33" s="42"/>
+      <c r="O33" s="42"/>
+      <c r="P33" s="42"/>
+      <c r="Q33" s="42"/>
+      <c r="R33" s="42"/>
+      <c r="S33" s="42"/>
+      <c r="T33" s="42"/>
+      <c r="U33" s="42"/>
+      <c r="V33" s="42"/>
+      <c r="W33" s="42"/>
     </row>
     <row r="34" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="37" t="s">
+      <c r="B34" s="35" t="s">
         <v>65</v>
       </c>
-      <c r="C34" s="38">
+      <c r="C34" s="36">
         <v>11.86</v>
       </c>
-      <c r="D34" s="42"/>
-      <c r="E34" s="42"/>
-      <c r="F34" s="42"/>
-      <c r="G34" s="38">
+      <c r="D34" s="40"/>
+      <c r="E34" s="40"/>
+      <c r="F34" s="40"/>
+      <c r="G34" s="36">
         <v>50.1</v>
       </c>
-      <c r="H34" s="42"/>
-      <c r="I34" s="38">
+      <c r="H34" s="40"/>
+      <c r="I34" s="36">
         <v>121.35</v>
       </c>
-      <c r="J34" s="38">
+      <c r="J34" s="36">
         <v>218.52</v>
       </c>
-      <c r="K34" s="38">
+      <c r="K34" s="36">
         <v>206.46</v>
       </c>
-      <c r="L34" s="38">
+      <c r="L34" s="36">
         <v>194.32</v>
       </c>
-      <c r="N34" s="44"/>
-      <c r="O34" s="44"/>
-      <c r="P34" s="44"/>
-      <c r="Q34" s="44"/>
-      <c r="R34" s="44"/>
-      <c r="S34" s="44"/>
-      <c r="T34" s="44"/>
-      <c r="U34" s="44"/>
-      <c r="V34" s="44"/>
-      <c r="W34" s="44"/>
+      <c r="N34" s="42"/>
+      <c r="O34" s="42"/>
+      <c r="P34" s="42"/>
+      <c r="Q34" s="42"/>
+      <c r="R34" s="42"/>
+      <c r="S34" s="42"/>
+      <c r="T34" s="42"/>
+      <c r="U34" s="42"/>
+      <c r="V34" s="42"/>
+      <c r="W34" s="42"/>
     </row>
     <row r="36" spans="2:23" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="47" t="s">
+      <c r="B36" s="45" t="s">
         <v>258</v>
       </c>
-      <c r="C36" s="48"/>
-      <c r="D36" s="48"/>
-      <c r="E36" s="48"/>
-      <c r="F36" s="48"/>
-      <c r="G36" s="48"/>
-      <c r="H36" s="48"/>
-      <c r="I36" s="48"/>
-      <c r="J36" s="48"/>
-      <c r="K36" s="48"/>
-      <c r="L36" s="48"/>
+      <c r="C36" s="46"/>
+      <c r="D36" s="46"/>
+      <c r="E36" s="46"/>
+      <c r="F36" s="46"/>
+      <c r="G36" s="46"/>
+      <c r="H36" s="46"/>
+      <c r="I36" s="46"/>
+      <c r="J36" s="46"/>
+      <c r="K36" s="46"/>
+      <c r="L36" s="46"/>
     </row>
     <row r="37" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="35" t="s">
+      <c r="B37" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="C37" s="36" t="s">
+      <c r="C37" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="D37" s="36" t="s">
+      <c r="D37" s="34" t="s">
         <v>35</v>
       </c>
-      <c r="E37" s="36" t="s">
+      <c r="E37" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="F37" s="36" t="s">
+      <c r="F37" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="G37" s="36" t="s">
+      <c r="G37" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="H37" s="36" t="s">
+      <c r="H37" s="34" t="s">
         <v>39</v>
       </c>
-      <c r="I37" s="36" t="s">
+      <c r="I37" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="J37" s="36" t="s">
+      <c r="J37" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="K37" s="36" t="s">
+      <c r="K37" s="34" t="s">
         <v>42</v>
       </c>
-      <c r="L37" s="36" t="s">
+      <c r="L37" s="34" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="38" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B38" s="37" t="s">
+      <c r="B38" s="35" t="s">
         <v>66</v>
       </c>
-      <c r="C38" s="38">
+      <c r="C38" s="36">
         <v>11.86</v>
       </c>
-      <c r="D38" s="38">
+      <c r="D38" s="36">
         <v>11.86</v>
       </c>
-      <c r="E38" s="38">
+      <c r="E38" s="36">
         <v>23.12</v>
       </c>
-      <c r="F38" s="38">
+      <c r="F38" s="36">
         <v>25.05</v>
       </c>
-      <c r="G38" s="38">
+      <c r="G38" s="36">
         <v>25.05</v>
       </c>
-      <c r="H38" s="38">
+      <c r="H38" s="36">
         <v>24.79</v>
       </c>
-      <c r="I38" s="38">
+      <c r="I38" s="36">
         <v>24.27</v>
       </c>
-      <c r="J38" s="38">
+      <c r="J38" s="36">
         <v>24.28</v>
       </c>
-      <c r="K38" s="38">
+      <c r="K38" s="36">
         <v>24.29</v>
       </c>
-      <c r="L38" s="38">
+      <c r="L38" s="36">
         <v>24.29</v>
       </c>
     </row>
     <row r="39" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B39" s="37" t="s">
+      <c r="B39" s="35" t="s">
         <v>67</v>
       </c>
-      <c r="C39" s="38">
+      <c r="C39" s="36">
         <v>221.12</v>
       </c>
-      <c r="D39" s="38">
+      <c r="D39" s="36">
         <v>317.41000000000003</v>
       </c>
-      <c r="E39" s="38">
+      <c r="E39" s="36">
         <v>683.4</v>
       </c>
-      <c r="F39" s="38">
+      <c r="F39" s="36">
         <v>865.09</v>
       </c>
-      <c r="G39" s="38">
+      <c r="G39" s="36">
         <v>1051.0999999999999</v>
       </c>
-      <c r="H39" s="38">
+      <c r="H39" s="36">
         <v>1074.57</v>
       </c>
-      <c r="I39" s="38">
+      <c r="I39" s="36">
         <v>1059.8599999999999</v>
       </c>
-      <c r="J39" s="38">
+      <c r="J39" s="36">
         <v>1370.77</v>
       </c>
-      <c r="K39" s="38">
+      <c r="K39" s="36">
         <v>1577.59</v>
       </c>
-      <c r="L39" s="38">
+      <c r="L39" s="36">
         <v>1762.02</v>
       </c>
     </row>
     <row r="40" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B40" s="45" t="s">
+      <c r="B40" s="43" t="s">
         <v>68</v>
       </c>
-      <c r="C40" s="53">
+      <c r="C40" s="51">
         <f>IFERROR(C38+C39,"")</f>
         <v>232.98000000000002</v>
       </c>
-      <c r="D40" s="53">
+      <c r="D40" s="51">
         <f t="shared" ref="D40:L40" si="2">IFERROR(D38+D39,"")</f>
         <v>329.27000000000004</v>
       </c>
-      <c r="E40" s="53">
+      <c r="E40" s="51">
         <f t="shared" si="2"/>
         <v>706.52</v>
       </c>
-      <c r="F40" s="53">
+      <c r="F40" s="51">
         <f t="shared" si="2"/>
         <v>890.14</v>
       </c>
-      <c r="G40" s="53">
+      <c r="G40" s="51">
         <f t="shared" si="2"/>
         <v>1076.1499999999999</v>
       </c>
-      <c r="H40" s="53">
+      <c r="H40" s="51">
         <f t="shared" si="2"/>
         <v>1099.3599999999999</v>
       </c>
-      <c r="I40" s="53">
+      <c r="I40" s="51">
         <f t="shared" si="2"/>
         <v>1084.1299999999999</v>
       </c>
-      <c r="J40" s="53">
+      <c r="J40" s="51">
         <f t="shared" si="2"/>
         <v>1395.05</v>
       </c>
-      <c r="K40" s="53">
+      <c r="K40" s="51">
         <f t="shared" si="2"/>
         <v>1601.8799999999999</v>
       </c>
-      <c r="L40" s="53">
+      <c r="L40" s="51">
         <f t="shared" si="2"/>
         <v>1786.31</v>
       </c>
     </row>
     <row r="41" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B41" s="45" t="s">
+      <c r="B41" s="43" t="s">
         <v>69</v>
       </c>
-      <c r="C41" s="49">
+      <c r="C41" s="47">
         <v>21.76</v>
       </c>
-      <c r="D41" s="49">
+      <c r="D41" s="47">
         <v>8.57</v>
       </c>
-      <c r="E41" s="49">
+      <c r="E41" s="47">
         <v>12.69</v>
       </c>
-      <c r="F41" s="50"/>
-      <c r="G41" s="49">
+      <c r="F41" s="48"/>
+      <c r="G41" s="47">
         <v>233.76</v>
       </c>
-      <c r="H41" s="49">
+      <c r="H41" s="47">
         <v>203.66</v>
       </c>
-      <c r="I41" s="49">
+      <c r="I41" s="47">
         <v>262.87</v>
       </c>
-      <c r="J41" s="49">
+      <c r="J41" s="47">
         <v>292.55</v>
       </c>
-      <c r="K41" s="49">
+      <c r="K41" s="47">
         <v>444.42</v>
       </c>
-      <c r="L41" s="49">
+      <c r="L41" s="47">
         <v>482.89</v>
       </c>
     </row>
     <row r="42" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B42" s="37" t="s">
+      <c r="B42" s="35" t="s">
         <v>70</v>
       </c>
-      <c r="C42" s="38">
+      <c r="C42" s="36">
         <v>109.35</v>
       </c>
-      <c r="D42" s="38">
+      <c r="D42" s="36">
         <v>153.85</v>
       </c>
-      <c r="E42" s="38">
+      <c r="E42" s="36">
         <v>220.96</v>
       </c>
-      <c r="F42" s="38">
+      <c r="F42" s="36">
         <v>256.88</v>
       </c>
-      <c r="G42" s="38">
+      <c r="G42" s="36">
         <v>280.77</v>
       </c>
-      <c r="H42" s="38">
+      <c r="H42" s="36">
         <v>319.61</v>
       </c>
-      <c r="I42" s="38">
+      <c r="I42" s="36">
         <v>401.96</v>
       </c>
-      <c r="J42" s="38">
+      <c r="J42" s="36">
         <v>473.22</v>
       </c>
-      <c r="K42" s="38">
+      <c r="K42" s="36">
         <v>462.01</v>
       </c>
-      <c r="L42" s="38">
+      <c r="L42" s="36">
         <v>477.38</v>
       </c>
     </row>
     <row r="43" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B43" s="45" t="s">
+      <c r="B43" s="43" t="s">
         <v>71</v>
       </c>
-      <c r="C43" s="54">
+      <c r="C43" s="52">
         <f>C40+C41+C42</f>
         <v>364.09000000000003</v>
       </c>
-      <c r="D43" s="54">
+      <c r="D43" s="52">
         <f>D40+D41+D42</f>
         <v>491.69000000000005</v>
       </c>
-      <c r="E43" s="54">
+      <c r="E43" s="52">
         <f t="shared" ref="E43:L43" si="3">E40+E41+E42</f>
         <v>940.17000000000007</v>
       </c>
-      <c r="F43" s="54">
+      <c r="F43" s="52">
         <f t="shared" si="3"/>
         <v>1147.02</v>
       </c>
-      <c r="G43" s="54">
+      <c r="G43" s="52">
         <f t="shared" si="3"/>
         <v>1590.6799999999998</v>
       </c>
-      <c r="H43" s="54">
+      <c r="H43" s="52">
         <f t="shared" si="3"/>
         <v>1622.63</v>
       </c>
-      <c r="I43" s="54">
+      <c r="I43" s="52">
         <f t="shared" si="3"/>
         <v>1748.96</v>
       </c>
-      <c r="J43" s="54">
+      <c r="J43" s="52">
         <f t="shared" si="3"/>
         <v>2160.8199999999997</v>
       </c>
-      <c r="K43" s="54">
+      <c r="K43" s="52">
         <f t="shared" si="3"/>
         <v>2508.31</v>
       </c>
-      <c r="L43" s="54">
+      <c r="L43" s="52">
         <f t="shared" si="3"/>
         <v>2746.58</v>
       </c>
     </row>
     <row r="44" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B44" s="37" t="s">
+      <c r="B44" s="35" t="s">
         <v>72</v>
       </c>
-      <c r="C44" s="38">
+      <c r="C44" s="36">
         <v>104.06</v>
       </c>
-      <c r="D44" s="38">
+      <c r="D44" s="36">
         <v>141.47999999999999</v>
       </c>
-      <c r="E44" s="38">
+      <c r="E44" s="36">
         <v>315.97000000000003</v>
       </c>
-      <c r="F44" s="38">
+      <c r="F44" s="36">
         <v>252.29</v>
       </c>
-      <c r="G44" s="38">
+      <c r="G44" s="36">
         <v>482.49</v>
       </c>
-      <c r="H44" s="38">
+      <c r="H44" s="36">
         <v>445.78</v>
       </c>
-      <c r="I44" s="38">
+      <c r="I44" s="36">
         <v>495.08</v>
       </c>
-      <c r="J44" s="38">
+      <c r="J44" s="36">
         <v>517.54</v>
       </c>
-      <c r="K44" s="38">
+      <c r="K44" s="36">
         <v>663.42</v>
       </c>
-      <c r="L44" s="38">
+      <c r="L44" s="36">
         <v>687.89</v>
       </c>
     </row>
     <row r="45" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B45" s="37" t="s">
+      <c r="B45" s="35" t="s">
         <v>73</v>
       </c>
-      <c r="C45" s="38">
+      <c r="C45" s="36">
         <v>3.06</v>
       </c>
-      <c r="D45" s="38">
+      <c r="D45" s="36">
         <v>4.66</v>
       </c>
-      <c r="E45" s="38">
+      <c r="E45" s="36">
         <v>0.67</v>
       </c>
-      <c r="F45" s="38">
+      <c r="F45" s="36">
         <v>2.4700000000000002</v>
       </c>
-      <c r="G45" s="38">
+      <c r="G45" s="36">
         <v>0.25</v>
       </c>
-      <c r="H45" s="38">
+      <c r="H45" s="36">
         <v>0.39</v>
       </c>
-      <c r="I45" s="38">
+      <c r="I45" s="36">
         <v>0.1</v>
       </c>
-      <c r="J45" s="38">
+      <c r="J45" s="36">
         <v>2.19</v>
       </c>
-      <c r="K45" s="38">
+      <c r="K45" s="36">
         <v>0.06</v>
       </c>
-      <c r="L45" s="38">
+      <c r="L45" s="36">
         <v>0.06</v>
       </c>
     </row>
     <row r="46" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B46" s="37" t="s">
+      <c r="B46" s="35" t="s">
         <v>74</v>
       </c>
-      <c r="C46" s="51"/>
-      <c r="D46" s="38">
+      <c r="C46" s="49"/>
+      <c r="D46" s="36">
         <v>0.1</v>
       </c>
-      <c r="E46" s="38">
+      <c r="E46" s="36">
         <v>138.31</v>
       </c>
-      <c r="F46" s="38">
+      <c r="F46" s="36">
         <v>194.52</v>
       </c>
-      <c r="G46" s="38">
+      <c r="G46" s="36">
         <v>371.19</v>
       </c>
-      <c r="H46" s="38">
+      <c r="H46" s="36">
         <v>552.86</v>
       </c>
-      <c r="I46" s="38">
+      <c r="I46" s="36">
         <v>523.79</v>
       </c>
-      <c r="J46" s="38">
+      <c r="J46" s="36">
         <v>792.67</v>
       </c>
-      <c r="K46" s="38">
+      <c r="K46" s="36">
         <v>959.22</v>
       </c>
-      <c r="L46" s="38">
+      <c r="L46" s="36">
         <v>1050.92</v>
       </c>
     </row>
     <row r="47" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B47" s="37" t="s">
+      <c r="B47" s="35" t="s">
         <v>78</v>
       </c>
-      <c r="C47" s="38">
+      <c r="C47" s="36">
         <v>62.240000000000009</v>
       </c>
-      <c r="D47" s="38">
+      <c r="D47" s="36">
         <v>62.240000000000009</v>
       </c>
-      <c r="E47" s="38">
+      <c r="E47" s="36">
         <v>62.240000000000009</v>
       </c>
-      <c r="F47" s="38">
+      <c r="F47" s="36">
         <v>62.240000000000009</v>
       </c>
-      <c r="G47" s="38">
+      <c r="G47" s="36">
         <v>62.240000000000009</v>
       </c>
-      <c r="H47" s="38">
+      <c r="H47" s="36">
         <v>62.240000000000009</v>
       </c>
-      <c r="I47" s="38">
+      <c r="I47" s="36">
         <v>62.240000000000009</v>
       </c>
-      <c r="J47" s="38">
+      <c r="J47" s="36">
         <v>62.240000000000009</v>
       </c>
-      <c r="K47" s="38">
+      <c r="K47" s="36">
         <v>62.240000000000009</v>
       </c>
-      <c r="L47" s="38">
+      <c r="L47" s="36">
         <v>62.240000000000009</v>
       </c>
     </row>
     <row r="48" spans="2:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B48" s="37" t="s">
+      <c r="B48" s="35" t="s">
         <v>75</v>
       </c>
-      <c r="C48" s="38">
+      <c r="C48" s="36">
         <v>107.19</v>
       </c>
-      <c r="D48" s="38">
+      <c r="D48" s="36">
         <v>188.5</v>
       </c>
-      <c r="E48" s="38">
+      <c r="E48" s="36">
         <v>321.86</v>
       </c>
-      <c r="F48" s="38">
+      <c r="F48" s="36">
         <v>337.37</v>
       </c>
-      <c r="G48" s="38">
+      <c r="G48" s="36">
         <v>391.42</v>
       </c>
-      <c r="H48" s="38">
+      <c r="H48" s="36">
         <v>366.38</v>
       </c>
-      <c r="I48" s="38">
+      <c r="I48" s="36">
         <v>394.8</v>
       </c>
-      <c r="J48" s="38">
+      <c r="J48" s="36">
         <v>472.84</v>
       </c>
-      <c r="K48" s="38">
+      <c r="K48" s="36">
         <v>564.52</v>
       </c>
-      <c r="L48" s="38">
+      <c r="L48" s="36">
         <v>618.61</v>
       </c>
     </row>
     <row r="49" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B49" s="37" t="s">
+      <c r="B49" s="35" t="s">
         <v>76</v>
       </c>
-      <c r="C49" s="38">
+      <c r="C49" s="36">
         <v>85.86</v>
       </c>
-      <c r="D49" s="38">
+      <c r="D49" s="36">
         <v>97.37</v>
       </c>
-      <c r="E49" s="38">
+      <c r="E49" s="36">
         <v>87.74</v>
       </c>
-      <c r="F49" s="38">
+      <c r="F49" s="36">
         <v>89.6</v>
       </c>
-      <c r="G49" s="38">
+      <c r="G49" s="36">
         <v>114.63</v>
       </c>
-      <c r="H49" s="38">
+      <c r="H49" s="36">
         <v>99.6</v>
       </c>
-      <c r="I49" s="38">
+      <c r="I49" s="36">
         <v>141.5</v>
       </c>
-      <c r="J49" s="38">
+      <c r="J49" s="36">
         <v>173.23</v>
       </c>
-      <c r="K49" s="38">
+      <c r="K49" s="36">
         <v>138.63</v>
       </c>
-      <c r="L49" s="38">
+      <c r="L49" s="36">
         <v>201.97</v>
       </c>
     </row>
     <row r="50" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B50" s="37" t="s">
+      <c r="B50" s="35" t="s">
         <v>77</v>
       </c>
-      <c r="C50" s="38">
+      <c r="C50" s="36">
         <v>1.68</v>
       </c>
-      <c r="D50" s="38">
+      <c r="D50" s="36">
         <v>1.18</v>
       </c>
-      <c r="E50" s="38">
+      <c r="E50" s="36">
         <v>4.71</v>
       </c>
-      <c r="F50" s="38">
+      <c r="F50" s="36">
         <v>118.94</v>
       </c>
-      <c r="G50" s="38">
+      <c r="G50" s="36">
         <v>69.36</v>
       </c>
-      <c r="H50" s="38">
+      <c r="H50" s="36">
         <v>6.94</v>
       </c>
-      <c r="I50" s="38">
+      <c r="I50" s="36">
         <v>3.33</v>
       </c>
-      <c r="J50" s="38">
+      <c r="J50" s="36">
         <v>8.17</v>
       </c>
-      <c r="K50" s="38">
+      <c r="K50" s="36">
         <v>21.71</v>
       </c>
-      <c r="L50" s="38">
+      <c r="L50" s="36">
         <v>17.23</v>
       </c>
     </row>
     <row r="51" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B51" s="45" t="s">
+      <c r="B51" s="43" t="s">
         <v>79</v>
       </c>
-      <c r="C51" s="49">
+      <c r="C51" s="47">
         <v>364.09</v>
       </c>
-      <c r="D51" s="49">
+      <c r="D51" s="47">
         <v>491.69</v>
       </c>
-      <c r="E51" s="49">
+      <c r="E51" s="47">
         <v>940.17</v>
       </c>
-      <c r="F51" s="49">
+      <c r="F51" s="47">
         <v>1147.02</v>
       </c>
-      <c r="G51" s="49">
+      <c r="G51" s="47">
         <v>1590.68</v>
       </c>
-      <c r="H51" s="49">
+      <c r="H51" s="47">
         <v>1622.63</v>
       </c>
-      <c r="I51" s="49">
+      <c r="I51" s="47">
         <v>1748.96</v>
       </c>
-      <c r="J51" s="49">
+      <c r="J51" s="47">
         <v>2160.8200000000002</v>
       </c>
-      <c r="K51" s="49">
+      <c r="K51" s="47">
         <v>2508.31</v>
       </c>
-      <c r="L51" s="49">
+      <c r="L51" s="47">
         <v>2746.58</v>
       </c>
     </row>
     <row r="52" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="L52" s="43"/>
-    </row>
-    <row r="53" spans="2:12" s="34" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B53" s="32" t="s">
+      <c r="L52" s="41"/>
+    </row>
+    <row r="53" spans="2:12" s="32" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B53" s="30" t="s">
         <v>259</v>
       </c>
-      <c r="C53" s="33"/>
-      <c r="D53" s="33"/>
-      <c r="E53" s="33"/>
-      <c r="F53" s="33"/>
-      <c r="G53" s="33"/>
-      <c r="H53" s="33"/>
-      <c r="I53" s="33"/>
-      <c r="J53" s="33"/>
-      <c r="K53" s="33"/>
-      <c r="L53" s="33"/>
+      <c r="C53" s="31"/>
+      <c r="D53" s="31"/>
+      <c r="E53" s="31"/>
+      <c r="F53" s="31"/>
+      <c r="G53" s="31"/>
+      <c r="H53" s="31"/>
+      <c r="I53" s="31"/>
+      <c r="J53" s="31"/>
+      <c r="K53" s="31"/>
+      <c r="L53" s="31"/>
     </row>
     <row r="54" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B54" s="35" t="s">
+      <c r="B54" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="C54" s="36" t="s">
+      <c r="C54" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="D54" s="36" t="s">
+      <c r="D54" s="34" t="s">
         <v>35</v>
       </c>
-      <c r="E54" s="36" t="s">
+      <c r="E54" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="F54" s="36" t="s">
+      <c r="F54" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="G54" s="36" t="s">
+      <c r="G54" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="H54" s="36" t="s">
+      <c r="H54" s="34" t="s">
         <v>39</v>
       </c>
-      <c r="I54" s="36" t="s">
+      <c r="I54" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="J54" s="36" t="s">
+      <c r="J54" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="K54" s="36" t="s">
+      <c r="K54" s="34" t="s">
         <v>42</v>
       </c>
-      <c r="L54" s="36" t="s">
+      <c r="L54" s="34" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="55" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B55" s="37" t="s">
+      <c r="B55" s="35" t="s">
         <v>80</v>
       </c>
-      <c r="C55" s="52"/>
-      <c r="D55" s="38">
+      <c r="C55" s="50"/>
+      <c r="D55" s="36">
         <v>36.869999999999997</v>
       </c>
-      <c r="E55" s="38">
+      <c r="E55" s="36">
         <v>51.76</v>
       </c>
-      <c r="F55" s="38">
+      <c r="F55" s="36">
         <v>178.68</v>
       </c>
-      <c r="G55" s="38">
+      <c r="G55" s="36">
         <v>250.63</v>
       </c>
-      <c r="H55" s="38">
+      <c r="H55" s="36">
         <v>252.7</v>
       </c>
-      <c r="I55" s="38">
+      <c r="I55" s="36">
         <v>341.07</v>
       </c>
-      <c r="J55" s="38">
+      <c r="J55" s="36">
         <v>459.12</v>
       </c>
-      <c r="K55" s="38">
+      <c r="K55" s="36">
         <v>483.08</v>
       </c>
-      <c r="L55" s="38">
+      <c r="L55" s="36">
         <v>388.6</v>
       </c>
     </row>
     <row r="56" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B56" s="37" t="s">
+      <c r="B56" s="35" t="s">
         <v>81</v>
       </c>
-      <c r="C56" s="52"/>
-      <c r="D56" s="38">
+      <c r="C56" s="50"/>
+      <c r="D56" s="36">
         <v>-21.53</v>
       </c>
-      <c r="E56" s="38">
+      <c r="E56" s="36">
         <v>-279.02999999999997</v>
       </c>
-      <c r="F56" s="38">
+      <c r="F56" s="36">
         <v>-165.01</v>
       </c>
-      <c r="G56" s="38">
+      <c r="G56" s="36">
         <v>-105.9</v>
       </c>
-      <c r="H56" s="38">
+      <c r="H56" s="36">
         <v>-90.02</v>
       </c>
-      <c r="I56" s="38">
+      <c r="I56" s="36">
         <v>62.01</v>
       </c>
-      <c r="J56" s="38">
+      <c r="J56" s="36">
         <v>-227.89</v>
       </c>
-      <c r="K56" s="38">
+      <c r="K56" s="36">
         <v>-109.52</v>
       </c>
-      <c r="L56" s="38">
+      <c r="L56" s="36">
         <v>-15.88</v>
       </c>
     </row>
     <row r="57" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B57" s="37" t="s">
+      <c r="B57" s="35" t="s">
         <v>82</v>
       </c>
-      <c r="C57" s="52"/>
-      <c r="D57" s="38">
+      <c r="C57" s="50"/>
+      <c r="D57" s="36">
         <v>-15.81</v>
       </c>
-      <c r="E57" s="38">
+      <c r="E57" s="36">
         <v>223.54</v>
       </c>
-      <c r="F57" s="38">
+      <c r="F57" s="36">
         <v>-12.86</v>
       </c>
-      <c r="G57" s="38">
+      <c r="G57" s="36">
         <v>-137.9</v>
       </c>
-      <c r="H57" s="38">
+      <c r="H57" s="36">
         <v>-164.75</v>
       </c>
-      <c r="I57" s="38">
+      <c r="I57" s="36">
         <v>-406.45</v>
       </c>
-      <c r="J57" s="38">
+      <c r="J57" s="36">
         <v>-226.39</v>
       </c>
-      <c r="K57" s="38">
+      <c r="K57" s="36">
         <v>-361.6</v>
       </c>
-      <c r="L57" s="38">
+      <c r="L57" s="36">
         <v>-377.2</v>
       </c>
     </row>
     <row r="58" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B58" s="37" t="s">
+      <c r="B58" s="35" t="s">
         <v>83</v>
       </c>
-      <c r="C58" s="52"/>
-      <c r="D58" s="38">
+      <c r="C58" s="50"/>
+      <c r="D58" s="36">
         <v>-0.47</v>
       </c>
-      <c r="E58" s="38">
+      <c r="E58" s="36">
         <v>-3.73</v>
       </c>
-      <c r="F58" s="38">
+      <c r="F58" s="36">
         <v>0.81</v>
       </c>
-      <c r="G58" s="38">
+      <c r="G58" s="36">
         <v>6.83</v>
       </c>
-      <c r="H58" s="38">
+      <c r="H58" s="36">
         <v>-2.0699999999999998</v>
       </c>
-      <c r="I58" s="38">
+      <c r="I58" s="36">
         <v>-3.38</v>
       </c>
-      <c r="J58" s="38">
+      <c r="J58" s="36">
         <v>4.84</v>
       </c>
-      <c r="K58" s="38">
+      <c r="K58" s="36">
         <v>11.95</v>
       </c>
-      <c r="L58" s="38">
+      <c r="L58" s="36">
         <v>-4.49</v>
       </c>
     </row>
-    <row r="60" spans="2:12" s="34" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B60" s="32" t="s">
+    <row r="60" spans="2:12" s="32" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B60" s="30" t="s">
         <v>260</v>
       </c>
-      <c r="C60" s="33"/>
-      <c r="D60" s="33"/>
-      <c r="E60" s="33"/>
-      <c r="F60" s="33"/>
-      <c r="G60" s="33"/>
-      <c r="H60" s="33"/>
-      <c r="I60" s="33"/>
-      <c r="J60" s="33"/>
-      <c r="K60" s="33"/>
-      <c r="L60" s="33"/>
+      <c r="C60" s="31"/>
+      <c r="D60" s="31"/>
+      <c r="E60" s="31"/>
+      <c r="F60" s="31"/>
+      <c r="G60" s="31"/>
+      <c r="H60" s="31"/>
+      <c r="I60" s="31"/>
+      <c r="J60" s="31"/>
+      <c r="K60" s="31"/>
+      <c r="L60" s="31"/>
     </row>
     <row r="61" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B61" s="35" t="s">
+      <c r="B61" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="C61" s="36" t="s">
+      <c r="C61" s="34" t="s">
         <v>84</v>
       </c>
-      <c r="D61" s="36" t="s">
+      <c r="D61" s="34" t="s">
         <v>85</v>
       </c>
-      <c r="E61" s="36" t="s">
+      <c r="E61" s="34" t="s">
         <v>86</v>
       </c>
-      <c r="F61" s="36" t="s">
+      <c r="F61" s="34" t="s">
         <v>87</v>
       </c>
-      <c r="G61" s="36" t="s">
+      <c r="G61" s="34" t="s">
         <v>88</v>
       </c>
-      <c r="H61" s="36" t="s">
+      <c r="H61" s="34" t="s">
         <v>89</v>
       </c>
-      <c r="I61" s="36" t="s">
+      <c r="I61" s="34" t="s">
         <v>90</v>
       </c>
-      <c r="J61" s="36" t="s">
+      <c r="J61" s="34" t="s">
         <v>91</v>
       </c>
-      <c r="K61" s="36" t="s">
+      <c r="K61" s="34" t="s">
         <v>92</v>
       </c>
-      <c r="L61" s="36" t="s">
+      <c r="L61" s="34" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="62" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B62" s="37" t="s">
+      <c r="B62" s="35" t="s">
         <v>94</v>
       </c>
-      <c r="C62" s="38">
+      <c r="C62" s="36">
         <v>217.86</v>
       </c>
-      <c r="D62" s="38">
+      <c r="D62" s="36">
         <v>474.46</v>
       </c>
-      <c r="E62" s="38">
+      <c r="E62" s="36">
         <v>363.16</v>
       </c>
-      <c r="F62" s="38">
+      <c r="F62" s="36">
         <v>239.82</v>
       </c>
-      <c r="G62" s="38">
+      <c r="G62" s="36">
         <v>267.95</v>
       </c>
-      <c r="H62" s="38">
+      <c r="H62" s="36">
         <v>511.28</v>
       </c>
-      <c r="I62" s="38">
+      <c r="I62" s="36">
         <v>367.44</v>
       </c>
-      <c r="J62" s="38">
+      <c r="J62" s="36">
         <v>281.19</v>
       </c>
-      <c r="K62" s="38">
+      <c r="K62" s="36">
         <v>263.14999999999998</v>
       </c>
-      <c r="L62" s="38">
+      <c r="L62" s="36">
         <v>491.71</v>
       </c>
     </row>
     <row r="63" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B63" s="37" t="s">
+      <c r="B63" s="35" t="s">
         <v>95</v>
       </c>
-      <c r="C63" s="38">
+      <c r="C63" s="36">
         <v>125.13</v>
       </c>
-      <c r="D63" s="38">
+      <c r="D63" s="36">
         <v>232.41</v>
       </c>
-      <c r="E63" s="38">
+      <c r="E63" s="36">
         <v>188.07</v>
       </c>
-      <c r="F63" s="38">
+      <c r="F63" s="36">
         <v>127.12</v>
       </c>
-      <c r="G63" s="38">
+      <c r="G63" s="36">
         <v>145.96</v>
       </c>
-      <c r="H63" s="38">
+      <c r="H63" s="36">
         <v>269.08</v>
       </c>
-      <c r="I63" s="38">
+      <c r="I63" s="36">
         <v>201.71</v>
       </c>
-      <c r="J63" s="38">
+      <c r="J63" s="36">
         <v>160.6</v>
       </c>
-      <c r="K63" s="38">
+      <c r="K63" s="36">
         <v>152.36000000000001</v>
       </c>
-      <c r="L63" s="38">
+      <c r="L63" s="36">
         <v>273.61</v>
       </c>
     </row>
     <row r="64" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B64" s="45" t="s">
+      <c r="B64" s="43" t="s">
         <v>96</v>
       </c>
-      <c r="C64" s="49">
+      <c r="C64" s="47">
         <v>92.73</v>
       </c>
-      <c r="D64" s="49">
+      <c r="D64" s="47">
         <v>242.05</v>
       </c>
-      <c r="E64" s="49">
+      <c r="E64" s="47">
         <v>175.09</v>
       </c>
-      <c r="F64" s="49">
+      <c r="F64" s="47">
         <v>112.7</v>
       </c>
-      <c r="G64" s="49">
+      <c r="G64" s="47">
         <v>121.99</v>
       </c>
-      <c r="H64" s="49">
+      <c r="H64" s="47">
         <v>242.2</v>
       </c>
-      <c r="I64" s="49">
+      <c r="I64" s="47">
         <v>165.73</v>
       </c>
-      <c r="J64" s="49">
+      <c r="J64" s="47">
         <v>120.59</v>
       </c>
-      <c r="K64" s="49">
+      <c r="K64" s="47">
         <v>110.79</v>
       </c>
-      <c r="L64" s="49">
+      <c r="L64" s="47">
         <v>218.1</v>
       </c>
     </row>
     <row r="65" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B65" s="45" t="s">
+      <c r="B65" s="43" t="s">
         <v>97</v>
       </c>
-      <c r="C65" s="55">
+      <c r="C65" s="53">
         <f>IFERROR(C64/C62,"")</f>
         <v>0.42564031947122005</v>
       </c>
-      <c r="D65" s="55">
+      <c r="D65" s="53">
         <f t="shared" ref="D65:L65" si="4">IFERROR(D64/D62,"")</f>
         <v>0.51015891750621767</v>
       </c>
-      <c r="E65" s="55">
+      <c r="E65" s="53">
         <f t="shared" si="4"/>
         <v>0.4821290891067298</v>
       </c>
-      <c r="F65" s="55">
+      <c r="F65" s="53">
         <f t="shared" si="4"/>
         <v>0.46993578517221252</v>
       </c>
-      <c r="G65" s="55">
+      <c r="G65" s="53">
         <f t="shared" si="4"/>
         <v>0.45527150587796228</v>
       </c>
-      <c r="H65" s="55">
+      <c r="H65" s="53">
         <f t="shared" si="4"/>
         <v>0.47371303395399783</v>
       </c>
-      <c r="I65" s="55">
+      <c r="I65" s="53">
         <f t="shared" si="4"/>
         <v>0.4510396255170912</v>
       </c>
-      <c r="J65" s="55">
+      <c r="J65" s="53">
         <f t="shared" si="4"/>
         <v>0.42885593371030267</v>
       </c>
-      <c r="K65" s="55">
+      <c r="K65" s="53">
         <f t="shared" si="4"/>
         <v>0.42101463043891324</v>
       </c>
-      <c r="L65" s="55">
+      <c r="L65" s="53">
         <f t="shared" si="4"/>
         <v>0.44355412743283645</v>
       </c>
     </row>
     <row r="66" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B66" s="37" t="s">
+      <c r="B66" s="35" t="s">
         <v>59</v>
       </c>
-      <c r="C66" s="38">
+      <c r="C66" s="36">
         <v>14.79</v>
       </c>
-      <c r="D66" s="38">
+      <c r="D66" s="36">
         <v>15.47</v>
       </c>
-      <c r="E66" s="38">
+      <c r="E66" s="36">
         <v>24.11</v>
       </c>
-      <c r="F66" s="38">
+      <c r="F66" s="36">
         <v>21.46</v>
       </c>
-      <c r="G66" s="38">
+      <c r="G66" s="36">
         <v>19.239999999999998</v>
       </c>
-      <c r="H66" s="38">
+      <c r="H66" s="36">
         <v>22.39</v>
       </c>
-      <c r="I66" s="38">
+      <c r="I66" s="36">
         <v>22.06</v>
       </c>
-      <c r="J66" s="38">
+      <c r="J66" s="36">
         <v>25.83</v>
       </c>
-      <c r="K66" s="38">
+      <c r="K66" s="36">
         <v>19.920000000000002</v>
       </c>
-      <c r="L66" s="38">
+      <c r="L66" s="36">
         <v>21.44</v>
       </c>
     </row>
     <row r="67" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B67" s="37" t="s">
+      <c r="B67" s="35" t="s">
         <v>98</v>
       </c>
-      <c r="C67" s="38">
+      <c r="C67" s="36">
         <v>31.81</v>
       </c>
-      <c r="D67" s="38">
+      <c r="D67" s="36">
         <v>34.43</v>
       </c>
-      <c r="E67" s="38">
+      <c r="E67" s="36">
         <v>38.06</v>
       </c>
-      <c r="F67" s="38">
+      <c r="F67" s="36">
         <v>37.18</v>
       </c>
-      <c r="G67" s="38">
+      <c r="G67" s="36">
         <v>37.29</v>
       </c>
-      <c r="H67" s="38">
+      <c r="H67" s="36">
         <v>39.130000000000003</v>
       </c>
-      <c r="I67" s="38">
+      <c r="I67" s="36">
         <v>39.46</v>
       </c>
-      <c r="J67" s="38">
+      <c r="J67" s="36">
         <v>39.78</v>
       </c>
-      <c r="K67" s="38">
+      <c r="K67" s="36">
         <v>41.69</v>
       </c>
-      <c r="L67" s="38">
+      <c r="L67" s="36">
         <v>44.21</v>
       </c>
     </row>
     <row r="68" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B68" s="37" t="s">
+      <c r="B68" s="35" t="s">
         <v>99</v>
       </c>
-      <c r="C68" s="38">
+      <c r="C68" s="36">
         <v>10.68</v>
       </c>
-      <c r="D68" s="38">
+      <c r="D68" s="36">
         <v>11.18</v>
       </c>
-      <c r="E68" s="38">
+      <c r="E68" s="36">
         <v>13.22</v>
       </c>
-      <c r="F68" s="38">
+      <c r="F68" s="36">
         <v>13.92</v>
       </c>
-      <c r="G68" s="38">
+      <c r="G68" s="36">
         <v>13.72</v>
       </c>
-      <c r="H68" s="38">
+      <c r="H68" s="36">
         <v>13.95</v>
       </c>
-      <c r="I68" s="38">
+      <c r="I68" s="36">
         <v>13.62</v>
       </c>
-      <c r="J68" s="38">
+      <c r="J68" s="36">
         <v>14.13</v>
       </c>
-      <c r="K68" s="38">
+      <c r="K68" s="36">
         <v>14.97</v>
       </c>
-      <c r="L68" s="38">
+      <c r="L68" s="36">
         <v>14.03</v>
       </c>
     </row>
     <row r="69" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B69" s="37" t="s">
+      <c r="B69" s="35" t="s">
         <v>62</v>
       </c>
-      <c r="C69" s="38">
+      <c r="C69" s="36">
         <v>65.03</v>
       </c>
-      <c r="D69" s="38">
+      <c r="D69" s="36">
         <v>211.91</v>
       </c>
-      <c r="E69" s="38">
+      <c r="E69" s="36">
         <v>147.91999999999999</v>
       </c>
-      <c r="F69" s="38">
+      <c r="F69" s="36">
         <v>83.06</v>
       </c>
-      <c r="G69" s="38">
+      <c r="G69" s="36">
         <v>90.22</v>
       </c>
-      <c r="H69" s="38">
+      <c r="H69" s="36">
         <v>211.51</v>
       </c>
-      <c r="I69" s="38">
+      <c r="I69" s="36">
         <v>134.71</v>
       </c>
-      <c r="J69" s="38">
+      <c r="J69" s="36">
         <v>92.51</v>
       </c>
-      <c r="K69" s="38">
+      <c r="K69" s="36">
         <v>74.05</v>
       </c>
-      <c r="L69" s="38">
+      <c r="L69" s="36">
         <v>181.3</v>
       </c>
     </row>
     <row r="70" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B70" s="37" t="s">
+      <c r="B70" s="35" t="s">
         <v>63</v>
       </c>
-      <c r="C70" s="38">
+      <c r="C70" s="36">
         <v>16.05</v>
       </c>
-      <c r="D70" s="38">
+      <c r="D70" s="36">
         <v>54.2</v>
       </c>
-      <c r="E70" s="38">
+      <c r="E70" s="36">
         <v>32.130000000000003</v>
       </c>
-      <c r="F70" s="38">
+      <c r="F70" s="36">
         <v>20.57</v>
       </c>
-      <c r="G70" s="38">
+      <c r="G70" s="36">
         <v>23.32</v>
       </c>
-      <c r="H70" s="38">
+      <c r="H70" s="36">
         <v>53.54</v>
       </c>
-      <c r="I70" s="38">
+      <c r="I70" s="36">
         <v>33.6</v>
       </c>
-      <c r="J70" s="38">
+      <c r="J70" s="36">
         <v>22.25</v>
       </c>
-      <c r="K70" s="38">
+      <c r="K70" s="36">
         <v>17.96</v>
       </c>
-      <c r="L70" s="38">
+      <c r="L70" s="36">
         <v>46.39</v>
       </c>
     </row>
     <row r="71" spans="2:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B71" s="45" t="s">
+      <c r="B71" s="43" t="s">
         <v>100</v>
       </c>
-      <c r="C71" s="49">
+      <c r="C71" s="47">
         <v>48.99</v>
       </c>
-      <c r="D71" s="49">
+      <c r="D71" s="47">
         <v>157.71</v>
       </c>
-      <c r="E71" s="49">
+      <c r="E71" s="47">
         <v>115.79</v>
       </c>
-      <c r="F71" s="49">
+      <c r="F71" s="47">
         <v>62.49</v>
       </c>
-      <c r="G71" s="49">
+      <c r="G71" s="47">
         <v>66.900000000000006</v>
       </c>
-      <c r="H71" s="49">
+      <c r="H71" s="47">
         <v>157.97999999999999</v>
       </c>
-      <c r="I71" s="49">
+      <c r="I71" s="47">
         <v>101.11</v>
       </c>
-      <c r="J71" s="49">
+      <c r="J71" s="47">
         <v>70.260000000000005</v>
       </c>
-      <c r="K71" s="49">
+      <c r="K71" s="47">
         <v>56.08</v>
       </c>
-      <c r="L71" s="49">
+      <c r="L71" s="47">
         <v>134.9</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="/fZuglZPg+ZUfxCZ98acyOaLbd6xIrfMG3plQEYlvKIJ0Jc0oGrw+9R/2xwPlbZZnoA6mp3oHBv7EVhUiVn8DQ==" saltValue="4X4EypuT7oGnSy2zN+m3DQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="r9yiSwHTC28c/juavDPz/+zEqBmcW7BXgB8udSHhpNwx4EktkfKAmxkDJ5Y+dlA2AVgn0KjEDfYl6sr3hjQKwg==" saltValue="70D5tSqFa8bP6avnO3oMZQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="73" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <drawing r:id="rId2"/>
@@ -5683,7 +6132,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <sheetPr>
+  <sheetPr codeName="Sheet3">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B2:I80"/>
@@ -5711,7 +6160,7 @@
       <c r="I2" s="3"/>
     </row>
     <row r="3" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="56" t="s">
+      <c r="B3" s="54" t="s">
         <v>101</v>
       </c>
       <c r="C3" s="1"/>
@@ -5733,458 +6182,458 @@
       <c r="I4" s="3"/>
     </row>
     <row r="6" spans="2:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="32" t="s">
+      <c r="B6" s="30" t="s">
         <v>261</v>
       </c>
-      <c r="C6" s="33"/>
-      <c r="D6" s="33"/>
+      <c r="C6" s="31"/>
+      <c r="D6" s="31"/>
     </row>
     <row r="7" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="37" t="s">
+      <c r="B7" s="35" t="s">
         <v>102</v>
       </c>
-      <c r="D7" s="86">
+      <c r="D7" s="83">
         <f>'Data Sheet'!L19</f>
         <v>1386.48</v>
       </c>
-      <c r="E7" s="57"/>
+      <c r="E7" s="55"/>
     </row>
     <row r="8" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="37" t="s">
+      <c r="B8" s="35" t="s">
         <v>103</v>
       </c>
-      <c r="D8" s="86">
+      <c r="D8" s="83">
         <f>'Data Sheet'!L27</f>
         <v>642.61</v>
       </c>
-      <c r="E8" s="57"/>
+      <c r="E8" s="55"/>
     </row>
     <row r="9" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="37" t="s">
+      <c r="B9" s="35" t="s">
         <v>104</v>
       </c>
-      <c r="D9" s="93">
+      <c r="D9" s="90">
         <f>D8/D7</f>
         <v>0.46348306502798453</v>
       </c>
-      <c r="E9" s="57"/>
+      <c r="E9" s="55"/>
     </row>
     <row r="10" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="37" t="s">
+      <c r="B10" s="35" t="s">
         <v>105</v>
       </c>
-      <c r="D10" s="86">
+      <c r="D10" s="83">
         <f>'Data Sheet'!L29</f>
         <v>153.06</v>
       </c>
-      <c r="E10" s="57"/>
+      <c r="E10" s="55"/>
     </row>
     <row r="11" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="37" t="s">
+      <c r="B11" s="35" t="s">
         <v>106</v>
       </c>
-      <c r="D11" s="94">
+      <c r="D11" s="91">
         <f>D8-D10</f>
         <v>489.55</v>
       </c>
-      <c r="E11" s="57"/>
+      <c r="E11" s="55"/>
     </row>
     <row r="12" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="37" t="s">
+      <c r="B12" s="35" t="s">
         <v>107</v>
       </c>
-      <c r="D12" s="86">
+      <c r="D12" s="83">
         <f>'Data Sheet'!L30</f>
         <v>55.21</v>
       </c>
-      <c r="E12" s="57"/>
+      <c r="E12" s="55"/>
     </row>
     <row r="13" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="37" t="s">
+      <c r="B13" s="35" t="s">
         <v>108</v>
       </c>
-      <c r="D13" s="86">
+      <c r="D13" s="83">
         <f>'Data Sheet'!L31</f>
         <v>519.5</v>
       </c>
-      <c r="E13" s="57"/>
+      <c r="E13" s="55"/>
     </row>
     <row r="14" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="37" t="s">
+      <c r="B14" s="35" t="s">
         <v>109</v>
       </c>
-      <c r="D14" s="93">
+      <c r="D14" s="90">
         <f>'Data Sheet'!L32/'Data Sheet'!L31</f>
         <v>0.25222329162656398</v>
       </c>
-      <c r="E14" s="58"/>
+      <c r="E14" s="56"/>
     </row>
     <row r="15" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="37" t="s">
+      <c r="B15" s="35" t="s">
         <v>110</v>
       </c>
-      <c r="D15" s="86">
+      <c r="D15" s="83">
         <f>'Data Sheet'!L33</f>
         <v>388.47</v>
       </c>
-      <c r="E15" s="57"/>
+      <c r="E15" s="55"/>
     </row>
     <row r="16" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="37" t="s">
+      <c r="B16" s="35" t="s">
         <v>111</v>
       </c>
-      <c r="D16" s="59">
+      <c r="D16" s="57">
         <v>114</v>
       </c>
-      <c r="E16" s="57"/>
+      <c r="E16" s="55"/>
     </row>
     <row r="17" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="37" t="s">
+      <c r="B17" s="35" t="s">
         <v>112</v>
       </c>
-      <c r="D17" s="59">
+      <c r="D17" s="57">
         <v>104</v>
       </c>
-      <c r="E17" s="57"/>
+      <c r="E17" s="55"/>
     </row>
     <row r="18" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="37" t="s">
+      <c r="B18" s="35" t="s">
         <v>113</v>
       </c>
-      <c r="D18" s="86">
+      <c r="D18" s="83">
         <f>'Data Sheet'!L41</f>
         <v>482.89</v>
       </c>
-      <c r="E18" s="57"/>
+      <c r="E18" s="55"/>
     </row>
     <row r="19" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="37" t="s">
+      <c r="B19" s="35" t="s">
         <v>114</v>
       </c>
-      <c r="D19" s="86">
+      <c r="D19" s="83">
         <f>'Data Sheet'!L50</f>
         <v>17.23</v>
       </c>
-      <c r="E19" s="57"/>
+      <c r="E19" s="55"/>
     </row>
     <row r="20" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="37" t="s">
+      <c r="B20" s="35" t="s">
         <v>115</v>
       </c>
-      <c r="D20" s="86">
+      <c r="D20" s="83">
         <f>D18-D19</f>
         <v>465.65999999999997</v>
       </c>
-      <c r="E20" s="57"/>
+      <c r="E20" s="55"/>
     </row>
     <row r="22" spans="2:5" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="32" t="s">
+      <c r="B22" s="30" t="s">
         <v>116</v>
       </c>
-      <c r="C22" s="33"/>
-      <c r="D22" s="33"/>
+      <c r="C22" s="31"/>
+      <c r="D22" s="31"/>
     </row>
     <row r="23" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="37" t="s">
+      <c r="B23" s="35" t="s">
         <v>117</v>
       </c>
-      <c r="D23" s="59">
+      <c r="D23" s="57">
         <v>350.1</v>
       </c>
-      <c r="E23" s="57"/>
+      <c r="E23" s="55"/>
     </row>
     <row r="24" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="37" t="s">
+      <c r="B24" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="D24" s="86">
+      <c r="D24" s="83">
         <f>'Data Sheet'!L11</f>
         <v>24.29</v>
       </c>
-      <c r="E24" s="57"/>
+      <c r="E24" s="55"/>
     </row>
     <row r="25" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="37" t="s">
+      <c r="B25" s="35" t="s">
         <v>118</v>
       </c>
-      <c r="D25" s="95">
+      <c r="D25" s="92">
         <f>D23*D24</f>
         <v>8503.9290000000001</v>
       </c>
-      <c r="E25" s="57"/>
+      <c r="E25" s="55"/>
     </row>
     <row r="26" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="37" t="s">
+      <c r="B26" s="35" t="s">
         <v>119</v>
       </c>
-      <c r="D26" s="61">
+      <c r="D26" s="59">
         <v>0.3</v>
       </c>
-      <c r="E26" s="57"/>
+      <c r="E26" s="55"/>
     </row>
     <row r="27" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="37" t="s">
+      <c r="B27" s="35" t="s">
         <v>120</v>
       </c>
-      <c r="D27" s="86">
+      <c r="D27" s="83">
         <f>D23*(1+D26)</f>
         <v>455.13000000000005</v>
       </c>
-      <c r="E27" s="57"/>
+      <c r="E27" s="55"/>
     </row>
     <row r="28" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="37" t="s">
+      <c r="B28" s="35" t="s">
         <v>121</v>
       </c>
-      <c r="D28" s="86">
+      <c r="D28" s="83">
         <f>D27*D24</f>
         <v>11055.1077</v>
       </c>
-      <c r="E28" s="57"/>
+      <c r="E28" s="55"/>
     </row>
     <row r="29" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="37" t="s">
+      <c r="B29" s="35" t="s">
         <v>122</v>
       </c>
-      <c r="D29" s="86">
+      <c r="D29" s="83">
         <f>D18</f>
         <v>482.89</v>
       </c>
-      <c r="E29" s="57"/>
+      <c r="E29" s="55"/>
     </row>
     <row r="30" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="37" t="s">
+      <c r="B30" s="35" t="s">
         <v>123</v>
       </c>
-      <c r="D30" s="86">
+      <c r="D30" s="83">
         <f>D19</f>
         <v>17.23</v>
       </c>
-      <c r="E30" s="57"/>
+      <c r="E30" s="55"/>
     </row>
     <row r="31" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="45" t="s">
+      <c r="B31" s="43" t="s">
         <v>124</v>
       </c>
-      <c r="D31" s="95">
+      <c r="D31" s="92">
         <f>D28+D29-D30</f>
         <v>11520.7677</v>
       </c>
-      <c r="E31" s="57"/>
+      <c r="E31" s="55"/>
     </row>
     <row r="32" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="45" t="s">
+      <c r="B32" s="43" t="s">
         <v>125</v>
       </c>
-      <c r="D32" s="96">
+      <c r="D32" s="93">
         <f>D31/D8</f>
         <v>17.928086553274927</v>
       </c>
-      <c r="E32" s="57"/>
+      <c r="E32" s="55"/>
     </row>
     <row r="33" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="37" t="s">
+      <c r="B33" s="35" t="s">
         <v>126</v>
       </c>
-      <c r="D33" s="61">
+      <c r="D33" s="59">
         <v>0.02</v>
       </c>
-      <c r="E33" s="57"/>
+      <c r="E33" s="55"/>
     </row>
     <row r="34" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="37" t="s">
+      <c r="B34" s="35" t="s">
         <v>127</v>
       </c>
-      <c r="D34" s="86">
+      <c r="D34" s="83">
         <f>D33*D31</f>
         <v>230.41535400000001</v>
       </c>
-      <c r="E34" s="57"/>
+      <c r="E34" s="55"/>
     </row>
     <row r="35" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="62" t="s">
+      <c r="B35" s="60" t="s">
         <v>128</v>
       </c>
-      <c r="C35" s="62"/>
-      <c r="D35" s="112">
+      <c r="C35" s="60"/>
+      <c r="D35" s="109">
         <f>D28+D29+D34</f>
         <v>11768.413054000001</v>
       </c>
-      <c r="E35" s="57"/>
+      <c r="E35" s="55"/>
     </row>
     <row r="37" spans="2:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="126" t="s">
+      <c r="B37" s="125" t="s">
         <v>129</v>
       </c>
-      <c r="C37" s="126"/>
-      <c r="D37" s="126"/>
-      <c r="E37" s="126"/>
-      <c r="F37" s="126"/>
-      <c r="G37" s="126"/>
-      <c r="H37" s="126"/>
-      <c r="I37" s="126"/>
-    </row>
-    <row r="38" spans="2:9" s="68" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B38" s="63" t="s">
+      <c r="C37" s="125"/>
+      <c r="D37" s="125"/>
+      <c r="E37" s="125"/>
+      <c r="F37" s="125"/>
+      <c r="G37" s="125"/>
+      <c r="H37" s="125"/>
+      <c r="I37" s="125"/>
+    </row>
+    <row r="38" spans="2:9" s="66" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B38" s="61" t="s">
         <v>130</v>
       </c>
-      <c r="C38" s="63"/>
-      <c r="D38" s="63"/>
-      <c r="E38" s="64" t="s">
+      <c r="C38" s="61"/>
+      <c r="D38" s="61"/>
+      <c r="E38" s="62" t="s">
         <v>131</v>
       </c>
-      <c r="F38" s="65" t="s">
+      <c r="F38" s="63" t="s">
         <v>132</v>
       </c>
-      <c r="G38" s="66" t="s">
+      <c r="G38" s="64" t="s">
         <v>133</v>
       </c>
-      <c r="H38" s="65" t="s">
+      <c r="H38" s="63" t="s">
         <v>134</v>
       </c>
-      <c r="I38" s="67" t="s">
+      <c r="I38" s="65" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="39" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B39" s="37" t="s">
+      <c r="B39" s="35" t="s">
         <v>136</v>
       </c>
-      <c r="E39" s="69">
+      <c r="E39" s="67">
         <v>1800</v>
       </c>
-      <c r="F39" s="99">
+      <c r="F39" s="96">
         <f>E39/D31</f>
         <v>0.15623958809619953</v>
       </c>
-      <c r="G39" s="97">
+      <c r="G39" s="94">
         <f>E39/D8</f>
         <v>2.8010768584366876</v>
       </c>
-      <c r="H39" s="61">
+      <c r="H39" s="59">
         <v>0.105</v>
       </c>
-      <c r="I39" s="70">
+      <c r="I39" s="68">
         <v>5</v>
       </c>
     </row>
     <row r="40" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B40" s="37" t="s">
+      <c r="B40" s="35" t="s">
         <v>137</v>
       </c>
-      <c r="E40" s="69">
+      <c r="E40" s="67">
         <v>700</v>
       </c>
-      <c r="F40" s="99">
+      <c r="F40" s="96">
         <f>E40/D31</f>
         <v>6.0759839815188704E-2</v>
       </c>
-      <c r="G40" s="97">
+      <c r="G40" s="94">
         <f>E40/D8</f>
         <v>1.089307667169823</v>
       </c>
-      <c r="H40" s="61">
+      <c r="H40" s="59">
         <v>0.12</v>
       </c>
-      <c r="I40" s="71">
+      <c r="I40" s="69">
         <v>6</v>
       </c>
     </row>
     <row r="41" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B41" s="37" t="s">
+      <c r="B41" s="35" t="s">
         <v>138</v>
       </c>
-      <c r="E41" s="69">
+      <c r="E41" s="67">
         <v>200</v>
       </c>
-      <c r="F41" s="99">
+      <c r="F41" s="96">
         <f>E41/D31</f>
         <v>1.7359954232911059E-2</v>
       </c>
-      <c r="G41" s="97">
+      <c r="G41" s="94">
         <f>E41/D8</f>
         <v>0.31123076204852085</v>
       </c>
-      <c r="H41" s="61">
+      <c r="H41" s="59">
         <v>0.14000000000000001</v>
       </c>
-      <c r="I41" s="70">
+      <c r="I41" s="68">
         <v>5</v>
       </c>
     </row>
     <row r="42" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B42" s="45" t="s">
+      <c r="B42" s="43" t="s">
         <v>139</v>
       </c>
-      <c r="C42" s="45"/>
-      <c r="D42" s="45"/>
-      <c r="E42" s="95">
+      <c r="C42" s="43"/>
+      <c r="D42" s="43"/>
+      <c r="E42" s="92">
         <f>E39+E40+E41</f>
         <v>2700</v>
       </c>
-      <c r="F42" s="98">
+      <c r="F42" s="95">
         <f>E42/D31</f>
         <v>0.23435938214429927</v>
       </c>
-      <c r="G42" s="96">
+      <c r="G42" s="93">
         <f>E42/D8</f>
         <v>4.2016152876550317</v>
       </c>
-      <c r="H42" s="98">
+      <c r="H42" s="95">
         <f>SUMPRODUCT(E39:E41,H39:H41)/E42</f>
         <v>0.11148148148148149</v>
       </c>
-      <c r="I42" s="71"/>
+      <c r="I42" s="69"/>
     </row>
     <row r="43" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B43" s="72" t="s">
+      <c r="B43" s="70" t="s">
         <v>140</v>
       </c>
-      <c r="C43" s="72"/>
-      <c r="D43" s="72"/>
-      <c r="E43" s="95">
+      <c r="C43" s="70"/>
+      <c r="D43" s="70"/>
+      <c r="E43" s="92">
         <f>D35-E42</f>
         <v>9068.4130540000006</v>
       </c>
-      <c r="F43" s="98">
+      <c r="F43" s="95">
         <f>E43/D31</f>
         <v>0.78713617791286605</v>
       </c>
     </row>
     <row r="44" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B44" s="62" t="s">
+      <c r="B44" s="60" t="s">
         <v>141</v>
       </c>
-      <c r="C44" s="62"/>
-      <c r="D44" s="62"/>
-      <c r="E44" s="124">
+      <c r="C44" s="60"/>
+      <c r="D44" s="60"/>
+      <c r="E44" s="121">
         <f>E42+E43</f>
         <v>11768.413054000001</v>
       </c>
-      <c r="F44" s="73"/>
-      <c r="G44" s="74"/>
-      <c r="H44" s="73"/>
-      <c r="I44" s="75"/>
+      <c r="F44" s="71"/>
+      <c r="G44" s="72"/>
+      <c r="H44" s="71"/>
+      <c r="I44" s="73"/>
     </row>
     <row r="45" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="46" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B46" s="76" t="s">
+      <c r="B46" s="74" t="s">
         <v>241</v>
       </c>
-      <c r="C46" s="77"/>
-      <c r="D46" s="77"/>
-      <c r="E46" s="77"/>
-      <c r="F46" s="77"/>
-      <c r="G46" s="77"/>
+      <c r="C46" s="75"/>
+      <c r="D46" s="75"/>
+      <c r="E46" s="75"/>
+      <c r="F46" s="75"/>
+      <c r="G46" s="75"/>
     </row>
     <row r="47" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E47" s="78" t="s">
+      <c r="E47" s="76" t="s">
         <v>242</v>
       </c>
-      <c r="F47" s="78" t="s">
+      <c r="F47" s="76" t="s">
         <v>243</v>
       </c>
-      <c r="G47" s="78" t="s">
+      <c r="G47" s="76" t="s">
         <v>244</v>
       </c>
     </row>
@@ -6192,15 +6641,15 @@
       <c r="B48" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="E48" s="100">
+      <c r="E48" s="97">
         <f>E39</f>
         <v>1800</v>
       </c>
-      <c r="F48" s="101">
+      <c r="F48" s="98">
         <f>E48/$D$8</f>
         <v>2.8010768584366876</v>
       </c>
-      <c r="G48" s="102">
+      <c r="G48" s="99">
         <f>E48/$E$52</f>
         <v>0.15295180341993458</v>
       </c>
@@ -6209,15 +6658,15 @@
       <c r="B49" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="E49" s="100">
+      <c r="E49" s="97">
         <f>E40</f>
         <v>700</v>
       </c>
-      <c r="F49" s="101">
+      <c r="F49" s="98">
         <f>E49/$D$8</f>
         <v>1.089307667169823</v>
       </c>
-      <c r="G49" s="102">
+      <c r="G49" s="99">
         <f>E49/$E$52</f>
         <v>5.9481256885530111E-2</v>
       </c>
@@ -6226,15 +6675,15 @@
       <c r="B50" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="E50" s="100">
+      <c r="E50" s="97">
         <f>E41</f>
         <v>200</v>
       </c>
-      <c r="F50" s="101">
+      <c r="F50" s="98">
         <f>E50/$D$8</f>
         <v>0.31123076204852085</v>
       </c>
-      <c r="G50" s="102">
+      <c r="G50" s="99">
         <f>E50/$E$52</f>
         <v>1.6994644824437175E-2</v>
       </c>
@@ -6243,57 +6692,57 @@
       <c r="B51" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="E51" s="100">
+      <c r="E51" s="97">
         <f>E43</f>
         <v>9068.4130540000006</v>
       </c>
-      <c r="F51" s="101">
+      <c r="F51" s="98">
         <f>E51/$D$8</f>
         <v>14.111845526835873</v>
       </c>
-      <c r="G51" s="102">
+      <c r="G51" s="99">
         <f>E51/$E$52</f>
         <v>0.77057229487009815</v>
       </c>
     </row>
     <row r="52" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B52" s="79" t="s">
+      <c r="B52" s="77" t="s">
         <v>247</v>
       </c>
-      <c r="C52" s="80"/>
-      <c r="D52" s="80"/>
-      <c r="E52" s="91">
+      <c r="C52" s="78"/>
+      <c r="D52" s="78"/>
+      <c r="E52" s="88">
         <f>SUM(E48:E51)</f>
         <v>11768.413054000001</v>
       </c>
-      <c r="F52" s="103">
+      <c r="F52" s="100">
         <f>SUM(F48:F51)</f>
         <v>18.313460814490902</v>
       </c>
-      <c r="G52" s="92">
+      <c r="G52" s="89">
         <f>SUM(G48:G51)</f>
         <v>1</v>
       </c>
     </row>
     <row r="53" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="54" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B54" s="76" t="s">
+      <c r="B54" s="74" t="s">
         <v>250</v>
       </c>
-      <c r="C54" s="76"/>
-      <c r="D54" s="76"/>
-      <c r="E54" s="76"/>
-      <c r="F54" s="76"/>
-      <c r="G54" s="76"/>
+      <c r="C54" s="74"/>
+      <c r="D54" s="74"/>
+      <c r="E54" s="74"/>
+      <c r="F54" s="74"/>
+      <c r="G54" s="74"/>
     </row>
     <row r="55" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E55" s="78" t="s">
+      <c r="E55" s="76" t="s">
         <v>242</v>
       </c>
-      <c r="F55" s="78" t="s">
+      <c r="F55" s="76" t="s">
         <v>243</v>
       </c>
-      <c r="G55" s="78" t="s">
+      <c r="G55" s="76" t="s">
         <v>244</v>
       </c>
     </row>
@@ -6301,15 +6750,15 @@
       <c r="B56" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="E56" s="100">
+      <c r="E56" s="97">
         <f>D28</f>
         <v>11055.1077</v>
       </c>
-      <c r="F56" s="101">
+      <c r="F56" s="98">
         <f>E56/$D$8</f>
         <v>17.203447969997356</v>
       </c>
-      <c r="G56" s="104">
+      <c r="G56" s="101">
         <f>E56/$E$59</f>
         <v>0.9393881442870029</v>
       </c>
@@ -6318,15 +6767,15 @@
       <c r="B57" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="E57" s="100">
+      <c r="E57" s="97">
         <f>D29</f>
         <v>482.89</v>
       </c>
-      <c r="F57" s="101">
+      <c r="F57" s="98">
         <f>E57/$D$8</f>
         <v>0.75145111342805115</v>
       </c>
-      <c r="G57" s="104">
+      <c r="G57" s="101">
         <f>E57/$E$59</f>
         <v>4.1032720196362338E-2</v>
       </c>
@@ -6335,291 +6784,293 @@
       <c r="B58" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="E58" s="100">
+      <c r="E58" s="97">
         <f>D34</f>
         <v>230.41535400000001</v>
       </c>
-      <c r="F58" s="101">
+      <c r="F58" s="98">
         <f>E58/$D$8</f>
         <v>0.35856173106549855</v>
       </c>
-      <c r="G58" s="104">
+      <c r="G58" s="101">
         <f>E58/$E$59</f>
         <v>1.9579135516634798E-2</v>
       </c>
     </row>
     <row r="59" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B59" s="79" t="s">
+      <c r="B59" s="77" t="s">
         <v>247</v>
       </c>
-      <c r="C59" s="80"/>
-      <c r="D59" s="80"/>
-      <c r="E59" s="91">
+      <c r="C59" s="78"/>
+      <c r="D59" s="78"/>
+      <c r="E59" s="88">
         <f>SUM(E56:E58)</f>
         <v>11768.413054000001</v>
       </c>
-      <c r="F59" s="103">
+      <c r="F59" s="100">
         <f>SUM(F56:F58)</f>
         <v>18.313460814490906</v>
       </c>
-      <c r="G59" s="92">
+      <c r="G59" s="89">
         <f>SUM(G56:G58)</f>
         <v>1</v>
       </c>
     </row>
     <row r="60" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="61" spans="2:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B61" s="32" t="s">
+      <c r="B61" s="30" t="s">
         <v>142</v>
       </c>
-      <c r="C61" s="33"/>
-      <c r="D61" s="33"/>
-      <c r="E61" s="33"/>
-      <c r="F61" s="33"/>
-      <c r="G61" s="33"/>
-      <c r="H61" s="33"/>
-      <c r="I61" s="32"/>
+      <c r="C61" s="31"/>
+      <c r="D61" s="31"/>
+      <c r="E61" s="31"/>
+      <c r="F61" s="31"/>
+      <c r="G61" s="31"/>
+      <c r="H61" s="31"/>
+      <c r="I61" s="30"/>
     </row>
     <row r="62" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B62" s="35" t="s">
+      <c r="B62" s="33" t="s">
         <v>143</v>
       </c>
-      <c r="C62" s="81" t="s">
+      <c r="C62" s="79" t="s">
         <v>144</v>
       </c>
-      <c r="D62" s="81" t="s">
+      <c r="D62" s="79" t="s">
         <v>145</v>
       </c>
-      <c r="E62" s="81" t="s">
+      <c r="E62" s="79" t="s">
         <v>146</v>
       </c>
-      <c r="F62" s="81" t="s">
+      <c r="F62" s="79" t="s">
         <v>147</v>
       </c>
-      <c r="G62" s="81" t="s">
+      <c r="G62" s="79" t="s">
         <v>148</v>
       </c>
-      <c r="H62" s="81" t="s">
+      <c r="H62" s="79" t="s">
         <v>149</v>
       </c>
-      <c r="I62" s="81" t="s">
+      <c r="I62" s="79" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="63" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B63" s="45" t="s">
+      <c r="B63" s="43" t="s">
         <v>151</v>
       </c>
-      <c r="C63" s="82" t="s">
+      <c r="C63" s="80" t="s">
         <v>152</v>
       </c>
-      <c r="D63" s="83">
+      <c r="D63" s="81">
         <v>0.06</v>
       </c>
-      <c r="E63" s="83">
+      <c r="E63" s="122">
+        <f>'Sensitivity Analysis'!C8</f>
         <v>0.1</v>
       </c>
-      <c r="F63" s="83">
+      <c r="F63" s="81">
         <v>0.12</v>
       </c>
-      <c r="G63" s="83">
+      <c r="G63" s="81">
         <v>0.12</v>
       </c>
-      <c r="H63" s="83">
+      <c r="H63" s="81">
         <v>0.12</v>
       </c>
-      <c r="I63" s="83">
+      <c r="I63" s="81">
         <v>0.11</v>
       </c>
     </row>
     <row r="64" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="65" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B65" s="45" t="s">
+      <c r="B65" s="43" t="s">
         <v>153</v>
       </c>
-      <c r="C65" s="82" t="s">
+      <c r="C65" s="80" t="s">
         <v>154</v>
       </c>
-      <c r="D65" s="83">
+      <c r="D65" s="81">
         <v>0.44</v>
       </c>
-      <c r="E65" s="83">
+      <c r="E65" s="81">
         <v>0.44800000000000001</v>
       </c>
-      <c r="F65" s="83">
+      <c r="F65" s="81">
         <v>0.45500000000000002</v>
       </c>
-      <c r="G65" s="83">
+      <c r="G65" s="81">
         <v>0.46</v>
       </c>
-      <c r="H65" s="83">
+      <c r="H65" s="81">
         <v>0.46200000000000002</v>
       </c>
-      <c r="I65" s="83">
+      <c r="I65" s="81">
         <v>0.46500000000000002</v>
       </c>
     </row>
     <row r="66" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="67" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B67" s="45" t="s">
+      <c r="B67" s="43" t="s">
         <v>155</v>
       </c>
-      <c r="C67" s="82" t="s">
+      <c r="C67" s="80" t="s">
         <v>154</v>
       </c>
-      <c r="D67" s="83">
+      <c r="D67" s="81">
         <v>0.11</v>
       </c>
-      <c r="E67" s="83">
+      <c r="E67" s="81">
         <v>0.108</v>
       </c>
-      <c r="F67" s="83">
+      <c r="F67" s="81">
         <v>0.105</v>
       </c>
-      <c r="G67" s="83">
+      <c r="G67" s="81">
         <v>0.10299999999999999</v>
       </c>
-      <c r="H67" s="83">
+      <c r="H67" s="81">
         <v>0.1</v>
       </c>
-      <c r="I67" s="83">
+      <c r="I67" s="81">
         <v>9.8000000000000004E-2</v>
       </c>
     </row>
     <row r="68" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="69" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B69" s="45" t="s">
+      <c r="B69" s="43" t="s">
         <v>156</v>
       </c>
-      <c r="C69" s="82" t="s">
+      <c r="C69" s="80" t="s">
         <v>154</v>
       </c>
-      <c r="D69" s="83">
+      <c r="D69" s="81">
         <v>8.5000000000000006E-2</v>
       </c>
-      <c r="E69" s="83">
+      <c r="E69" s="81">
         <v>0.08</v>
       </c>
-      <c r="F69" s="83">
+      <c r="F69" s="81">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="G69" s="83">
+      <c r="G69" s="81">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="H69" s="83">
+      <c r="H69" s="81">
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="I69" s="83">
+      <c r="I69" s="81">
         <v>0.06</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="71" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B71" s="45" t="s">
+      <c r="B71" s="43" t="s">
         <v>157</v>
       </c>
-      <c r="C71" s="82" t="s">
+      <c r="C71" s="80" t="s">
         <v>154</v>
       </c>
-      <c r="D71" s="83">
+      <c r="D71" s="81">
         <v>5.5E-2</v>
       </c>
-      <c r="E71" s="83">
+      <c r="E71" s="81">
         <v>4.4999999999999998E-2</v>
       </c>
-      <c r="F71" s="83">
+      <c r="F71" s="81">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="G71" s="83">
+      <c r="G71" s="81">
         <v>0.03</v>
       </c>
-      <c r="H71" s="83">
+      <c r="H71" s="81">
         <v>2.8000000000000001E-2</v>
       </c>
-      <c r="I71" s="83">
+      <c r="I71" s="81">
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
     <row r="72" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="73" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B73" s="45" t="s">
+      <c r="B73" s="43" t="s">
         <v>158</v>
       </c>
-      <c r="C73" s="82" t="s">
+      <c r="C73" s="80" t="s">
         <v>159</v>
       </c>
-      <c r="D73" s="83">
+      <c r="D73" s="81">
         <v>0.252</v>
       </c>
-      <c r="E73" s="83">
+      <c r="E73" s="81">
         <v>0.252</v>
       </c>
-      <c r="F73" s="83">
+      <c r="F73" s="81">
         <v>0.252</v>
       </c>
-      <c r="G73" s="83">
+      <c r="G73" s="81">
         <v>0.252</v>
       </c>
-      <c r="H73" s="83">
+      <c r="H73" s="81">
         <v>0.252</v>
       </c>
-      <c r="I73" s="83">
+      <c r="I73" s="81">
         <v>0.252</v>
       </c>
     </row>
     <row r="74" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="76" spans="2:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B76" s="32" t="s">
+      <c r="B76" s="30" t="s">
         <v>160</v>
       </c>
-      <c r="C76" s="33"/>
-      <c r="D76" s="33"/>
-      <c r="E76" s="33"/>
-      <c r="F76" s="33"/>
-      <c r="G76" s="33"/>
-      <c r="H76" s="33"/>
-      <c r="I76" s="32"/>
+      <c r="C76" s="31"/>
+      <c r="D76" s="31"/>
+      <c r="E76" s="31"/>
+      <c r="F76" s="31"/>
+      <c r="G76" s="31"/>
+      <c r="H76" s="31"/>
+      <c r="I76" s="30"/>
     </row>
     <row r="77" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B77" s="37" t="s">
+      <c r="B77" s="35" t="s">
         <v>161</v>
       </c>
-      <c r="C77" s="71">
+      <c r="C77" s="69">
         <v>6</v>
       </c>
-      <c r="E77" s="84"/>
+      <c r="E77" s="82"/>
     </row>
     <row r="78" spans="2:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B78" s="45" t="s">
+      <c r="B78" s="43" t="s">
         <v>162</v>
       </c>
-      <c r="C78" s="85">
+      <c r="C78" s="123">
+        <f>'Sensitivity Analysis'!C7</f>
         <v>22</v>
       </c>
-      <c r="E78" s="84"/>
+      <c r="E78" s="82"/>
     </row>
     <row r="79" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B79" s="45" t="s">
+      <c r="B79" s="43" t="s">
         <v>163</v>
       </c>
-      <c r="C79" s="105">
+      <c r="C79" s="102">
         <f>Financials!M10*C78</f>
         <v>25790.801576045269</v>
       </c>
-      <c r="E79" s="84"/>
+      <c r="E79" s="82"/>
     </row>
     <row r="80" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B80" s="37" t="s">
+      <c r="B80" s="35" t="s">
         <v>164</v>
       </c>
-      <c r="C80" s="105">
+      <c r="C80" s="102">
         <f>C79-'Debt Schedule'!H19</f>
         <v>25790.801576045269</v>
       </c>
-      <c r="E80" s="84"/>
+      <c r="E80" s="82"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="cKgYt20wjkH6wCjheLSwEOPiTCvvBJmq2SDyPOE+L4ST9RYK+DUnCya3rltdNG9jFriUtUvOzPOlw3t1xI3sLg==" saltValue="3HDXUZyu4YMZbX49MIsj+g==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="SdOPv8wBqZoHrXjAFLQHUyKwChUT0B6asH9yc7T534fW9ee0QZZ5I5EXiKRxRfKd/4hpGuL1jqO6Qey4yO3Ubw==" saltValue="1BUwTv7SumuICdHrGA5FoA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="B37:I37"/>
   </mergeCells>
@@ -6628,13 +7079,16 @@
   <colBreaks count="1" manualBreakCount="1">
     <brk id="7" max="1048575" man="1"/>
   </colBreaks>
+  <ignoredErrors>
+    <ignoredError sqref="E63 C78" unlockedFormula="1"/>
+  </ignoredErrors>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <sheetPr>
+  <sheetPr codeName="Sheet4">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B2:T34"/>
@@ -6662,7 +7116,7 @@
       <c r="T2" s="3"/>
     </row>
     <row r="3" spans="2:20" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="106" t="s">
+      <c r="B3" s="103" t="s">
         <v>165</v>
       </c>
       <c r="C3" s="1"/>
@@ -6694,1195 +7148,1195 @@
       <c r="T4" s="3"/>
     </row>
     <row r="6" spans="2:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="107" t="s">
+      <c r="B6" s="104" t="s">
         <v>263</v>
       </c>
-      <c r="C6" s="81" t="s">
+      <c r="C6" s="79" t="s">
         <v>166</v>
       </c>
-      <c r="D6" s="81" t="s">
+      <c r="D6" s="79" t="s">
         <v>167</v>
       </c>
-      <c r="E6" s="81" t="s">
+      <c r="E6" s="79" t="s">
         <v>168</v>
       </c>
-      <c r="F6" s="81" t="s">
+      <c r="F6" s="79" t="s">
         <v>169</v>
       </c>
-      <c r="G6" s="81" t="s">
+      <c r="G6" s="79" t="s">
         <v>170</v>
       </c>
-      <c r="H6" s="108" t="s">
+      <c r="H6" s="105" t="s">
         <v>145</v>
       </c>
-      <c r="I6" s="108" t="s">
+      <c r="I6" s="105" t="s">
         <v>146</v>
       </c>
-      <c r="J6" s="108" t="s">
+      <c r="J6" s="105" t="s">
         <v>147</v>
       </c>
-      <c r="K6" s="108" t="s">
+      <c r="K6" s="105" t="s">
         <v>148</v>
       </c>
-      <c r="L6" s="108" t="s">
+      <c r="L6" s="105" t="s">
         <v>149</v>
       </c>
-      <c r="M6" s="108" t="s">
+      <c r="M6" s="105" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="7" spans="2:20" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="32" t="s">
+      <c r="B7" s="30" t="s">
         <v>171</v>
       </c>
-      <c r="C7" s="32"/>
-      <c r="D7" s="32"/>
-      <c r="E7" s="32"/>
-      <c r="F7" s="32"/>
-      <c r="G7" s="32"/>
-      <c r="H7" s="32"/>
-      <c r="I7" s="32"/>
-      <c r="J7" s="32"/>
-      <c r="K7" s="32"/>
-      <c r="L7" s="32"/>
-      <c r="M7" s="32"/>
+      <c r="C7" s="30"/>
+      <c r="D7" s="30"/>
+      <c r="E7" s="30"/>
+      <c r="F7" s="30"/>
+      <c r="G7" s="30"/>
+      <c r="H7" s="30"/>
+      <c r="I7" s="30"/>
+      <c r="J7" s="30"/>
+      <c r="K7" s="30"/>
+      <c r="L7" s="30"/>
+      <c r="M7" s="30"/>
     </row>
     <row r="8" spans="2:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="45" t="s">
+      <c r="B8" s="43" t="s">
         <v>50</v>
       </c>
-      <c r="C8" s="95">
+      <c r="C8" s="92">
         <f>'Data Sheet'!H19</f>
         <v>542.41</v>
       </c>
-      <c r="D8" s="95">
+      <c r="D8" s="92">
         <f>'Data Sheet'!I19</f>
         <v>1008.75</v>
       </c>
-      <c r="E8" s="95">
+      <c r="E8" s="92">
         <f>'Data Sheet'!J19</f>
         <v>1325.96</v>
       </c>
-      <c r="F8" s="95">
+      <c r="F8" s="92">
         <f>'Data Sheet'!K19</f>
         <v>1367.53</v>
       </c>
-      <c r="G8" s="95">
+      <c r="G8" s="92">
         <f>'Data Sheet'!L19</f>
         <v>1386.48</v>
       </c>
-      <c r="H8" s="95">
+      <c r="H8" s="92">
         <f>G8*(1+Assumptions!D63)</f>
         <v>1469.6688000000001</v>
       </c>
-      <c r="I8" s="95">
+      <c r="I8" s="92">
         <f>H8*(1+Assumptions!E63)</f>
         <v>1616.6356800000003</v>
       </c>
-      <c r="J8" s="95">
+      <c r="J8" s="92">
         <f>I8*(1+Assumptions!F63)</f>
         <v>1810.6319616000005</v>
       </c>
-      <c r="K8" s="95">
+      <c r="K8" s="92">
         <f>J8*(1+Assumptions!G63)</f>
         <v>2027.9077969920008</v>
       </c>
-      <c r="L8" s="95">
+      <c r="L8" s="92">
         <f>K8*(1+Assumptions!H63)</f>
         <v>2271.2567326310414</v>
       </c>
-      <c r="M8" s="95">
+      <c r="M8" s="92">
         <f>L8*(1+Assumptions!I63)</f>
         <v>2521.0949732204563</v>
       </c>
     </row>
     <row r="9" spans="2:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="107" t="s">
+      <c r="B9" s="104" t="s">
         <v>172</v>
       </c>
-      <c r="C9" s="109" t="s">
+      <c r="C9" s="106" t="s">
         <v>47</v>
       </c>
-      <c r="D9" s="99">
+      <c r="D9" s="96">
         <f>D8/C8-1</f>
         <v>0.85975553548054062</v>
       </c>
-      <c r="E9" s="99">
+      <c r="E9" s="96">
         <f t="shared" ref="E9:G9" si="0">E8/D8-1</f>
         <v>0.31445848822800504</v>
       </c>
-      <c r="F9" s="99">
+      <c r="F9" s="96">
         <f t="shared" si="0"/>
         <v>3.1350870312829793E-2</v>
       </c>
-      <c r="G9" s="99">
+      <c r="G9" s="96">
         <f t="shared" si="0"/>
         <v>1.3857100027056202E-2</v>
       </c>
-      <c r="H9" s="99">
+      <c r="H9" s="96">
         <f>Assumptions!D63</f>
         <v>0.06</v>
       </c>
-      <c r="I9" s="99">
+      <c r="I9" s="96">
         <f>Assumptions!E63</f>
         <v>0.1</v>
       </c>
-      <c r="J9" s="99">
+      <c r="J9" s="96">
         <f>Assumptions!F63</f>
         <v>0.12</v>
       </c>
-      <c r="K9" s="99">
+      <c r="K9" s="96">
         <f>Assumptions!G63</f>
         <v>0.12</v>
       </c>
-      <c r="L9" s="99">
+      <c r="L9" s="96">
         <f>Assumptions!H63</f>
         <v>0.12</v>
       </c>
-      <c r="M9" s="99">
+      <c r="M9" s="96">
         <f>Assumptions!I63</f>
         <v>0.11</v>
       </c>
     </row>
     <row r="10" spans="2:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="45" t="s">
+      <c r="B10" s="43" t="s">
         <v>96</v>
       </c>
-      <c r="C10" s="95">
+      <c r="C10" s="92">
         <f>'Data Sheet'!H27</f>
         <v>235.03999999999996</v>
       </c>
-      <c r="D10" s="95">
+      <c r="D10" s="92">
         <f>'Data Sheet'!I27</f>
         <v>480.34000000000003</v>
       </c>
-      <c r="E10" s="95">
+      <c r="E10" s="92">
         <f>'Data Sheet'!J27</f>
         <v>657.80000000000007</v>
       </c>
-      <c r="F10" s="95">
+      <c r="F10" s="92">
         <f>'Data Sheet'!K27</f>
         <v>658.09</v>
       </c>
-      <c r="G10" s="95">
+      <c r="G10" s="92">
         <f>'Data Sheet'!L27</f>
         <v>642.61</v>
       </c>
-      <c r="H10" s="95">
+      <c r="H10" s="92">
         <f>H8*Assumptions!D65</f>
         <v>646.65427200000011</v>
       </c>
-      <c r="I10" s="95">
+      <c r="I10" s="92">
         <f>I8*Assumptions!E65</f>
         <v>724.25278464000019</v>
       </c>
-      <c r="J10" s="95">
+      <c r="J10" s="92">
         <f>J8*Assumptions!F65</f>
         <v>823.83754252800031</v>
       </c>
-      <c r="K10" s="95">
+      <c r="K10" s="92">
         <f>K8*Assumptions!G65</f>
         <v>932.83758661632044</v>
       </c>
-      <c r="L10" s="95">
+      <c r="L10" s="92">
         <f>L8*Assumptions!H65</f>
         <v>1049.3206104755411</v>
       </c>
-      <c r="M10" s="95">
+      <c r="M10" s="92">
         <f>M8*Assumptions!I65</f>
         <v>1172.3091625475122</v>
       </c>
     </row>
     <row r="11" spans="2:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="110" t="s">
+      <c r="B11" s="107" t="s">
         <v>173</v>
       </c>
-      <c r="C11" s="99">
+      <c r="C11" s="96">
         <f>C10/C8</f>
         <v>0.43332534429674963</v>
       </c>
-      <c r="D11" s="99">
+      <c r="D11" s="96">
         <f t="shared" ref="D11:G11" si="1">D10/D8</f>
         <v>0.4761734820322181</v>
       </c>
-      <c r="E11" s="99">
+      <c r="E11" s="96">
         <f t="shared" si="1"/>
         <v>0.49609339648254852</v>
       </c>
-      <c r="F11" s="99">
+      <c r="F11" s="96">
         <f t="shared" si="1"/>
         <v>0.48122527476545307</v>
       </c>
-      <c r="G11" s="99">
+      <c r="G11" s="96">
         <f t="shared" si="1"/>
         <v>0.46348306502798453</v>
       </c>
-      <c r="H11" s="99">
+      <c r="H11" s="96">
         <f>IFERROR(H10/H8,"")</f>
         <v>0.44</v>
       </c>
-      <c r="I11" s="99">
+      <c r="I11" s="96">
         <f t="shared" ref="I11:M11" si="2">IFERROR(I10/I8,"")</f>
         <v>0.44800000000000001</v>
       </c>
-      <c r="J11" s="99">
+      <c r="J11" s="96">
         <f t="shared" si="2"/>
         <v>0.45500000000000002</v>
       </c>
-      <c r="K11" s="99">
+      <c r="K11" s="96">
         <f t="shared" si="2"/>
         <v>0.46</v>
       </c>
-      <c r="L11" s="99">
+      <c r="L11" s="96">
         <f t="shared" si="2"/>
         <v>0.46200000000000002</v>
       </c>
-      <c r="M11" s="99">
+      <c r="M11" s="96">
         <f t="shared" si="2"/>
         <v>0.46500000000000002</v>
       </c>
     </row>
     <row r="12" spans="2:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="37" t="s">
+      <c r="B12" s="35" t="s">
         <v>174</v>
       </c>
-      <c r="C12" s="86">
+      <c r="C12" s="83">
         <f>'Data Sheet'!H29</f>
         <v>89.05</v>
       </c>
-      <c r="D12" s="86">
+      <c r="D12" s="83">
         <f>'Data Sheet'!I29</f>
         <v>88.03</v>
       </c>
-      <c r="E12" s="86">
+      <c r="E12" s="83">
         <f>'Data Sheet'!J29</f>
         <v>97.46</v>
       </c>
-      <c r="F12" s="86">
+      <c r="F12" s="83">
         <f>'Data Sheet'!K29</f>
         <v>134.85</v>
       </c>
-      <c r="G12" s="86">
+      <c r="G12" s="83">
         <f>'Data Sheet'!L29</f>
         <v>153.06</v>
       </c>
-      <c r="H12" s="86">
+      <c r="H12" s="83">
         <f>H8*Assumptions!D67</f>
         <v>161.66356800000003</v>
       </c>
-      <c r="I12" s="86">
+      <c r="I12" s="83">
         <f>I8*Assumptions!E67</f>
         <v>174.59665344000004</v>
       </c>
-      <c r="J12" s="86">
+      <c r="J12" s="83">
         <f>J8*Assumptions!F67</f>
         <v>190.11635596800005</v>
       </c>
-      <c r="K12" s="86">
+      <c r="K12" s="83">
         <f>K8*Assumptions!G67</f>
         <v>208.87450309017606</v>
       </c>
-      <c r="L12" s="86">
+      <c r="L12" s="83">
         <f>L8*Assumptions!H67</f>
         <v>227.12567326310415</v>
       </c>
-      <c r="M12" s="86">
+      <c r="M12" s="83">
         <f>M8*Assumptions!I67</f>
         <v>247.06730737560471</v>
       </c>
     </row>
     <row r="13" spans="2:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="45" t="s">
+      <c r="B13" s="43" t="s">
         <v>175</v>
       </c>
-      <c r="C13" s="95">
+      <c r="C13" s="92">
         <f>C10-C12</f>
         <v>145.98999999999995</v>
       </c>
-      <c r="D13" s="95">
+      <c r="D13" s="92">
         <f t="shared" ref="D13:M13" si="3">D10-D12</f>
         <v>392.31000000000006</v>
       </c>
-      <c r="E13" s="95">
+      <c r="E13" s="92">
         <f t="shared" si="3"/>
         <v>560.34</v>
       </c>
-      <c r="F13" s="95">
+      <c r="F13" s="92">
         <f t="shared" si="3"/>
         <v>523.24</v>
       </c>
-      <c r="G13" s="95">
+      <c r="G13" s="92">
         <f>G10-G12</f>
         <v>489.55</v>
       </c>
-      <c r="H13" s="95">
+      <c r="H13" s="92">
         <f t="shared" si="3"/>
         <v>484.99070400000005</v>
       </c>
-      <c r="I13" s="95">
+      <c r="I13" s="92">
         <f t="shared" si="3"/>
         <v>549.65613120000012</v>
       </c>
-      <c r="J13" s="95">
+      <c r="J13" s="92">
         <f t="shared" si="3"/>
         <v>633.72118656000021</v>
       </c>
-      <c r="K13" s="95">
+      <c r="K13" s="92">
         <f t="shared" si="3"/>
         <v>723.96308352614437</v>
       </c>
-      <c r="L13" s="95">
+      <c r="L13" s="92">
         <f t="shared" si="3"/>
         <v>822.19493721243703</v>
       </c>
-      <c r="M13" s="95">
+      <c r="M13" s="92">
         <f t="shared" si="3"/>
         <v>925.24185517190745</v>
       </c>
     </row>
     <row r="14" spans="2:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="37" t="s">
+      <c r="B14" s="35" t="s">
         <v>176</v>
       </c>
-      <c r="C14" s="86">
+      <c r="C14" s="83">
         <f>'Data Sheet'!H30</f>
         <v>25.07</v>
       </c>
-      <c r="D14" s="86">
+      <c r="D14" s="83">
         <f>'Data Sheet'!I30</f>
         <v>27.07</v>
       </c>
-      <c r="E14" s="86">
+      <c r="E14" s="83">
         <f>'Data Sheet'!J30</f>
         <v>30.35</v>
       </c>
-      <c r="F14" s="86">
+      <c r="F14" s="83">
         <f>'Data Sheet'!K30</f>
         <v>44.5</v>
       </c>
-      <c r="G14" s="86">
+      <c r="G14" s="83">
         <f>'Data Sheet'!L30</f>
         <v>55.21</v>
       </c>
-      <c r="H14" s="86">
+      <c r="H14" s="83">
         <f>'Debt Schedule'!C26</f>
         <v>282.10000000000002</v>
       </c>
-      <c r="I14" s="86">
+      <c r="I14" s="83">
         <f>'Debt Schedule'!D26</f>
         <v>244.29999999999998</v>
       </c>
-      <c r="J14" s="86">
+      <c r="J14" s="83">
         <f>'Debt Schedule'!E26</f>
         <v>206.5</v>
       </c>
-      <c r="K14" s="86">
+      <c r="K14" s="83">
         <f>'Debt Schedule'!F26</f>
         <v>168.7</v>
       </c>
-      <c r="L14" s="86">
+      <c r="L14" s="83">
         <f>'Debt Schedule'!G26</f>
         <v>116.9</v>
       </c>
-      <c r="M14" s="86">
+      <c r="M14" s="83">
         <f>'Debt Schedule'!H26</f>
         <v>42</v>
       </c>
     </row>
     <row r="15" spans="2:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="45" t="s">
+      <c r="B15" s="43" t="s">
         <v>177</v>
       </c>
-      <c r="C15" s="95">
+      <c r="C15" s="92">
         <f>C13-C14</f>
         <v>120.91999999999996</v>
       </c>
-      <c r="D15" s="95">
+      <c r="D15" s="92">
         <f t="shared" ref="D15:M15" si="4">D13-D14</f>
         <v>365.24000000000007</v>
       </c>
-      <c r="E15" s="95">
+      <c r="E15" s="92">
         <f t="shared" si="4"/>
         <v>529.99</v>
       </c>
-      <c r="F15" s="95">
+      <c r="F15" s="92">
         <f t="shared" si="4"/>
         <v>478.74</v>
       </c>
-      <c r="G15" s="95">
+      <c r="G15" s="92">
         <f t="shared" si="4"/>
         <v>434.34000000000003</v>
       </c>
-      <c r="H15" s="95">
+      <c r="H15" s="92">
         <f t="shared" si="4"/>
         <v>202.89070400000003</v>
       </c>
-      <c r="I15" s="95">
+      <c r="I15" s="92">
         <f t="shared" si="4"/>
         <v>305.35613120000016</v>
       </c>
-      <c r="J15" s="95">
+      <c r="J15" s="92">
         <f t="shared" si="4"/>
         <v>427.22118656000021</v>
       </c>
-      <c r="K15" s="95">
+      <c r="K15" s="92">
         <f t="shared" si="4"/>
         <v>555.26308352614433</v>
       </c>
-      <c r="L15" s="95">
+      <c r="L15" s="92">
         <f t="shared" si="4"/>
         <v>705.29493721243705</v>
       </c>
-      <c r="M15" s="95">
+      <c r="M15" s="92">
         <f t="shared" si="4"/>
         <v>883.24185517190745</v>
       </c>
     </row>
     <row r="16" spans="2:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="37" t="s">
+      <c r="B16" s="35" t="s">
         <v>178</v>
       </c>
-      <c r="C16" s="86">
+      <c r="C16" s="83">
         <f>'Data Sheet'!H32</f>
         <v>47.74</v>
       </c>
-      <c r="D16" s="86">
+      <c r="D16" s="83">
         <f>'Data Sheet'!I32</f>
         <v>105.41</v>
       </c>
-      <c r="E16" s="86">
+      <c r="E16" s="83">
         <f>'Data Sheet'!J32</f>
         <v>144.13999999999999</v>
       </c>
-      <c r="F16" s="86">
+      <c r="F16" s="83">
         <f>'Data Sheet'!K32</f>
         <v>134.22999999999999</v>
       </c>
-      <c r="G16" s="86">
+      <c r="G16" s="83">
         <f>'Data Sheet'!L32</f>
         <v>131.03</v>
       </c>
-      <c r="H16" s="86">
+      <c r="H16" s="83">
         <f>MAX(0,H15*Assumptions!D73)</f>
         <v>51.12845740800001</v>
       </c>
-      <c r="I16" s="86">
+      <c r="I16" s="83">
         <f>MAX(0,I15*Assumptions!E73)</f>
         <v>76.949745062400041</v>
       </c>
-      <c r="J16" s="86">
+      <c r="J16" s="83">
         <f>MAX(0,J15*Assumptions!F73)</f>
         <v>107.65973901312005</v>
       </c>
-      <c r="K16" s="86">
+      <c r="K16" s="83">
         <f>MAX(0,K15*Assumptions!G73)</f>
         <v>139.92629704858837</v>
       </c>
-      <c r="L16" s="86">
+      <c r="L16" s="83">
         <f>MAX(0,L15*Assumptions!H73)</f>
         <v>177.73432417753415</v>
       </c>
-      <c r="M16" s="86">
+      <c r="M16" s="83">
         <f>MAX(0,M15*Assumptions!I73)</f>
         <v>222.57694750332067</v>
       </c>
     </row>
     <row r="17" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="45" t="s">
+      <c r="B17" s="43" t="s">
         <v>64</v>
       </c>
-      <c r="C17" s="95">
+      <c r="C17" s="92">
         <f>C15-C16</f>
         <v>73.17999999999995</v>
       </c>
-      <c r="D17" s="95">
+      <c r="D17" s="92">
         <f t="shared" ref="D17:M17" si="5">D15-D16</f>
         <v>259.83000000000004</v>
       </c>
-      <c r="E17" s="95">
+      <c r="E17" s="92">
         <f t="shared" si="5"/>
         <v>385.85</v>
       </c>
-      <c r="F17" s="95">
+      <c r="F17" s="92">
         <f t="shared" si="5"/>
         <v>344.51</v>
       </c>
-      <c r="G17" s="95">
+      <c r="G17" s="92">
         <f t="shared" si="5"/>
         <v>303.31000000000006</v>
       </c>
-      <c r="H17" s="95">
+      <c r="H17" s="92">
         <f t="shared" si="5"/>
         <v>151.76224659200003</v>
       </c>
-      <c r="I17" s="95">
+      <c r="I17" s="92">
         <f t="shared" si="5"/>
         <v>228.40638613760012</v>
       </c>
-      <c r="J17" s="95">
+      <c r="J17" s="92">
         <f t="shared" si="5"/>
         <v>319.56144754688017</v>
       </c>
-      <c r="K17" s="95">
+      <c r="K17" s="92">
         <f t="shared" si="5"/>
         <v>415.33678647755596</v>
       </c>
-      <c r="L17" s="95">
+      <c r="L17" s="92">
         <f t="shared" si="5"/>
         <v>527.56061303490287</v>
       </c>
-      <c r="M17" s="95">
+      <c r="M17" s="92">
         <f t="shared" si="5"/>
         <v>660.66490766858681</v>
       </c>
     </row>
     <row r="18" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="110" t="s">
+      <c r="B18" s="107" t="s">
         <v>179</v>
       </c>
-      <c r="C18" s="99">
+      <c r="C18" s="96">
         <f>IFERROR(C17/C8,"")</f>
         <v>0.13491639165944572</v>
       </c>
-      <c r="D18" s="99">
+      <c r="D18" s="96">
         <f t="shared" ref="D18:M18" si="6">IFERROR(D17/D8,"")</f>
         <v>0.25757620817843868</v>
       </c>
-      <c r="E18" s="99">
+      <c r="E18" s="96">
         <f t="shared" si="6"/>
         <v>0.2909967118163444</v>
       </c>
-      <c r="F18" s="99">
+      <c r="F18" s="96">
         <f t="shared" si="6"/>
         <v>0.25192134724649551</v>
       </c>
-      <c r="G18" s="99">
+      <c r="G18" s="96">
         <f t="shared" si="6"/>
         <v>0.21876262189140849</v>
       </c>
-      <c r="H18" s="99">
+      <c r="H18" s="96">
         <f t="shared" si="6"/>
         <v>0.10326288929315232</v>
       </c>
-      <c r="I18" s="99">
+      <c r="I18" s="96">
         <f t="shared" si="6"/>
         <v>0.14128500871488875</v>
       </c>
-      <c r="J18" s="99">
+      <c r="J18" s="96">
         <f t="shared" si="6"/>
         <v>0.17649166386331402</v>
       </c>
-      <c r="K18" s="99">
+      <c r="K18" s="96">
         <f t="shared" si="6"/>
         <v>0.20481048847172723</v>
       </c>
-      <c r="L18" s="99">
+      <c r="L18" s="96">
         <f t="shared" si="6"/>
         <v>0.23227696167300849</v>
       </c>
-      <c r="M18" s="99">
+      <c r="M18" s="96">
         <f t="shared" si="6"/>
         <v>0.26205474791163896</v>
       </c>
     </row>
     <row r="20" spans="2:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="32" t="s">
+      <c r="B20" s="30" t="s">
         <v>180</v>
       </c>
-      <c r="C20" s="32"/>
-      <c r="D20" s="32"/>
-      <c r="E20" s="32"/>
-      <c r="F20" s="32"/>
-      <c r="G20" s="32"/>
-      <c r="H20" s="32"/>
-      <c r="I20" s="32"/>
-      <c r="J20" s="32"/>
-      <c r="K20" s="32"/>
-      <c r="L20" s="32"/>
-      <c r="M20" s="32"/>
+      <c r="C20" s="30"/>
+      <c r="D20" s="30"/>
+      <c r="E20" s="30"/>
+      <c r="F20" s="30"/>
+      <c r="G20" s="30"/>
+      <c r="H20" s="30"/>
+      <c r="I20" s="30"/>
+      <c r="J20" s="30"/>
+      <c r="K20" s="30"/>
+      <c r="L20" s="30"/>
+      <c r="M20" s="30"/>
     </row>
     <row r="21" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="45" t="s">
+      <c r="B21" s="43" t="s">
         <v>96</v>
       </c>
-      <c r="C21" s="95">
+      <c r="C21" s="92">
         <f>C10</f>
         <v>235.03999999999996</v>
       </c>
-      <c r="D21" s="95">
+      <c r="D21" s="92">
         <f t="shared" ref="D21:M21" si="7">D10</f>
         <v>480.34000000000003</v>
       </c>
-      <c r="E21" s="95">
+      <c r="E21" s="92">
         <f t="shared" si="7"/>
         <v>657.80000000000007</v>
       </c>
-      <c r="F21" s="95">
+      <c r="F21" s="92">
         <f t="shared" si="7"/>
         <v>658.09</v>
       </c>
-      <c r="G21" s="95">
+      <c r="G21" s="92">
         <f t="shared" si="7"/>
         <v>642.61</v>
       </c>
-      <c r="H21" s="95">
+      <c r="H21" s="92">
         <f t="shared" si="7"/>
         <v>646.65427200000011</v>
       </c>
-      <c r="I21" s="95">
+      <c r="I21" s="92">
         <f t="shared" si="7"/>
         <v>724.25278464000019</v>
       </c>
-      <c r="J21" s="95">
+      <c r="J21" s="92">
         <f t="shared" si="7"/>
         <v>823.83754252800031</v>
       </c>
-      <c r="K21" s="95">
+      <c r="K21" s="92">
         <f t="shared" si="7"/>
         <v>932.83758661632044</v>
       </c>
-      <c r="L21" s="95">
+      <c r="L21" s="92">
         <f t="shared" si="7"/>
         <v>1049.3206104755411</v>
       </c>
-      <c r="M21" s="95">
+      <c r="M21" s="92">
         <f t="shared" si="7"/>
         <v>1172.3091625475122</v>
       </c>
     </row>
     <row r="22" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="37" t="s">
+      <c r="B22" s="35" t="s">
         <v>181</v>
       </c>
-      <c r="C22" s="86">
+      <c r="C22" s="83">
         <f t="shared" ref="C22:M22" si="8">C14</f>
         <v>25.07</v>
       </c>
-      <c r="D22" s="86">
+      <c r="D22" s="83">
         <f t="shared" si="8"/>
         <v>27.07</v>
       </c>
-      <c r="E22" s="86">
+      <c r="E22" s="83">
         <f t="shared" si="8"/>
         <v>30.35</v>
       </c>
-      <c r="F22" s="86">
+      <c r="F22" s="83">
         <f t="shared" si="8"/>
         <v>44.5</v>
       </c>
-      <c r="G22" s="86">
+      <c r="G22" s="83">
         <f t="shared" si="8"/>
         <v>55.21</v>
       </c>
-      <c r="H22" s="86">
+      <c r="H22" s="83">
         <f t="shared" si="8"/>
         <v>282.10000000000002</v>
       </c>
-      <c r="I22" s="86">
+      <c r="I22" s="83">
         <f t="shared" si="8"/>
         <v>244.29999999999998</v>
       </c>
-      <c r="J22" s="86">
+      <c r="J22" s="83">
         <f t="shared" si="8"/>
         <v>206.5</v>
       </c>
-      <c r="K22" s="86">
+      <c r="K22" s="83">
         <f t="shared" si="8"/>
         <v>168.7</v>
       </c>
-      <c r="L22" s="86">
+      <c r="L22" s="83">
         <f t="shared" si="8"/>
         <v>116.9</v>
       </c>
-      <c r="M22" s="86">
+      <c r="M22" s="83">
         <f t="shared" si="8"/>
         <v>42</v>
       </c>
     </row>
     <row r="23" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="37" t="s">
+      <c r="B23" s="35" t="s">
         <v>182</v>
       </c>
-      <c r="C23" s="86">
+      <c r="C23" s="83">
         <f t="shared" ref="C23:L23" si="9">C16</f>
         <v>47.74</v>
       </c>
-      <c r="D23" s="86">
+      <c r="D23" s="83">
         <f t="shared" si="9"/>
         <v>105.41</v>
       </c>
-      <c r="E23" s="86">
+      <c r="E23" s="83">
         <f t="shared" si="9"/>
         <v>144.13999999999999</v>
       </c>
-      <c r="F23" s="86">
+      <c r="F23" s="83">
         <f t="shared" si="9"/>
         <v>134.22999999999999</v>
       </c>
-      <c r="G23" s="86">
+      <c r="G23" s="83">
         <f t="shared" si="9"/>
         <v>131.03</v>
       </c>
-      <c r="H23" s="86">
+      <c r="H23" s="83">
         <f>H16</f>
         <v>51.12845740800001</v>
       </c>
-      <c r="I23" s="86">
+      <c r="I23" s="83">
         <f t="shared" si="9"/>
         <v>76.949745062400041</v>
       </c>
-      <c r="J23" s="86">
+      <c r="J23" s="83">
         <f t="shared" si="9"/>
         <v>107.65973901312005</v>
       </c>
-      <c r="K23" s="86">
+      <c r="K23" s="83">
         <f t="shared" si="9"/>
         <v>139.92629704858837</v>
       </c>
-      <c r="L23" s="86">
+      <c r="L23" s="83">
         <f t="shared" si="9"/>
         <v>177.73432417753415</v>
       </c>
-      <c r="M23" s="86">
+      <c r="M23" s="83">
         <f>M16</f>
         <v>222.57694750332067</v>
       </c>
     </row>
     <row r="24" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="37" t="s">
+      <c r="B24" s="35" t="s">
         <v>183</v>
       </c>
-      <c r="C24" s="59">
+      <c r="C24" s="57">
         <v>23</v>
       </c>
-      <c r="D24" s="59">
+      <c r="D24" s="57">
         <v>111</v>
       </c>
-      <c r="E24" s="59">
+      <c r="E24" s="57">
         <v>104</v>
       </c>
-      <c r="F24" s="59">
+      <c r="F24" s="57">
         <v>256</v>
       </c>
-      <c r="G24" s="86">
+      <c r="G24" s="83">
         <f>Assumptions!D16</f>
         <v>114</v>
       </c>
-      <c r="H24" s="86">
+      <c r="H24" s="83">
         <f>H8*Assumptions!D69</f>
         <v>124.92184800000003</v>
       </c>
-      <c r="I24" s="86">
+      <c r="I24" s="83">
         <f>I8*Assumptions!E69</f>
         <v>129.33085440000002</v>
       </c>
-      <c r="J24" s="86">
+      <c r="J24" s="83">
         <f>J8*Assumptions!F69</f>
         <v>135.79739712000003</v>
       </c>
-      <c r="K24" s="86">
+      <c r="K24" s="83">
         <f>K8*Assumptions!G69</f>
         <v>141.95354578944008</v>
       </c>
-      <c r="L24" s="86">
+      <c r="L24" s="83">
         <f>L8*Assumptions!H69</f>
         <v>147.6316876210177</v>
       </c>
-      <c r="M24" s="86">
+      <c r="M24" s="83">
         <f>M8*Assumptions!I69</f>
         <v>151.26569839322738</v>
       </c>
     </row>
     <row r="25" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="37" t="s">
+      <c r="B25" s="35" t="s">
         <v>184</v>
       </c>
-      <c r="C25" s="59">
+      <c r="C25" s="57">
         <v>-39</v>
       </c>
-      <c r="D25" s="59">
+      <c r="D25" s="57">
         <v>51</v>
       </c>
-      <c r="E25" s="59">
+      <c r="E25" s="57">
         <v>93</v>
       </c>
-      <c r="F25" s="59">
+      <c r="F25" s="57">
         <v>53</v>
       </c>
-      <c r="G25" s="86">
+      <c r="G25" s="83">
         <f>Assumptions!D17</f>
         <v>104</v>
       </c>
-      <c r="H25" s="86">
+      <c r="H25" s="83">
         <f>H8*Assumptions!D71</f>
         <v>80.831784000000013</v>
       </c>
-      <c r="I25" s="86">
+      <c r="I25" s="83">
         <f>I8*Assumptions!E71</f>
         <v>72.748605600000005</v>
       </c>
-      <c r="J25" s="86">
+      <c r="J25" s="83">
         <f>J8*Assumptions!F71</f>
         <v>63.372118656000026</v>
       </c>
-      <c r="K25" s="86">
+      <c r="K25" s="83">
         <f>K8*Assumptions!G71</f>
         <v>60.837233909760023</v>
       </c>
-      <c r="L25" s="86">
+      <c r="L25" s="83">
         <f>L8*Assumptions!H71</f>
         <v>63.595188513669157</v>
       </c>
-      <c r="M25" s="86">
+      <c r="M25" s="83">
         <f>M8*Assumptions!I71</f>
         <v>63.027374330511407</v>
       </c>
     </row>
     <row r="26" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="37" t="s">
+      <c r="B26" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="C26" s="59">
+      <c r="C26" s="57">
         <v>0</v>
       </c>
-      <c r="D26" s="59">
+      <c r="D26" s="57">
         <v>0</v>
       </c>
-      <c r="E26" s="59">
+      <c r="E26" s="57">
         <v>0</v>
       </c>
-      <c r="F26" s="59">
+      <c r="F26" s="57">
         <v>0</v>
       </c>
-      <c r="G26" s="59">
+      <c r="G26" s="57">
         <v>0</v>
       </c>
-      <c r="H26" s="86">
+      <c r="H26" s="83">
         <f>'Debt Schedule'!C29</f>
         <v>360</v>
       </c>
-      <c r="I26" s="86">
+      <c r="I26" s="83">
         <f>'Debt Schedule'!D29</f>
         <v>360</v>
       </c>
-      <c r="J26" s="86">
+      <c r="J26" s="83">
         <f>'Debt Schedule'!E29</f>
         <v>360</v>
       </c>
-      <c r="K26" s="86">
+      <c r="K26" s="83">
         <f>'Debt Schedule'!F29</f>
         <v>360</v>
       </c>
-      <c r="L26" s="86">
+      <c r="L26" s="83">
         <f>'Debt Schedule'!G29</f>
         <v>560</v>
       </c>
-      <c r="M26" s="86">
+      <c r="M26" s="83">
         <f>'Debt Schedule'!H29</f>
         <v>700</v>
       </c>
     </row>
     <row r="27" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="62" t="s">
+      <c r="B27" s="60" t="s">
         <v>186</v>
       </c>
-      <c r="C27" s="112">
+      <c r="C27" s="109">
         <f t="shared" ref="C27:L27" si="10">C21-C22-C23-C24-C25-C26</f>
         <v>178.22999999999996</v>
       </c>
-      <c r="D27" s="112">
+      <c r="D27" s="109">
         <f t="shared" si="10"/>
         <v>185.86</v>
       </c>
-      <c r="E27" s="112">
+      <c r="E27" s="109">
         <f t="shared" si="10"/>
         <v>286.31000000000006</v>
       </c>
-      <c r="F27" s="112">
+      <c r="F27" s="109">
         <f t="shared" si="10"/>
         <v>170.36</v>
       </c>
-      <c r="G27" s="112">
+      <c r="G27" s="109">
         <f t="shared" si="10"/>
         <v>238.37</v>
       </c>
-      <c r="H27" s="112">
+      <c r="H27" s="109">
         <f>H21-H22-H23-H24-H25-H26</f>
         <v>-252.32781740799999</v>
       </c>
-      <c r="I27" s="112">
+      <c r="I27" s="109">
         <f>I21-I22-I23-I24-I25-I26</f>
         <v>-159.07642042239985</v>
       </c>
-      <c r="J27" s="112">
+      <c r="J27" s="109">
         <f>J21-J22-J23-J24-J25-J26</f>
         <v>-49.491712261119801</v>
       </c>
-      <c r="K27" s="112">
+      <c r="K27" s="109">
         <f>K21-K22-K23-K24-K25-K26</f>
         <v>61.420509868532008</v>
       </c>
-      <c r="L27" s="112">
+      <c r="L27" s="109">
         <f t="shared" si="10"/>
         <v>-16.540589836679942</v>
       </c>
-      <c r="M27" s="112">
+      <c r="M27" s="109">
         <f>M21-M22-M23-M24-M25-M26</f>
         <v>-6.5608576795472118</v>
       </c>
     </row>
     <row r="29" spans="2:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="32" t="s">
+      <c r="B29" s="30" t="s">
         <v>187</v>
       </c>
-      <c r="C29" s="32"/>
-      <c r="D29" s="32"/>
-      <c r="E29" s="32"/>
-      <c r="F29" s="32"/>
-      <c r="G29" s="32"/>
-      <c r="H29" s="32"/>
-      <c r="I29" s="32"/>
-      <c r="J29" s="32"/>
-      <c r="K29" s="32"/>
-      <c r="L29" s="32"/>
-      <c r="M29" s="32"/>
+      <c r="C29" s="30"/>
+      <c r="D29" s="30"/>
+      <c r="E29" s="30"/>
+      <c r="F29" s="30"/>
+      <c r="G29" s="30"/>
+      <c r="H29" s="30"/>
+      <c r="I29" s="30"/>
+      <c r="J29" s="30"/>
+      <c r="K29" s="30"/>
+      <c r="L29" s="30"/>
+      <c r="M29" s="30"/>
     </row>
     <row r="30" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="35" t="s">
+      <c r="B30" s="33" t="s">
         <v>188</v>
       </c>
-      <c r="C30" s="81" t="s">
+      <c r="C30" s="79" t="s">
         <v>166</v>
       </c>
-      <c r="D30" s="81" t="s">
+      <c r="D30" s="79" t="s">
         <v>167</v>
       </c>
-      <c r="E30" s="81" t="s">
+      <c r="E30" s="79" t="s">
         <v>168</v>
       </c>
-      <c r="F30" s="81" t="s">
+      <c r="F30" s="79" t="s">
         <v>169</v>
       </c>
-      <c r="G30" s="81" t="s">
+      <c r="G30" s="79" t="s">
         <v>170</v>
       </c>
-      <c r="H30" s="108" t="s">
+      <c r="H30" s="105" t="s">
         <v>145</v>
       </c>
-      <c r="I30" s="108" t="s">
+      <c r="I30" s="105" t="s">
         <v>146</v>
       </c>
-      <c r="J30" s="108" t="s">
+      <c r="J30" s="105" t="s">
         <v>147</v>
       </c>
-      <c r="K30" s="108" t="s">
+      <c r="K30" s="105" t="s">
         <v>148</v>
       </c>
-      <c r="L30" s="108" t="s">
+      <c r="L30" s="105" t="s">
         <v>149</v>
       </c>
-      <c r="M30" s="108" t="s">
+      <c r="M30" s="105" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="31" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="111" t="s">
+      <c r="B31" s="108" t="s">
         <v>97</v>
       </c>
-      <c r="C31" s="99">
+      <c r="C31" s="96">
         <f t="shared" ref="C31:M31" si="11">IFERROR(C10/C8,"")</f>
         <v>0.43332534429674963</v>
       </c>
-      <c r="D31" s="99">
+      <c r="D31" s="96">
         <f t="shared" si="11"/>
         <v>0.4761734820322181</v>
       </c>
-      <c r="E31" s="99">
+      <c r="E31" s="96">
         <f t="shared" si="11"/>
         <v>0.49609339648254852</v>
       </c>
-      <c r="F31" s="99">
+      <c r="F31" s="96">
         <f t="shared" si="11"/>
         <v>0.48122527476545307</v>
       </c>
-      <c r="G31" s="99">
+      <c r="G31" s="96">
         <f t="shared" si="11"/>
         <v>0.46348306502798453</v>
       </c>
-      <c r="H31" s="99">
+      <c r="H31" s="96">
         <f t="shared" si="11"/>
         <v>0.44</v>
       </c>
-      <c r="I31" s="99">
+      <c r="I31" s="96">
         <f t="shared" si="11"/>
         <v>0.44800000000000001</v>
       </c>
-      <c r="J31" s="99">
+      <c r="J31" s="96">
         <f t="shared" si="11"/>
         <v>0.45500000000000002</v>
       </c>
-      <c r="K31" s="99">
+      <c r="K31" s="96">
         <f t="shared" si="11"/>
         <v>0.46</v>
       </c>
-      <c r="L31" s="99">
+      <c r="L31" s="96">
         <f t="shared" si="11"/>
         <v>0.46200000000000002</v>
       </c>
-      <c r="M31" s="99">
+      <c r="M31" s="96">
         <f t="shared" si="11"/>
         <v>0.46500000000000002</v>
       </c>
     </row>
     <row r="32" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="111" t="s">
+      <c r="B32" s="108" t="s">
         <v>189</v>
       </c>
-      <c r="C32" s="99">
+      <c r="C32" s="96">
         <f t="shared" ref="C32:M32" si="12">IFERROR(C17/C8,"")</f>
         <v>0.13491639165944572</v>
       </c>
-      <c r="D32" s="99">
+      <c r="D32" s="96">
         <f t="shared" si="12"/>
         <v>0.25757620817843868</v>
       </c>
-      <c r="E32" s="99">
+      <c r="E32" s="96">
         <f t="shared" si="12"/>
         <v>0.2909967118163444</v>
       </c>
-      <c r="F32" s="99">
+      <c r="F32" s="96">
         <f t="shared" si="12"/>
         <v>0.25192134724649551</v>
       </c>
-      <c r="G32" s="99">
+      <c r="G32" s="96">
         <f t="shared" si="12"/>
         <v>0.21876262189140849</v>
       </c>
-      <c r="H32" s="99">
+      <c r="H32" s="96">
         <f t="shared" si="12"/>
         <v>0.10326288929315232</v>
       </c>
-      <c r="I32" s="99">
+      <c r="I32" s="96">
         <f t="shared" si="12"/>
         <v>0.14128500871488875</v>
       </c>
-      <c r="J32" s="99">
+      <c r="J32" s="96">
         <f t="shared" si="12"/>
         <v>0.17649166386331402</v>
       </c>
-      <c r="K32" s="99">
+      <c r="K32" s="96">
         <f t="shared" si="12"/>
         <v>0.20481048847172723</v>
       </c>
-      <c r="L32" s="99">
+      <c r="L32" s="96">
         <f t="shared" si="12"/>
         <v>0.23227696167300849</v>
       </c>
-      <c r="M32" s="99">
+      <c r="M32" s="96">
         <f t="shared" si="12"/>
         <v>0.26205474791163896</v>
       </c>
     </row>
     <row r="33" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="111" t="s">
+      <c r="B33" s="108" t="s">
         <v>190</v>
       </c>
-      <c r="C33" s="99">
+      <c r="C33" s="96">
         <f>IFERROR(C24/C8,"")</f>
         <v>4.2403348020869827E-2</v>
       </c>
-      <c r="D33" s="99">
+      <c r="D33" s="96">
         <f t="shared" ref="D33:M33" si="13">IFERROR(D24/D8,"")</f>
         <v>0.1100371747211896</v>
       </c>
-      <c r="E33" s="99">
+      <c r="E33" s="96">
         <f t="shared" si="13"/>
         <v>7.8433738574315959E-2</v>
       </c>
-      <c r="F33" s="99">
+      <c r="F33" s="96">
         <f t="shared" si="13"/>
         <v>0.18719881830745944</v>
       </c>
-      <c r="G33" s="99">
+      <c r="G33" s="96">
         <f t="shared" si="13"/>
         <v>8.2222606889388955E-2</v>
       </c>
-      <c r="H33" s="99">
+      <c r="H33" s="96">
         <f t="shared" si="13"/>
         <v>8.5000000000000006E-2</v>
       </c>
-      <c r="I33" s="99">
+      <c r="I33" s="96">
         <f t="shared" si="13"/>
         <v>0.08</v>
       </c>
-      <c r="J33" s="99">
+      <c r="J33" s="96">
         <f t="shared" si="13"/>
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="K33" s="99">
+      <c r="K33" s="96">
         <f t="shared" si="13"/>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="L33" s="99">
+      <c r="L33" s="96">
         <f t="shared" si="13"/>
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="M33" s="99">
+      <c r="M33" s="96">
         <f t="shared" si="13"/>
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
     <row r="34" spans="2:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="111" t="s">
+      <c r="B34" s="108" t="s">
         <v>191</v>
       </c>
-      <c r="C34" s="99">
+      <c r="C34" s="96">
         <f t="shared" ref="C34:M34" si="14">IFERROR(C27/C10,"")</f>
         <v>0.75829646017699115</v>
       </c>
-      <c r="D34" s="99">
+      <c r="D34" s="96">
         <f t="shared" si="14"/>
         <v>0.38693425490277722</v>
       </c>
-      <c r="E34" s="99">
+      <c r="E34" s="96">
         <f t="shared" si="14"/>
         <v>0.43525387655822445</v>
       </c>
-      <c r="F34" s="99">
+      <c r="F34" s="96">
         <f t="shared" si="14"/>
         <v>0.2588703672749928</v>
       </c>
-      <c r="G34" s="99">
+      <c r="G34" s="96">
         <f t="shared" si="14"/>
         <v>0.37094038374752958</v>
       </c>
-      <c r="H34" s="99">
+      <c r="H34" s="96">
         <f t="shared" si="14"/>
         <v>-0.39020513485140934</v>
       </c>
-      <c r="I34" s="99">
+      <c r="I34" s="96">
         <f t="shared" si="14"/>
         <v>-0.21964212467815497</v>
       </c>
-      <c r="J34" s="99">
+      <c r="J34" s="96">
         <f t="shared" si="14"/>
         <v>-6.0074601734282695E-2</v>
       </c>
-      <c r="K34" s="99">
+      <c r="K34" s="96">
         <f t="shared" si="14"/>
         <v>6.5842661948606163E-2</v>
       </c>
-      <c r="L34" s="99">
+      <c r="L34" s="96">
         <f t="shared" si="14"/>
         <v>-1.5763142047866496E-2</v>
       </c>
-      <c r="M34" s="99">
+      <c r="M34" s="96">
         <f t="shared" si="14"/>
         <v>-5.5965251225111945E-3</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="8dVxxy7H6ghVTq/TIqqfti5ZA23DCqeCHM4PBkCdVtYlxZQgCRV9uB/7yRI8aCRaAAUTHDHn5lYAxAfDQJia2A==" saltValue="T3KPf0wDnMqxFhhmMNX+0A==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="lZoYesOiX4l4ZdhNP1rNz/XvHFTqZUqJzEPd18/XYeL2BTWF6xhmbL+5O3COpfPi53J8vpHlInGX2hiLsKraRw==" saltValue="S1kGddJHXTY/DQJldW8Nag==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.75" right="0.75" top="1.1299999999999999" bottom="1.58" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="71" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <colBreaks count="1" manualBreakCount="1">
@@ -7893,7 +8347,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <sheetPr>
+  <sheetPr codeName="Sheet5">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B2:I29"/>
@@ -7915,7 +8369,7 @@
       <c r="H2" s="3"/>
     </row>
     <row r="3" spans="2:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="56" t="s">
+      <c r="B3" s="54" t="s">
         <v>192</v>
       </c>
       <c r="C3" s="1"/>
@@ -7935,528 +8389,528 @@
       <c r="H4" s="3"/>
     </row>
     <row r="6" spans="2:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="57" t="s">
+      <c r="B6" s="55" t="s">
         <v>193</v>
       </c>
-      <c r="C6" s="108" t="s">
+      <c r="C6" s="105" t="s">
         <v>145</v>
       </c>
-      <c r="D6" s="108" t="s">
+      <c r="D6" s="105" t="s">
         <v>146</v>
       </c>
-      <c r="E6" s="108" t="s">
+      <c r="E6" s="105" t="s">
         <v>147</v>
       </c>
-      <c r="F6" s="108" t="s">
+      <c r="F6" s="105" t="s">
         <v>148</v>
       </c>
-      <c r="G6" s="108" t="s">
+      <c r="G6" s="105" t="s">
         <v>149</v>
       </c>
-      <c r="H6" s="108" t="s">
+      <c r="H6" s="105" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="7" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="32" t="s">
+      <c r="B7" s="30" t="s">
         <v>194</v>
       </c>
-      <c r="C7" s="32"/>
-      <c r="D7" s="32"/>
-      <c r="E7" s="32"/>
-      <c r="F7" s="32"/>
-      <c r="G7" s="32"/>
-      <c r="H7" s="32"/>
+      <c r="C7" s="30"/>
+      <c r="D7" s="30"/>
+      <c r="E7" s="30"/>
+      <c r="F7" s="30"/>
+      <c r="G7" s="30"/>
+      <c r="H7" s="30"/>
     </row>
     <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="37" t="s">
+      <c r="B8" s="35" t="s">
         <v>195</v>
       </c>
-      <c r="C8" s="86">
+      <c r="C8" s="83">
         <f>Assumptions!E39</f>
         <v>1800</v>
       </c>
-      <c r="D8" s="87">
+      <c r="D8" s="84">
         <f>MAX(0,C11)</f>
         <v>1440</v>
       </c>
-      <c r="E8" s="87">
+      <c r="E8" s="84">
         <f>MAX(0,D11)</f>
         <v>1080</v>
       </c>
-      <c r="F8" s="87">
+      <c r="F8" s="84">
         <f>MAX(0,E11)</f>
         <v>720</v>
       </c>
-      <c r="G8" s="87">
+      <c r="G8" s="84">
         <f>MAX(0,F11)</f>
         <v>360</v>
       </c>
-      <c r="H8" s="87">
+      <c r="H8" s="84">
         <f>MAX(0,G11)</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="37" t="s">
+      <c r="B9" s="35" t="s">
         <v>196</v>
       </c>
-      <c r="C9" s="87">
+      <c r="C9" s="84">
         <f>IFERROR($C$8*0.2,0)</f>
         <v>360</v>
       </c>
-      <c r="D9" s="87">
+      <c r="D9" s="84">
         <f t="shared" ref="D9:G9" si="0">IFERROR($C$8*0.2,0)</f>
         <v>360</v>
       </c>
-      <c r="E9" s="87">
+      <c r="E9" s="84">
         <f t="shared" si="0"/>
         <v>360</v>
       </c>
-      <c r="F9" s="87">
+      <c r="F9" s="84">
         <f t="shared" si="0"/>
         <v>360</v>
       </c>
-      <c r="G9" s="87">
+      <c r="G9" s="84">
         <f t="shared" si="0"/>
         <v>360</v>
       </c>
-      <c r="H9" s="60">
+      <c r="H9" s="58">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="37" t="s">
+      <c r="B10" s="35" t="s">
         <v>198</v>
       </c>
-      <c r="C10" s="87">
+      <c r="C10" s="84">
         <f t="shared" ref="C10:G10" si="1">IFERROR((C8+C11)/2*0.105,0)</f>
         <v>170.1</v>
       </c>
-      <c r="D10" s="87">
+      <c r="D10" s="84">
         <f t="shared" si="1"/>
         <v>132.29999999999998</v>
       </c>
-      <c r="E10" s="87">
+      <c r="E10" s="84">
         <f t="shared" si="1"/>
         <v>94.5</v>
       </c>
-      <c r="F10" s="87">
+      <c r="F10" s="84">
         <f t="shared" si="1"/>
         <v>56.699999999999996</v>
       </c>
-      <c r="G10" s="87">
+      <c r="G10" s="84">
         <f t="shared" si="1"/>
         <v>18.899999999999999</v>
       </c>
-      <c r="H10" s="87">
+      <c r="H10" s="84">
         <f>IFERROR((H8+H11)/2*0.105,0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="45" t="s">
+      <c r="B11" s="43" t="s">
         <v>197</v>
       </c>
-      <c r="C11" s="88">
+      <c r="C11" s="85">
         <f>MAX(0,C8-C9)</f>
         <v>1440</v>
       </c>
-      <c r="D11" s="88">
+      <c r="D11" s="85">
         <f t="shared" ref="D11:H11" si="2">MAX(0,D8-D9)</f>
         <v>1080</v>
       </c>
-      <c r="E11" s="88">
+      <c r="E11" s="85">
         <f t="shared" si="2"/>
         <v>720</v>
       </c>
-      <c r="F11" s="88">
+      <c r="F11" s="85">
         <f t="shared" si="2"/>
         <v>360</v>
       </c>
-      <c r="G11" s="88">
+      <c r="G11" s="85">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H11" s="88">
+      <c r="H11" s="85">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="13" spans="2:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="32" t="s">
+      <c r="B13" s="30" t="s">
         <v>266</v>
       </c>
-      <c r="C13" s="32"/>
-      <c r="D13" s="32"/>
-      <c r="E13" s="32"/>
-      <c r="F13" s="32"/>
-      <c r="G13" s="32"/>
-      <c r="H13" s="32"/>
+      <c r="C13" s="30"/>
+      <c r="D13" s="30"/>
+      <c r="E13" s="30"/>
+      <c r="F13" s="30"/>
+      <c r="G13" s="30"/>
+      <c r="H13" s="30"/>
     </row>
     <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="37" t="s">
+      <c r="B14" s="35" t="s">
         <v>195</v>
       </c>
-      <c r="C14" s="86">
+      <c r="C14" s="83">
         <f>Assumptions!E40</f>
         <v>700</v>
       </c>
-      <c r="D14" s="87">
+      <c r="D14" s="84">
         <f>C14</f>
         <v>700</v>
       </c>
-      <c r="E14" s="87">
+      <c r="E14" s="84">
         <f>D14</f>
         <v>700</v>
       </c>
-      <c r="F14" s="87">
+      <c r="F14" s="84">
         <f>E14</f>
         <v>700</v>
       </c>
-      <c r="G14" s="87">
+      <c r="G14" s="84">
         <f>F14</f>
         <v>700</v>
       </c>
-      <c r="H14" s="87">
+      <c r="H14" s="84">
         <f>G14</f>
         <v>700</v>
       </c>
     </row>
     <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="37" t="s">
+      <c r="B15" s="35" t="s">
         <v>254</v>
       </c>
-      <c r="C15" s="59">
+      <c r="C15" s="57">
         <v>0</v>
       </c>
-      <c r="D15" s="59">
+      <c r="D15" s="57">
         <v>0</v>
       </c>
-      <c r="E15" s="59">
+      <c r="E15" s="57">
         <v>0</v>
       </c>
-      <c r="F15" s="59">
+      <c r="F15" s="57">
         <v>0</v>
       </c>
-      <c r="G15" s="59">
+      <c r="G15" s="57">
         <v>0</v>
       </c>
-      <c r="H15" s="59">
+      <c r="H15" s="57">
         <v>700</v>
       </c>
     </row>
     <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="45" t="s">
+      <c r="B16" s="43" t="s">
         <v>197</v>
       </c>
-      <c r="C16" s="88">
+      <c r="C16" s="85">
         <f t="shared" ref="C16:H16" si="3">C14-C15</f>
         <v>700</v>
       </c>
-      <c r="D16" s="88">
+      <c r="D16" s="85">
         <f t="shared" si="3"/>
         <v>700</v>
       </c>
-      <c r="E16" s="88">
+      <c r="E16" s="85">
         <f t="shared" si="3"/>
         <v>700</v>
       </c>
-      <c r="F16" s="88">
+      <c r="F16" s="85">
         <f t="shared" si="3"/>
         <v>700</v>
       </c>
-      <c r="G16" s="88">
+      <c r="G16" s="85">
         <f t="shared" si="3"/>
         <v>700</v>
       </c>
-      <c r="H16" s="88">
+      <c r="H16" s="85">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="37" t="s">
+      <c r="B17" s="35" t="s">
         <v>199</v>
       </c>
-      <c r="C17" s="87">
+      <c r="C17" s="84">
         <f t="shared" ref="C17:F17" si="4">(C14+C16)/2*0.12</f>
         <v>84</v>
       </c>
-      <c r="D17" s="87">
+      <c r="D17" s="84">
         <f t="shared" si="4"/>
         <v>84</v>
       </c>
-      <c r="E17" s="87">
+      <c r="E17" s="84">
         <f t="shared" si="4"/>
         <v>84</v>
       </c>
-      <c r="F17" s="87">
+      <c r="F17" s="84">
         <f t="shared" si="4"/>
         <v>84</v>
       </c>
-      <c r="G17" s="87">
+      <c r="G17" s="84">
         <f>(G14+G16)/2*0.12</f>
         <v>84</v>
       </c>
-      <c r="H17" s="87">
+      <c r="H17" s="84">
         <f>(H14+H16)/2*0.12</f>
         <v>42</v>
       </c>
-      <c r="I17" s="113"/>
+      <c r="I17" s="110"/>
     </row>
     <row r="19" spans="2:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="32" t="s">
+      <c r="B19" s="30" t="s">
         <v>200</v>
       </c>
-      <c r="C19" s="32"/>
-      <c r="D19" s="32"/>
-      <c r="E19" s="32"/>
-      <c r="F19" s="32"/>
-      <c r="G19" s="32"/>
-      <c r="H19" s="32"/>
+      <c r="C19" s="30"/>
+      <c r="D19" s="30"/>
+      <c r="E19" s="30"/>
+      <c r="F19" s="30"/>
+      <c r="G19" s="30"/>
+      <c r="H19" s="30"/>
     </row>
     <row r="20" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="37" t="s">
+      <c r="B20" s="35" t="s">
         <v>195</v>
       </c>
-      <c r="C20" s="86">
+      <c r="C20" s="83">
         <f>Assumptions!E41</f>
         <v>200</v>
       </c>
-      <c r="D20" s="87">
+      <c r="D20" s="84">
         <f>C20</f>
         <v>200</v>
       </c>
-      <c r="E20" s="87">
+      <c r="E20" s="84">
         <f>D20</f>
         <v>200</v>
       </c>
-      <c r="F20" s="87">
+      <c r="F20" s="84">
         <f>E20</f>
         <v>200</v>
       </c>
-      <c r="G20" s="87">
+      <c r="G20" s="84">
         <f>F20</f>
         <v>200</v>
       </c>
-      <c r="H20" s="87">
+      <c r="H20" s="84">
         <f>G22</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="37" t="s">
+      <c r="B21" s="35" t="s">
         <v>267</v>
       </c>
-      <c r="C21" s="59">
+      <c r="C21" s="57">
         <v>0</v>
       </c>
-      <c r="D21" s="59">
+      <c r="D21" s="57">
         <v>0</v>
       </c>
-      <c r="E21" s="59">
+      <c r="E21" s="57">
         <v>0</v>
       </c>
-      <c r="F21" s="59">
+      <c r="F21" s="57">
         <v>0</v>
       </c>
-      <c r="G21" s="89">
+      <c r="G21" s="86">
         <f>Assumptions!E41</f>
         <v>200</v>
       </c>
-      <c r="H21" s="59">
+      <c r="H21" s="57">
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="45" t="s">
+      <c r="B22" s="43" t="s">
         <v>197</v>
       </c>
-      <c r="C22" s="88">
+      <c r="C22" s="85">
         <f>MAX(0,C20-C21)</f>
         <v>200</v>
       </c>
-      <c r="D22" s="88">
+      <c r="D22" s="85">
         <f t="shared" ref="D22:H22" si="5">MAX(0,D20-D21)</f>
         <v>200</v>
       </c>
-      <c r="E22" s="88">
+      <c r="E22" s="85">
         <f t="shared" si="5"/>
         <v>200</v>
       </c>
-      <c r="F22" s="88">
+      <c r="F22" s="85">
         <f t="shared" si="5"/>
         <v>200</v>
       </c>
-      <c r="G22" s="88">
+      <c r="G22" s="85">
         <f>MAX(0,G20-G21)</f>
         <v>0</v>
       </c>
-      <c r="H22" s="88">
+      <c r="H22" s="85">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="37" t="s">
+      <c r="B23" s="35" t="s">
         <v>201</v>
       </c>
-      <c r="C23" s="87">
+      <c r="C23" s="84">
         <f t="shared" ref="C23:H23" si="6">(C20+C22)/2*0.14</f>
         <v>28.000000000000004</v>
       </c>
-      <c r="D23" s="87">
+      <c r="D23" s="84">
         <f t="shared" si="6"/>
         <v>28.000000000000004</v>
       </c>
-      <c r="E23" s="87">
+      <c r="E23" s="84">
         <f t="shared" si="6"/>
         <v>28.000000000000004</v>
       </c>
-      <c r="F23" s="87">
+      <c r="F23" s="84">
         <f t="shared" si="6"/>
         <v>28.000000000000004</v>
       </c>
-      <c r="G23" s="87">
+      <c r="G23" s="84">
         <f>(G20+G22)/2*0.14</f>
         <v>14.000000000000002</v>
       </c>
-      <c r="H23" s="87">
+      <c r="H23" s="84">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="2:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="32" t="s">
+      <c r="B25" s="30" t="s">
         <v>202</v>
       </c>
-      <c r="C25" s="32"/>
-      <c r="D25" s="32"/>
-      <c r="E25" s="32"/>
-      <c r="F25" s="32"/>
-      <c r="G25" s="32"/>
-      <c r="H25" s="32"/>
+      <c r="C25" s="30"/>
+      <c r="D25" s="30"/>
+      <c r="E25" s="30"/>
+      <c r="F25" s="30"/>
+      <c r="G25" s="30"/>
+      <c r="H25" s="30"/>
     </row>
     <row r="26" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="37" t="s">
+      <c r="B26" s="35" t="s">
         <v>203</v>
       </c>
-      <c r="C26" s="88">
+      <c r="C26" s="85">
         <f t="shared" ref="C26:H26" si="7">C10+C17+C23</f>
         <v>282.10000000000002</v>
       </c>
-      <c r="D26" s="88">
+      <c r="D26" s="85">
         <f t="shared" si="7"/>
         <v>244.29999999999998</v>
       </c>
-      <c r="E26" s="88">
+      <c r="E26" s="85">
         <f t="shared" si="7"/>
         <v>206.5</v>
       </c>
-      <c r="F26" s="88">
+      <c r="F26" s="85">
         <f t="shared" si="7"/>
         <v>168.7</v>
       </c>
-      <c r="G26" s="88">
+      <c r="G26" s="85">
         <f t="shared" si="7"/>
         <v>116.9</v>
       </c>
-      <c r="H26" s="88">
+      <c r="H26" s="85">
         <f t="shared" si="7"/>
         <v>42</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="37" t="s">
+      <c r="B27" s="35" t="s">
         <v>204</v>
       </c>
-      <c r="C27" s="87">
+      <c r="C27" s="84">
         <f t="shared" ref="C27:H27" si="8">C11+C16+C22</f>
         <v>2340</v>
       </c>
-      <c r="D27" s="87">
+      <c r="D27" s="84">
         <f t="shared" si="8"/>
         <v>1980</v>
       </c>
-      <c r="E27" s="87">
+      <c r="E27" s="84">
         <f t="shared" si="8"/>
         <v>1620</v>
       </c>
-      <c r="F27" s="87">
+      <c r="F27" s="84">
         <f t="shared" si="8"/>
         <v>1260</v>
       </c>
-      <c r="G27" s="87">
+      <c r="G27" s="84">
         <f t="shared" si="8"/>
         <v>700</v>
       </c>
-      <c r="H27" s="87">
+      <c r="H27" s="84">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="37" t="s">
+      <c r="B28" s="35" t="s">
         <v>205</v>
       </c>
-      <c r="C28" s="90">
+      <c r="C28" s="87">
         <f>IFERROR(C27/Financials!H10,"")</f>
         <v>3.6186260592739106</v>
       </c>
-      <c r="D28" s="90">
+      <c r="D28" s="87">
         <f>IFERROR(D27/Financials!I10,"")</f>
         <v>2.7338521052206741</v>
       </c>
-      <c r="E28" s="90">
+      <c r="E28" s="87">
         <f>IFERROR(E27/Financials!J10,"")</f>
         <v>1.9664071086502348</v>
       </c>
-      <c r="F28" s="90">
+      <c r="F28" s="87">
         <f>IFERROR(F27/Financials!K10,"")</f>
         <v>1.3507174432908466</v>
       </c>
-      <c r="G28" s="90">
+      <c r="G28" s="87">
         <f>IFERROR(G27/Financials!L10,"")</f>
         <v>0.66709830438074336</v>
       </c>
-      <c r="H28" s="90">
+      <c r="H28" s="87">
         <f>IFERROR(H27/Financials!M10,"")</f>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="37" t="s">
+      <c r="B29" s="35" t="s">
         <v>206</v>
       </c>
-      <c r="C29" s="87">
+      <c r="C29" s="84">
         <f>C9+C15+C21</f>
         <v>360</v>
       </c>
-      <c r="D29" s="87">
+      <c r="D29" s="84">
         <f t="shared" ref="D29:H29" si="9">D9+D15+D21</f>
         <v>360</v>
       </c>
-      <c r="E29" s="87">
+      <c r="E29" s="84">
         <f t="shared" si="9"/>
         <v>360</v>
       </c>
-      <c r="F29" s="87">
+      <c r="F29" s="84">
         <f t="shared" si="9"/>
         <v>360</v>
       </c>
-      <c r="G29" s="87">
+      <c r="G29" s="84">
         <f t="shared" si="9"/>
         <v>560</v>
       </c>
-      <c r="H29" s="87">
+      <c r="H29" s="84">
         <f t="shared" si="9"/>
         <v>700</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="pgCRRNNX3LOiQtFFeic77gNuyMpBGLYZnU5GqnB1LzNK+IFKot50Tdkr8wpPuas9aMHXxqCszjRRyJcjWPEhDg==" saltValue="aRsjp9BCEoGR1qAkt5l0Pw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="JiB4wASacRvtzaUOklY44Mf+D/jyXll6Qsy6APAwlv4CS6+yEyshllyJRoJ+utQFkvjlu3sJJDkqOFNd/Ldhcw==" saltValue="oAi8us+UN4Zm6/XUKov1dQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="82" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
@@ -8464,6 +8918,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <sheetPr codeName="Sheet6"/>
   <dimension ref="B2:D45"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -8481,7 +8936,7 @@
       <c r="D2" s="3"/>
     </row>
     <row r="3" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="56" t="s">
+      <c r="B3" s="54" t="s">
         <v>207</v>
       </c>
       <c r="C3" s="1"/>
@@ -8493,311 +8948,797 @@
       <c r="D4" s="3"/>
     </row>
     <row r="6" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="32" t="s">
+      <c r="B6" s="30" t="s">
         <v>208</v>
       </c>
-      <c r="C6" s="32"/>
-      <c r="D6" s="32"/>
+      <c r="C6" s="30"/>
+      <c r="D6" s="30"/>
     </row>
     <row r="7" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="37" t="s">
+      <c r="B7" s="35" t="s">
         <v>209</v>
       </c>
-      <c r="D7" s="114" t="s">
+      <c r="D7" s="111" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="8" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="37" t="s">
+      <c r="B8" s="35" t="s">
         <v>211</v>
       </c>
-      <c r="D8" s="114" t="s">
+      <c r="D8" s="111" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="9" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="37" t="s">
+      <c r="B9" s="35" t="s">
         <v>161</v>
       </c>
-      <c r="D9" s="117">
+      <c r="D9" s="114">
         <f>Assumptions!C77</f>
         <v>6</v>
       </c>
     </row>
     <row r="10" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="37" t="s">
+      <c r="B10" s="35" t="s">
         <v>213</v>
       </c>
-      <c r="D10" s="86">
+      <c r="D10" s="83">
         <f>Assumptions!D31</f>
         <v>11520.7677</v>
       </c>
     </row>
     <row r="11" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="37" t="s">
+      <c r="B11" s="35" t="s">
         <v>214</v>
       </c>
-      <c r="D11" s="86">
+      <c r="D11" s="83">
         <f>Assumptions!E43</f>
         <v>9068.4130540000006</v>
       </c>
     </row>
     <row r="12" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="37" t="s">
+      <c r="B12" s="35" t="s">
         <v>215</v>
       </c>
-      <c r="D12" s="86">
+      <c r="D12" s="83">
         <f>Assumptions!D8</f>
         <v>642.61</v>
       </c>
     </row>
     <row r="13" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="37" t="s">
+      <c r="B13" s="35" t="s">
         <v>125</v>
       </c>
-      <c r="D13" s="97">
+      <c r="D13" s="94">
         <f>Assumptions!D32</f>
         <v>17.928086553274927</v>
       </c>
     </row>
     <row r="15" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="32" t="s">
+      <c r="B15" s="30" t="s">
         <v>216</v>
       </c>
-      <c r="C15" s="32"/>
-      <c r="D15" s="32"/>
+      <c r="C15" s="30"/>
+      <c r="D15" s="30"/>
     </row>
     <row r="16" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="37" t="s">
+      <c r="B16" s="35" t="s">
         <v>217</v>
       </c>
-      <c r="D16" s="94">
+      <c r="D16" s="91">
         <f>Financials!M10</f>
         <v>1172.3091625475122</v>
       </c>
     </row>
     <row r="17" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="37" t="s">
+      <c r="B17" s="35" t="s">
         <v>218</v>
       </c>
-      <c r="D17" s="118">
+      <c r="D17" s="115">
         <f>Assumptions!C78</f>
         <v>22</v>
       </c>
     </row>
     <row r="18" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="45" t="s">
+      <c r="B18" s="43" t="s">
         <v>163</v>
       </c>
-      <c r="C18" s="45"/>
-      <c r="D18" s="105">
+      <c r="C18" s="43"/>
+      <c r="D18" s="102">
         <f>D17*D16</f>
         <v>25790.801576045269</v>
       </c>
     </row>
     <row r="19" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="37" t="s">
+      <c r="B19" s="35" t="s">
         <v>219</v>
       </c>
-      <c r="D19" s="86">
+      <c r="D19" s="83">
         <f>'Debt Schedule'!H27</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="37" t="s">
+      <c r="B20" s="35" t="s">
         <v>164</v>
       </c>
-      <c r="D20" s="94">
+      <c r="D20" s="91">
         <f>D18-D19</f>
         <v>25790.801576045269</v>
       </c>
     </row>
     <row r="21" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="37" t="s">
+      <c r="B21" s="35" t="s">
         <v>220</v>
       </c>
-      <c r="D21" s="87">
+      <c r="D21" s="84">
         <f>D20*0.05</f>
         <v>1289.5400788022635</v>
       </c>
     </row>
     <row r="22" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="45" t="s">
+      <c r="B22" s="43" t="s">
         <v>221</v>
       </c>
-      <c r="C22" s="45"/>
-      <c r="D22" s="119">
+      <c r="C22" s="43"/>
+      <c r="D22" s="116">
         <f>D20-D21</f>
         <v>24501.261497243006</v>
       </c>
     </row>
     <row r="25" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="32" t="s">
+      <c r="B25" s="30" t="s">
         <v>222</v>
       </c>
-      <c r="C25" s="32"/>
-      <c r="D25" s="32"/>
+      <c r="C25" s="30"/>
+      <c r="D25" s="30"/>
     </row>
     <row r="26" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="35" t="s">
+      <c r="B26" s="33" t="s">
         <v>223</v>
       </c>
-      <c r="C26" s="35"/>
-      <c r="D26" s="81" t="s">
+      <c r="C26" s="33"/>
+      <c r="D26" s="79" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="27" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="115" t="s">
+      <c r="B27" s="112" t="s">
         <v>225</v>
       </c>
-      <c r="D27" s="88">
+      <c r="D27" s="85">
         <f>-Assumptions!E43</f>
         <v>-9068.4130540000006</v>
       </c>
     </row>
     <row r="28" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="37" t="s">
+      <c r="B28" s="35" t="s">
         <v>226</v>
       </c>
-      <c r="D28" s="120">
+      <c r="D28" s="117">
         <f>Financials!H27</f>
         <v>-252.32781740799999</v>
       </c>
     </row>
     <row r="29" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="37" t="s">
+      <c r="B29" s="35" t="s">
         <v>227</v>
       </c>
-      <c r="D29" s="120">
+      <c r="D29" s="117">
         <f>Financials!I27</f>
         <v>-159.07642042239985</v>
       </c>
     </row>
     <row r="30" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="37" t="s">
+      <c r="B30" s="35" t="s">
         <v>228</v>
       </c>
-      <c r="D30" s="120">
+      <c r="D30" s="117">
         <f>Financials!J27</f>
         <v>-49.491712261119801</v>
       </c>
     </row>
     <row r="31" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="37" t="s">
+      <c r="B31" s="35" t="s">
         <v>229</v>
       </c>
-      <c r="D31" s="120">
+      <c r="D31" s="117">
         <f>Financials!K27</f>
         <v>61.420509868532008</v>
       </c>
     </row>
     <row r="32" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="115" t="s">
+      <c r="B32" s="112" t="s">
         <v>230</v>
       </c>
-      <c r="D32" s="105">
+      <c r="D32" s="102">
         <f>Financials!L27</f>
         <v>-16.540589836679942</v>
       </c>
     </row>
     <row r="33" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="37" t="s">
+      <c r="B33" s="35" t="s">
         <v>231</v>
       </c>
-      <c r="D33" s="120">
+      <c r="D33" s="117">
         <f>Financials!M27+D22</f>
         <v>24494.70063956346</v>
       </c>
     </row>
     <row r="35" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="32" t="s">
+      <c r="B35" s="30" t="s">
         <v>232</v>
       </c>
-      <c r="C35" s="32"/>
-      <c r="D35" s="32"/>
+      <c r="C35" s="30"/>
+      <c r="D35" s="30"/>
     </row>
     <row r="36" spans="2:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="62" t="s">
+      <c r="B36" s="60" t="s">
         <v>233</v>
       </c>
-      <c r="C36" s="62"/>
-      <c r="D36" s="121">
+      <c r="C36" s="60"/>
+      <c r="D36" s="118">
         <f>IFERROR(IRR(D27:D33),"Check CFs")</f>
         <v>0.17297006771309897</v>
       </c>
     </row>
     <row r="37" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="45" t="s">
+      <c r="B37" s="43" t="s">
         <v>234</v>
       </c>
-      <c r="D37" s="122">
+      <c r="D37" s="119">
         <f>IFERROR(D22/Assumptions!E43,"")</f>
         <v>2.7018246027551323</v>
       </c>
     </row>
     <row r="38" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B38" s="107" t="s">
+      <c r="B38" s="104" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="40" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B40" s="116" t="s">
+      <c r="B40" s="113" t="s">
         <v>236</v>
       </c>
-      <c r="C40" s="116"/>
+      <c r="C40" s="113"/>
       <c r="D40" s="1"/>
     </row>
     <row r="41" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B41" s="37" t="s">
+      <c r="B41" s="35" t="s">
         <v>237</v>
       </c>
-      <c r="D41" s="94">
+      <c r="D41" s="91">
         <f>Assumptions!E43</f>
         <v>9068.4130540000006</v>
       </c>
     </row>
     <row r="42" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B42" s="37" t="s">
+      <c r="B42" s="35" t="s">
         <v>238</v>
       </c>
-      <c r="D42" s="86">
+      <c r="D42" s="83">
         <f>D22-D41</f>
         <v>15432.848443243005</v>
       </c>
     </row>
     <row r="43" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B43" s="37" t="s">
+      <c r="B43" s="35" t="s">
         <v>239</v>
       </c>
-      <c r="D43" s="86">
+      <c r="D43" s="83">
         <f>Assumptions!E42-'Debt Schedule'!H19</f>
         <v>2700</v>
       </c>
     </row>
     <row r="44" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B44" s="37" t="s">
+      <c r="B44" s="35" t="s">
         <v>164</v>
       </c>
-      <c r="D44" s="86">
+      <c r="D44" s="83">
         <f>D22</f>
         <v>24501.261497243006</v>
       </c>
     </row>
     <row r="45" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B45" s="37" t="s">
+      <c r="B45" s="35" t="s">
         <v>240</v>
       </c>
-      <c r="D45" s="123">
+      <c r="D45" s="120">
         <f>IFERROR(D22/Assumptions!E43,"")</f>
         <v>2.7018246027551323</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="DBmKfChwxNqkRRczapjYOd7ojCgDnR26RPa/9v8MTI508GPxySwT09k6HauZiLXiGL+YiXXv/KTzT9QPxnYhMw==" saltValue="ldUilwbOa3rAGruLRtXHPw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="Ngl9lsf9N17DG7csYWh2Z2XzXpVJucapDFcSxTgLVghYPQgfDo3OZ713vZ0z+88NRYm8gtUjdyRljW2ONkTK3A==" saltValue="h/IB1524w7vCmKy6bm+yHg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="98" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87F1537E-989B-4598-B713-1F5D348308BE}">
+  <dimension ref="B1:I34"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="2.33203125" style="128" customWidth="1"/>
+    <col min="2" max="2" width="15.5546875" style="128" customWidth="1"/>
+    <col min="3" max="16384" width="8.88671875" style="128"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:9" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="129" t="s">
+        <v>269</v>
+      </c>
+      <c r="C2" s="129"/>
+      <c r="D2" s="129"/>
+      <c r="E2" s="129"/>
+      <c r="F2" s="129"/>
+      <c r="G2" s="129"/>
+      <c r="H2" s="129"/>
+      <c r="I2" s="129"/>
+    </row>
+    <row r="3" spans="2:9" ht="3" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="130"/>
+      <c r="C3" s="130"/>
+      <c r="D3" s="130"/>
+      <c r="E3" s="130"/>
+      <c r="F3" s="130"/>
+      <c r="G3" s="130"/>
+      <c r="H3" s="130"/>
+      <c r="I3" s="130"/>
+    </row>
+    <row r="5" spans="2:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="131" t="s">
+        <v>282</v>
+      </c>
+      <c r="C5" s="132"/>
+      <c r="D5" s="132"/>
+      <c r="E5" s="132"/>
+      <c r="F5" s="132"/>
+      <c r="G5" s="132"/>
+      <c r="H5" s="132"/>
+      <c r="I5" s="132"/>
+    </row>
+    <row r="6" spans="2:9" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B7" s="133" t="s">
+        <v>270</v>
+      </c>
+      <c r="C7" s="148">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B8" s="133" t="s">
+        <v>271</v>
+      </c>
+      <c r="C8" s="147">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" ht="21.6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="10" spans="2:9" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="134" t="s">
+        <v>273</v>
+      </c>
+      <c r="C10" s="132"/>
+      <c r="D10" s="132"/>
+      <c r="E10" s="132"/>
+      <c r="F10" s="132"/>
+      <c r="G10" s="132"/>
+      <c r="H10" s="132"/>
+      <c r="I10" s="132"/>
+    </row>
+    <row r="11" spans="2:9" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B12" s="145">
+        <f>'LBO Return'!D36</f>
+        <v>0.17297006771309897</v>
+      </c>
+      <c r="C12" s="135">
+        <v>16</v>
+      </c>
+      <c r="D12" s="135">
+        <v>18</v>
+      </c>
+      <c r="E12" s="135">
+        <v>20</v>
+      </c>
+      <c r="F12" s="135">
+        <v>22</v>
+      </c>
+      <c r="G12" s="135">
+        <v>24</v>
+      </c>
+      <c r="H12" s="135">
+        <v>26</v>
+      </c>
+      <c r="I12" s="135">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B13" s="146">
+        <v>0.06</v>
+      </c>
+      <c r="C13" s="142">
+        <f t="dataTable" ref="C13:I17" dt2D="1" dtr="1" r1="C7" r2="C8"/>
+        <v>0.10363160661332715</v>
+      </c>
+      <c r="D13" s="142">
+        <v>0.12580885902026084</v>
+      </c>
+      <c r="E13" s="142">
+        <v>0.1460117860229706</v>
+      </c>
+      <c r="F13" s="142">
+        <v>0.16458990769758652</v>
+      </c>
+      <c r="G13" s="142">
+        <v>0.18180548754836834</v>
+      </c>
+      <c r="H13" s="142">
+        <v>0.19786063218235217</v>
+      </c>
+      <c r="I13" s="142">
+        <v>0.21291456952671317</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B14" s="146">
+        <v>0.08</v>
+      </c>
+      <c r="C14" s="142">
+        <v>0.10776441705451001</v>
+      </c>
+      <c r="D14" s="142">
+        <v>0.12997172988432903</v>
+      </c>
+      <c r="E14" s="142">
+        <v>0.15020502730465557</v>
+      </c>
+      <c r="F14" s="142">
+        <v>0.16881333576554058</v>
+      </c>
+      <c r="G14" s="142">
+        <v>0.18605864381915294</v>
+      </c>
+      <c r="H14" s="142">
+        <v>0.20214290744049879</v>
+      </c>
+      <c r="I14" s="142">
+        <v>0.21722527675951087</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B15" s="146">
+        <v>0.1</v>
+      </c>
+      <c r="C15" s="142">
+        <v>0.11183099746768033</v>
+      </c>
+      <c r="D15" s="142">
+        <v>0.1340682859861293</v>
+      </c>
+      <c r="E15" s="143">
+        <v>0.15433178900802358</v>
+      </c>
+      <c r="F15" s="144">
+        <v>0.17297006771309897</v>
+      </c>
+      <c r="G15" s="142">
+        <v>0.19024485366775412</v>
+      </c>
+      <c r="H15" s="142">
+        <v>0.20635796399028861</v>
+      </c>
+      <c r="I15" s="142">
+        <v>0.2214684789387833</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B16" s="146">
+        <v>0.12</v>
+      </c>
+      <c r="C16" s="142">
+        <v>0.11583370019940298</v>
+      </c>
+      <c r="D16" s="142">
+        <v>0.13810086680498257</v>
+      </c>
+      <c r="E16" s="142">
+        <v>0.15839440354924439</v>
+      </c>
+      <c r="F16" s="142">
+        <v>0.17706243287475254</v>
+      </c>
+      <c r="G16" s="142">
+        <v>0.19436644615296883</v>
+      </c>
+      <c r="H16" s="142">
+        <v>0.21050813263482704</v>
+      </c>
+      <c r="I16" s="142">
+        <v>0.22564651008937209</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B17" s="146">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="C17" s="142">
+        <v>0.11977475103000135</v>
+      </c>
+      <c r="D17" s="142">
+        <v>0.14207168675806736</v>
+      </c>
+      <c r="E17" s="142">
+        <v>0.1623950793216018</v>
+      </c>
+      <c r="F17" s="142">
+        <v>0.18109263726864011</v>
+      </c>
+      <c r="G17" s="142">
+        <v>0.19842562749028581</v>
+      </c>
+      <c r="H17" s="142">
+        <v>0.21459562163370394</v>
+      </c>
+      <c r="I17" s="142">
+        <v>0.22976158186240103</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9" ht="23.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="19" spans="2:9" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="134" t="s">
+        <v>272</v>
+      </c>
+      <c r="C19" s="132"/>
+      <c r="D19" s="132"/>
+      <c r="E19" s="132"/>
+      <c r="F19" s="132"/>
+      <c r="G19" s="132"/>
+      <c r="H19" s="132"/>
+      <c r="I19" s="132"/>
+    </row>
+    <row r="20" spans="2:9" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B21" s="141">
+        <f>'LBO Return'!D37</f>
+        <v>2.7018246027551323</v>
+      </c>
+      <c r="C21" s="149">
+        <v>16</v>
+      </c>
+      <c r="D21" s="149">
+        <v>18</v>
+      </c>
+      <c r="E21" s="149">
+        <v>20</v>
+      </c>
+      <c r="F21" s="149">
+        <v>22</v>
+      </c>
+      <c r="G21" s="149">
+        <v>24</v>
+      </c>
+      <c r="H21" s="149">
+        <v>26</v>
+      </c>
+      <c r="I21" s="149">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B22" s="146">
+        <v>0.06</v>
+      </c>
+      <c r="C22" s="150">
+        <f t="dataTable" ref="C22:I26" dt2D="1" dtr="1" r1="C7" r2="C8" ca="1"/>
+        <v>1.8935101348234316</v>
+      </c>
+      <c r="D22" s="150">
+        <v>2.1301989016763603</v>
+      </c>
+      <c r="E22" s="150">
+        <v>2.366887668529289</v>
+      </c>
+      <c r="F22" s="150">
+        <v>2.6035764353822182</v>
+      </c>
+      <c r="G22" s="150">
+        <v>2.8402652022351469</v>
+      </c>
+      <c r="H22" s="150">
+        <v>3.0769539690880761</v>
+      </c>
+      <c r="I22" s="150">
+        <v>3.3136427359410048</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B23" s="146">
+        <v>0.08</v>
+      </c>
+      <c r="C23" s="150">
+        <v>1.9292367411408546</v>
+      </c>
+      <c r="D23" s="150">
+        <v>2.1703913337834613</v>
+      </c>
+      <c r="E23" s="150">
+        <v>2.4115459264260681</v>
+      </c>
+      <c r="F23" s="150">
+        <v>2.652700519068675</v>
+      </c>
+      <c r="G23" s="150">
+        <v>2.8938551117112823</v>
+      </c>
+      <c r="H23" s="150">
+        <v>3.1350097043538887</v>
+      </c>
+      <c r="I23" s="150">
+        <v>3.3761642969964956</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B24" s="146">
+        <v>0.1</v>
+      </c>
+      <c r="C24" s="150">
+        <v>1.9649633474582777</v>
+      </c>
+      <c r="D24" s="150">
+        <v>2.2105837658905627</v>
+      </c>
+      <c r="E24" s="151">
+        <v>2.4562041843228468</v>
+      </c>
+      <c r="F24" s="152">
+        <v>2.7018246027551323</v>
+      </c>
+      <c r="G24" s="150">
+        <v>2.9474450211874168</v>
+      </c>
+      <c r="H24" s="150">
+        <v>3.1930654396197014</v>
+      </c>
+      <c r="I24" s="150">
+        <v>3.4386858580519863</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B25" s="146">
+        <v>0.12</v>
+      </c>
+      <c r="C25" s="150">
+        <v>2.0006899537757006</v>
+      </c>
+      <c r="D25" s="150">
+        <v>2.2507761979976628</v>
+      </c>
+      <c r="E25" s="150">
+        <v>2.5008624422196255</v>
+      </c>
+      <c r="F25" s="150">
+        <v>2.7509486864415882</v>
+      </c>
+      <c r="G25" s="150">
+        <v>3.0010349306635509</v>
+      </c>
+      <c r="H25" s="150">
+        <v>3.2511211748855131</v>
+      </c>
+      <c r="I25" s="150">
+        <v>3.5012074191074762</v>
+      </c>
+    </row>
+    <row r="26" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B26" s="146">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="C26" s="150">
+        <v>2.0364165600931239</v>
+      </c>
+      <c r="D26" s="150">
+        <v>2.2909686301047643</v>
+      </c>
+      <c r="E26" s="150">
+        <v>2.5455207001164046</v>
+      </c>
+      <c r="F26" s="150">
+        <v>2.8000727701280455</v>
+      </c>
+      <c r="G26" s="150">
+        <v>3.0546248401396854</v>
+      </c>
+      <c r="H26" s="150">
+        <v>3.3091769101513266</v>
+      </c>
+      <c r="I26" s="150">
+        <v>3.563728980162967</v>
+      </c>
+    </row>
+    <row r="27" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="28" spans="2:9" ht="18" x14ac:dyDescent="0.3">
+      <c r="B28" s="136" t="s">
+        <v>274</v>
+      </c>
+      <c r="C28" s="136"/>
+      <c r="D28" s="136"/>
+      <c r="E28" s="136"/>
+      <c r="F28" s="136"/>
+      <c r="G28" s="136"/>
+      <c r="H28" s="136"/>
+      <c r="I28" s="136"/>
+    </row>
+    <row r="29" spans="2:9" ht="6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B29" s="137"/>
+    </row>
+    <row r="30" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B30" s="138" t="s">
+        <v>275</v>
+      </c>
+      <c r="C30" s="139"/>
+      <c r="D30" s="139"/>
+      <c r="E30" s="139"/>
+      <c r="F30" s="139"/>
+      <c r="G30" s="139"/>
+      <c r="H30" s="139"/>
+    </row>
+    <row r="31" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B31" s="138" t="s">
+        <v>276</v>
+      </c>
+      <c r="C31" s="139"/>
+      <c r="D31" s="139"/>
+      <c r="E31" s="139"/>
+      <c r="F31" s="139"/>
+      <c r="G31" s="139"/>
+      <c r="H31" s="139"/>
+    </row>
+    <row r="32" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B32" s="140" t="s">
+        <v>277</v>
+      </c>
+      <c r="C32" s="139"/>
+      <c r="D32" s="139"/>
+      <c r="E32" s="139"/>
+      <c r="F32" s="139"/>
+      <c r="G32" s="139"/>
+      <c r="H32" s="139"/>
+    </row>
+    <row r="33" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B33" s="138" t="s">
+        <v>278</v>
+      </c>
+      <c r="C33" s="139"/>
+      <c r="D33" s="139"/>
+      <c r="E33" s="139"/>
+      <c r="F33" s="139"/>
+      <c r="G33" s="139"/>
+      <c r="H33" s="139"/>
+    </row>
+    <row r="34" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B34" s="138" t="s">
+        <v>279</v>
+      </c>
+      <c r="C34" s="139"/>
+      <c r="D34" s="139"/>
+      <c r="E34" s="139"/>
+      <c r="F34" s="139"/>
+      <c r="G34" s="139"/>
+      <c r="H34" s="139"/>
+    </row>
+  </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="Ol95qezzhflbtGPXWAa+eb/pdga8MAN00Fux2DMSXE6AcFf/rCPXkKhKDi0BpQhync/i1wogCWKQKs2b35CFSA==" saltValue="dY60W3ZymL4i7FOxo+5hPA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <mergeCells count="1">
+    <mergeCell ref="B2:I2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/assets/excel/lbo-model-vedant-fashion.xlsx
+++ b/assets/excel/lbo-model-vedant-fashion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Anvay Document\ANVAY-PORTFOLIO-WEBSITE\assets\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACEFA7E0-58AF-425F-9B5F-957A3A74E9CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93F5E0E0-CE40-4D9F-9F53-8E67C54DE045}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="674" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2790,7 +2790,7 @@
     <xf numFmtId="9" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="153">
+  <cellXfs count="152">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyProtection="1">
       <protection locked="0"/>
@@ -3183,6 +3183,87 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="50" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="45" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="45" fillId="19" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="45" fillId="17" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="42" fillId="15" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="44" fillId="18" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="41" fillId="17" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="172" fontId="41" fillId="17" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="172" fontId="43" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="171" fontId="45" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="45" fillId="19" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="45" fillId="17" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="36" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3190,95 +3271,11 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="45" fillId="0" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="45" fillId="19" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="45" fillId="17" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="42" fillId="15" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="44" fillId="18" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="41" fillId="17" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="172" fontId="41" fillId="17" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="172" fontId="43" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="171" fontId="45" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="45" fillId="19" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="45" fillId="17" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="171" fontId="42" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3690,7 +3687,7 @@
     </row>
     <row r="4" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4"/>
-      <c r="B4" s="126" t="s">
+      <c r="B4" s="124" t="s">
         <v>1</v>
       </c>
       <c r="C4" s="4"/>
@@ -3713,7 +3710,7 @@
     </row>
     <row r="5" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4"/>
-      <c r="B5" s="127" t="s">
+      <c r="B5" s="125" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="4"/>
@@ -3798,12 +3795,12 @@
       <c r="S8" s="6"/>
     </row>
     <row r="10" spans="1:19" ht="18" x14ac:dyDescent="0.35">
-      <c r="B10" s="124" t="s">
+      <c r="B10" s="148" t="s">
         <v>265</v>
       </c>
-      <c r="C10" s="124"/>
-      <c r="D10" s="124"/>
-      <c r="E10" s="124"/>
+      <c r="C10" s="148"/>
+      <c r="D10" s="148"/>
+      <c r="E10" s="148"/>
     </row>
     <row r="11" spans="1:19" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="12" spans="1:19" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
@@ -6462,16 +6459,16 @@
       <c r="E35" s="55"/>
     </row>
     <row r="37" spans="2:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="125" t="s">
+      <c r="B37" s="149" t="s">
         <v>129</v>
       </c>
-      <c r="C37" s="125"/>
-      <c r="D37" s="125"/>
-      <c r="E37" s="125"/>
-      <c r="F37" s="125"/>
-      <c r="G37" s="125"/>
-      <c r="H37" s="125"/>
-      <c r="I37" s="125"/>
+      <c r="C37" s="149"/>
+      <c r="D37" s="149"/>
+      <c r="E37" s="149"/>
+      <c r="F37" s="149"/>
+      <c r="G37" s="149"/>
+      <c r="H37" s="149"/>
+      <c r="I37" s="149"/>
     </row>
     <row r="38" spans="2:9" s="66" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="61" t="s">
@@ -9262,480 +9259,480 @@
   <dimension ref="B1:I34"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.33203125" style="128" customWidth="1"/>
-    <col min="2" max="2" width="15.5546875" style="128" customWidth="1"/>
-    <col min="3" max="16384" width="8.88671875" style="128"/>
+    <col min="1" max="1" width="2.33203125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="15.5546875" style="2" customWidth="1"/>
+    <col min="3" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:9" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:9" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="129" t="s">
+      <c r="B2" s="150" t="s">
         <v>269</v>
       </c>
-      <c r="C2" s="129"/>
-      <c r="D2" s="129"/>
-      <c r="E2" s="129"/>
-      <c r="F2" s="129"/>
-      <c r="G2" s="129"/>
-      <c r="H2" s="129"/>
-      <c r="I2" s="129"/>
+      <c r="C2" s="150"/>
+      <c r="D2" s="150"/>
+      <c r="E2" s="150"/>
+      <c r="F2" s="150"/>
+      <c r="G2" s="150"/>
+      <c r="H2" s="150"/>
+      <c r="I2" s="150"/>
     </row>
     <row r="3" spans="2:9" ht="3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="130"/>
-      <c r="C3" s="130"/>
-      <c r="D3" s="130"/>
-      <c r="E3" s="130"/>
-      <c r="F3" s="130"/>
-      <c r="G3" s="130"/>
-      <c r="H3" s="130"/>
-      <c r="I3" s="130"/>
+      <c r="B3" s="126"/>
+      <c r="C3" s="126"/>
+      <c r="D3" s="126"/>
+      <c r="E3" s="126"/>
+      <c r="F3" s="126"/>
+      <c r="G3" s="126"/>
+      <c r="H3" s="126"/>
+      <c r="I3" s="126"/>
     </row>
     <row r="5" spans="2:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="131" t="s">
+      <c r="B5" s="127" t="s">
         <v>282</v>
       </c>
-      <c r="C5" s="132"/>
-      <c r="D5" s="132"/>
-      <c r="E5" s="132"/>
-      <c r="F5" s="132"/>
-      <c r="G5" s="132"/>
-      <c r="H5" s="132"/>
-      <c r="I5" s="132"/>
+      <c r="C5" s="128"/>
+      <c r="D5" s="128"/>
+      <c r="E5" s="128"/>
+      <c r="F5" s="128"/>
+      <c r="G5" s="128"/>
+      <c r="H5" s="128"/>
+      <c r="I5" s="128"/>
     </row>
     <row r="6" spans="2:9" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="7" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B7" s="133" t="s">
+      <c r="B7" s="129" t="s">
         <v>270</v>
       </c>
-      <c r="C7" s="148">
+      <c r="C7" s="143">
         <v>22</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B8" s="133" t="s">
+      <c r="B8" s="129" t="s">
         <v>271</v>
       </c>
-      <c r="C8" s="147">
+      <c r="C8" s="142">
         <v>0.1</v>
       </c>
     </row>
     <row r="9" spans="2:9" ht="21.6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="10" spans="2:9" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="134" t="s">
+      <c r="B10" s="130" t="s">
         <v>273</v>
       </c>
-      <c r="C10" s="132"/>
-      <c r="D10" s="132"/>
-      <c r="E10" s="132"/>
-      <c r="F10" s="132"/>
-      <c r="G10" s="132"/>
-      <c r="H10" s="132"/>
-      <c r="I10" s="132"/>
+      <c r="C10" s="128"/>
+      <c r="D10" s="128"/>
+      <c r="E10" s="128"/>
+      <c r="F10" s="128"/>
+      <c r="G10" s="128"/>
+      <c r="H10" s="128"/>
+      <c r="I10" s="128"/>
     </row>
     <row r="11" spans="2:9" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="12" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B12" s="145">
+      <c r="B12" s="140">
         <f>'LBO Return'!D36</f>
         <v>0.17297006771309897</v>
       </c>
-      <c r="C12" s="135">
+      <c r="C12" s="131">
         <v>16</v>
       </c>
-      <c r="D12" s="135">
+      <c r="D12" s="131">
         <v>18</v>
       </c>
-      <c r="E12" s="135">
+      <c r="E12" s="131">
         <v>20</v>
       </c>
-      <c r="F12" s="135">
+      <c r="F12" s="131">
         <v>22</v>
       </c>
-      <c r="G12" s="135">
+      <c r="G12" s="131">
         <v>24</v>
       </c>
-      <c r="H12" s="135">
+      <c r="H12" s="131">
         <v>26</v>
       </c>
-      <c r="I12" s="135">
+      <c r="I12" s="131">
         <v>28</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B13" s="146">
+      <c r="B13" s="141">
         <v>0.06</v>
       </c>
-      <c r="C13" s="142">
+      <c r="C13" s="137">
         <f t="dataTable" ref="C13:I17" dt2D="1" dtr="1" r1="C7" r2="C8"/>
         <v>0.10363160661332715</v>
       </c>
-      <c r="D13" s="142">
+      <c r="D13" s="137">
         <v>0.12580885902026084</v>
       </c>
-      <c r="E13" s="142">
+      <c r="E13" s="137">
         <v>0.1460117860229706</v>
       </c>
-      <c r="F13" s="142">
+      <c r="F13" s="137">
         <v>0.16458990769758652</v>
       </c>
-      <c r="G13" s="142">
+      <c r="G13" s="137">
         <v>0.18180548754836834</v>
       </c>
-      <c r="H13" s="142">
+      <c r="H13" s="137">
         <v>0.19786063218235217</v>
       </c>
-      <c r="I13" s="142">
+      <c r="I13" s="137">
         <v>0.21291456952671317</v>
       </c>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B14" s="146">
+      <c r="B14" s="141">
         <v>0.08</v>
       </c>
-      <c r="C14" s="142">
+      <c r="C14" s="137">
         <v>0.10776441705451001</v>
       </c>
-      <c r="D14" s="142">
+      <c r="D14" s="137">
         <v>0.12997172988432903</v>
       </c>
-      <c r="E14" s="142">
+      <c r="E14" s="137">
         <v>0.15020502730465557</v>
       </c>
-      <c r="F14" s="142">
+      <c r="F14" s="137">
         <v>0.16881333576554058</v>
       </c>
-      <c r="G14" s="142">
+      <c r="G14" s="137">
         <v>0.18605864381915294</v>
       </c>
-      <c r="H14" s="142">
+      <c r="H14" s="137">
         <v>0.20214290744049879</v>
       </c>
-      <c r="I14" s="142">
+      <c r="I14" s="137">
         <v>0.21722527675951087</v>
       </c>
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B15" s="146">
+      <c r="B15" s="141">
         <v>0.1</v>
       </c>
-      <c r="C15" s="142">
+      <c r="C15" s="137">
         <v>0.11183099746768033</v>
       </c>
-      <c r="D15" s="142">
+      <c r="D15" s="137">
         <v>0.1340682859861293</v>
       </c>
-      <c r="E15" s="143">
+      <c r="E15" s="138">
         <v>0.15433178900802358</v>
       </c>
-      <c r="F15" s="144">
+      <c r="F15" s="139">
         <v>0.17297006771309897</v>
       </c>
-      <c r="G15" s="142">
+      <c r="G15" s="137">
         <v>0.19024485366775412</v>
       </c>
-      <c r="H15" s="142">
+      <c r="H15" s="137">
         <v>0.20635796399028861</v>
       </c>
-      <c r="I15" s="142">
+      <c r="I15" s="137">
         <v>0.2214684789387833</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B16" s="146">
+      <c r="B16" s="141">
         <v>0.12</v>
       </c>
-      <c r="C16" s="142">
+      <c r="C16" s="137">
         <v>0.11583370019940298</v>
       </c>
-      <c r="D16" s="142">
+      <c r="D16" s="137">
         <v>0.13810086680498257</v>
       </c>
-      <c r="E16" s="142">
+      <c r="E16" s="137">
         <v>0.15839440354924439</v>
       </c>
-      <c r="F16" s="142">
+      <c r="F16" s="137">
         <v>0.17706243287475254</v>
       </c>
-      <c r="G16" s="142">
+      <c r="G16" s="137">
         <v>0.19436644615296883</v>
       </c>
-      <c r="H16" s="142">
+      <c r="H16" s="137">
         <v>0.21050813263482704</v>
       </c>
-      <c r="I16" s="142">
+      <c r="I16" s="137">
         <v>0.22564651008937209</v>
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B17" s="146">
+      <c r="B17" s="141">
         <v>0.14000000000000001</v>
       </c>
-      <c r="C17" s="142">
+      <c r="C17" s="137">
         <v>0.11977475103000135</v>
       </c>
-      <c r="D17" s="142">
+      <c r="D17" s="137">
         <v>0.14207168675806736</v>
       </c>
-      <c r="E17" s="142">
+      <c r="E17" s="137">
         <v>0.1623950793216018</v>
       </c>
-      <c r="F17" s="142">
+      <c r="F17" s="137">
         <v>0.18109263726864011</v>
       </c>
-      <c r="G17" s="142">
+      <c r="G17" s="137">
         <v>0.19842562749028581</v>
       </c>
-      <c r="H17" s="142">
+      <c r="H17" s="137">
         <v>0.21459562163370394</v>
       </c>
-      <c r="I17" s="142">
+      <c r="I17" s="137">
         <v>0.22976158186240103</v>
       </c>
     </row>
     <row r="18" spans="2:9" ht="23.4" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="19" spans="2:9" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="134" t="s">
+      <c r="B19" s="130" t="s">
         <v>272</v>
       </c>
-      <c r="C19" s="132"/>
-      <c r="D19" s="132"/>
-      <c r="E19" s="132"/>
-      <c r="F19" s="132"/>
-      <c r="G19" s="132"/>
-      <c r="H19" s="132"/>
-      <c r="I19" s="132"/>
+      <c r="C19" s="128"/>
+      <c r="D19" s="128"/>
+      <c r="E19" s="128"/>
+      <c r="F19" s="128"/>
+      <c r="G19" s="128"/>
+      <c r="H19" s="128"/>
+      <c r="I19" s="128"/>
     </row>
     <row r="20" spans="2:9" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="21" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B21" s="141">
+      <c r="B21" s="151">
         <f>'LBO Return'!D37</f>
         <v>2.7018246027551323</v>
       </c>
-      <c r="C21" s="149">
+      <c r="C21" s="144">
         <v>16</v>
       </c>
-      <c r="D21" s="149">
+      <c r="D21" s="144">
         <v>18</v>
       </c>
-      <c r="E21" s="149">
+      <c r="E21" s="144">
         <v>20</v>
       </c>
-      <c r="F21" s="149">
+      <c r="F21" s="144">
         <v>22</v>
       </c>
-      <c r="G21" s="149">
+      <c r="G21" s="144">
         <v>24</v>
       </c>
-      <c r="H21" s="149">
+      <c r="H21" s="144">
         <v>26</v>
       </c>
-      <c r="I21" s="149">
+      <c r="I21" s="144">
         <v>28</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B22" s="146">
+      <c r="B22" s="141">
         <v>0.06</v>
       </c>
-      <c r="C22" s="150">
+      <c r="C22" s="145">
         <f t="dataTable" ref="C22:I26" dt2D="1" dtr="1" r1="C7" r2="C8" ca="1"/>
         <v>1.8935101348234316</v>
       </c>
-      <c r="D22" s="150">
+      <c r="D22" s="145">
         <v>2.1301989016763603</v>
       </c>
-      <c r="E22" s="150">
+      <c r="E22" s="145">
         <v>2.366887668529289</v>
       </c>
-      <c r="F22" s="150">
+      <c r="F22" s="145">
         <v>2.6035764353822182</v>
       </c>
-      <c r="G22" s="150">
+      <c r="G22" s="145">
         <v>2.8402652022351469</v>
       </c>
-      <c r="H22" s="150">
+      <c r="H22" s="145">
         <v>3.0769539690880761</v>
       </c>
-      <c r="I22" s="150">
+      <c r="I22" s="145">
         <v>3.3136427359410048</v>
       </c>
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B23" s="146">
+      <c r="B23" s="141">
         <v>0.08</v>
       </c>
-      <c r="C23" s="150">
+      <c r="C23" s="145">
         <v>1.9292367411408546</v>
       </c>
-      <c r="D23" s="150">
+      <c r="D23" s="145">
         <v>2.1703913337834613</v>
       </c>
-      <c r="E23" s="150">
+      <c r="E23" s="145">
         <v>2.4115459264260681</v>
       </c>
-      <c r="F23" s="150">
+      <c r="F23" s="145">
         <v>2.652700519068675</v>
       </c>
-      <c r="G23" s="150">
+      <c r="G23" s="145">
         <v>2.8938551117112823</v>
       </c>
-      <c r="H23" s="150">
+      <c r="H23" s="145">
         <v>3.1350097043538887</v>
       </c>
-      <c r="I23" s="150">
+      <c r="I23" s="145">
         <v>3.3761642969964956</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B24" s="146">
+      <c r="B24" s="141">
         <v>0.1</v>
       </c>
-      <c r="C24" s="150">
+      <c r="C24" s="145">
         <v>1.9649633474582777</v>
       </c>
-      <c r="D24" s="150">
+      <c r="D24" s="145">
         <v>2.2105837658905627</v>
       </c>
-      <c r="E24" s="151">
+      <c r="E24" s="146">
         <v>2.4562041843228468</v>
       </c>
-      <c r="F24" s="152">
+      <c r="F24" s="147">
         <v>2.7018246027551323</v>
       </c>
-      <c r="G24" s="150">
+      <c r="G24" s="145">
         <v>2.9474450211874168</v>
       </c>
-      <c r="H24" s="150">
+      <c r="H24" s="145">
         <v>3.1930654396197014</v>
       </c>
-      <c r="I24" s="150">
+      <c r="I24" s="145">
         <v>3.4386858580519863</v>
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B25" s="146">
+      <c r="B25" s="141">
         <v>0.12</v>
       </c>
-      <c r="C25" s="150">
+      <c r="C25" s="145">
         <v>2.0006899537757006</v>
       </c>
-      <c r="D25" s="150">
+      <c r="D25" s="145">
         <v>2.2507761979976628</v>
       </c>
-      <c r="E25" s="150">
+      <c r="E25" s="145">
         <v>2.5008624422196255</v>
       </c>
-      <c r="F25" s="150">
+      <c r="F25" s="145">
         <v>2.7509486864415882</v>
       </c>
-      <c r="G25" s="150">
+      <c r="G25" s="145">
         <v>3.0010349306635509</v>
       </c>
-      <c r="H25" s="150">
+      <c r="H25" s="145">
         <v>3.2511211748855131</v>
       </c>
-      <c r="I25" s="150">
+      <c r="I25" s="145">
         <v>3.5012074191074762</v>
       </c>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B26" s="146">
+      <c r="B26" s="141">
         <v>0.14000000000000001</v>
       </c>
-      <c r="C26" s="150">
+      <c r="C26" s="145">
         <v>2.0364165600931239</v>
       </c>
-      <c r="D26" s="150">
+      <c r="D26" s="145">
         <v>2.2909686301047643</v>
       </c>
-      <c r="E26" s="150">
+      <c r="E26" s="145">
         <v>2.5455207001164046</v>
       </c>
-      <c r="F26" s="150">
+      <c r="F26" s="145">
         <v>2.8000727701280455</v>
       </c>
-      <c r="G26" s="150">
+      <c r="G26" s="145">
         <v>3.0546248401396854</v>
       </c>
-      <c r="H26" s="150">
+      <c r="H26" s="145">
         <v>3.3091769101513266</v>
       </c>
-      <c r="I26" s="150">
+      <c r="I26" s="145">
         <v>3.563728980162967</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="21" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="28" spans="2:9" ht="18" x14ac:dyDescent="0.3">
-      <c r="B28" s="136" t="s">
+      <c r="B28" s="132" t="s">
         <v>274</v>
       </c>
-      <c r="C28" s="136"/>
-      <c r="D28" s="136"/>
-      <c r="E28" s="136"/>
-      <c r="F28" s="136"/>
-      <c r="G28" s="136"/>
-      <c r="H28" s="136"/>
-      <c r="I28" s="136"/>
+      <c r="C28" s="132"/>
+      <c r="D28" s="132"/>
+      <c r="E28" s="132"/>
+      <c r="F28" s="132"/>
+      <c r="G28" s="132"/>
+      <c r="H28" s="132"/>
+      <c r="I28" s="132"/>
     </row>
     <row r="29" spans="2:9" ht="6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="137"/>
+      <c r="B29" s="133"/>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B30" s="138" t="s">
+      <c r="B30" s="134" t="s">
         <v>275</v>
       </c>
-      <c r="C30" s="139"/>
-      <c r="D30" s="139"/>
-      <c r="E30" s="139"/>
-      <c r="F30" s="139"/>
-      <c r="G30" s="139"/>
-      <c r="H30" s="139"/>
+      <c r="C30" s="135"/>
+      <c r="D30" s="135"/>
+      <c r="E30" s="135"/>
+      <c r="F30" s="135"/>
+      <c r="G30" s="135"/>
+      <c r="H30" s="135"/>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B31" s="138" t="s">
+      <c r="B31" s="134" t="s">
         <v>276</v>
       </c>
-      <c r="C31" s="139"/>
-      <c r="D31" s="139"/>
-      <c r="E31" s="139"/>
-      <c r="F31" s="139"/>
-      <c r="G31" s="139"/>
-      <c r="H31" s="139"/>
+      <c r="C31" s="135"/>
+      <c r="D31" s="135"/>
+      <c r="E31" s="135"/>
+      <c r="F31" s="135"/>
+      <c r="G31" s="135"/>
+      <c r="H31" s="135"/>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B32" s="140" t="s">
+      <c r="B32" s="136" t="s">
         <v>277</v>
       </c>
-      <c r="C32" s="139"/>
-      <c r="D32" s="139"/>
-      <c r="E32" s="139"/>
-      <c r="F32" s="139"/>
-      <c r="G32" s="139"/>
-      <c r="H32" s="139"/>
+      <c r="C32" s="135"/>
+      <c r="D32" s="135"/>
+      <c r="E32" s="135"/>
+      <c r="F32" s="135"/>
+      <c r="G32" s="135"/>
+      <c r="H32" s="135"/>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B33" s="138" t="s">
+      <c r="B33" s="134" t="s">
         <v>278</v>
       </c>
-      <c r="C33" s="139"/>
-      <c r="D33" s="139"/>
-      <c r="E33" s="139"/>
-      <c r="F33" s="139"/>
-      <c r="G33" s="139"/>
-      <c r="H33" s="139"/>
+      <c r="C33" s="135"/>
+      <c r="D33" s="135"/>
+      <c r="E33" s="135"/>
+      <c r="F33" s="135"/>
+      <c r="G33" s="135"/>
+      <c r="H33" s="135"/>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B34" s="138" t="s">
+      <c r="B34" s="134" t="s">
         <v>279</v>
       </c>
-      <c r="C34" s="139"/>
-      <c r="D34" s="139"/>
-      <c r="E34" s="139"/>
-      <c r="F34" s="139"/>
-      <c r="G34" s="139"/>
-      <c r="H34" s="139"/>
+      <c r="C34" s="135"/>
+      <c r="D34" s="135"/>
+      <c r="E34" s="135"/>
+      <c r="F34" s="135"/>
+      <c r="G34" s="135"/>
+      <c r="H34" s="135"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="Ol95qezzhflbtGPXWAa+eb/pdga8MAN00Fux2DMSXE6AcFf/rCPXkKhKDi0BpQhync/i1wogCWKQKs2b35CFSA==" saltValue="dY60W3ZymL4i7FOxo+5hPA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="Jq/Q+B+dy4CojsjEPwRop2yGnp8AGCZGtGI/zm2nG7wMd1McL5Md0G82XdOXD8zqyWki5wBNfOBw9oAgWWS9zQ==" saltValue="7f19duQ3o3+8bg5RLjrRLw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="B2:I2"/>
   </mergeCells>
